--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rf472aa2292094093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R2d46dfc3eb5143a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="Rc2b5357f462b468a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R0c3025637cf24cb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rf8ca5c858eb94106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R63fcad1c82574fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R82f29ea3d02e441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R276474ebc1324d89"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,7 +133,10 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -144,35 +147,37 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable1" displayName="WeeklyTable1" ref="A1:Q5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Q5"/>
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable1" displayName="WeeklyTable1" ref="A1:S5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:S5"/>
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="层级"/>
     <x:tableColumn id="2" name="名称"/>
     <x:tableColumn id="3" name="总营收"/>
     <x:tableColumn id="4" name="目标"/>
     <x:tableColumn id="5" name="完成率"/>
-    <x:tableColumn id="6" name="新客数"/>
-    <x:tableColumn id="7" name="老客数"/>
-    <x:tableColumn id="8" name="总办卡数"/>
-    <x:tableColumn id="9" name="新签小卡数"/>
-    <x:tableColumn id="10" name="新签中卡数"/>
-    <x:tableColumn id="11" name="新签大卡数"/>
-    <x:tableColumn id="12" name="新签小卡率"/>
-    <x:tableColumn id="13" name="新签中卡率"/>
-    <x:tableColumn id="14" name="新签大卡率"/>
-    <x:tableColumn id="15" name="续费率"/>
-    <x:tableColumn id="16" name="续卡金额"/>
-    <x:tableColumn id="17" name="总引流金额"/>
+    <x:tableColumn id="6" name="总接待人数"/>
+    <x:tableColumn id="7" name="新客数"/>
+    <x:tableColumn id="8" name="老客数"/>
+    <x:tableColumn id="9" name="总办卡数"/>
+    <x:tableColumn id="10" name="新签卡数"/>
+    <x:tableColumn id="11" name="新签小卡数"/>
+    <x:tableColumn id="12" name="新签中卡数"/>
+    <x:tableColumn id="13" name="新签大卡数"/>
+    <x:tableColumn id="14" name="新签小卡率"/>
+    <x:tableColumn id="15" name="新签中卡率"/>
+    <x:tableColumn id="16" name="新签大卡率"/>
+    <x:tableColumn id="17" name="续费率"/>
+    <x:tableColumn id="18" name="续卡金额"/>
+    <x:tableColumn id="19" name="总引流金额"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable2" displayName="WeeklyTable2" ref="A1:V20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:V20"/>
-  <x:tableColumns count="22">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable2" displayName="WeeklyTable2" ref="A1:Y20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Y20"/>
+  <x:tableColumns count="25">
     <x:tableColumn id="1" name="区域"/>
     <x:tableColumn id="2" name="门店"/>
     <x:tableColumn id="3" name="总营收"/>
@@ -183,18 +188,21 @@
     <x:tableColumn id="8" name="老客数"/>
     <x:tableColumn id="9" name="新签营收"/>
     <x:tableColumn id="10" name="总办卡数"/>
-    <x:tableColumn id="11" name="新签小卡数"/>
-    <x:tableColumn id="12" name="新签中卡数"/>
-    <x:tableColumn id="13" name="新签大卡数"/>
-    <x:tableColumn id="14" name="新签小卡率"/>
-    <x:tableColumn id="15" name="新签中卡率"/>
-    <x:tableColumn id="16" name="新签大卡率"/>
-    <x:tableColumn id="17" name="续费率"/>
-    <x:tableColumn id="18" name="总续卡金额"/>
-    <x:tableColumn id="19" name="总引流金额"/>
-    <x:tableColumn id="20" name="扫楼金额"/>
-    <x:tableColumn id="21" name="异常指标"/>
-    <x:tableColumn id="22" name="来源"/>
+    <x:tableColumn id="11" name="新签卡数"/>
+    <x:tableColumn id="12" name="新签小卡数"/>
+    <x:tableColumn id="13" name="新签中卡数"/>
+    <x:tableColumn id="14" name="新签大卡数"/>
+    <x:tableColumn id="15" name="新签小卡率"/>
+    <x:tableColumn id="16" name="新签中卡率"/>
+    <x:tableColumn id="17" name="新签大卡率"/>
+    <x:tableColumn id="18" name="新签办卡率"/>
+    <x:tableColumn id="19" name="续卡数"/>
+    <x:tableColumn id="20" name="续费率"/>
+    <x:tableColumn id="21" name="总续卡金额"/>
+    <x:tableColumn id="22" name="总引流金额"/>
+    <x:tableColumn id="23" name="扫楼金额"/>
+    <x:tableColumn id="24" name="异常指标"/>
+    <x:tableColumn id="25" name="来源"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -498,18 +506,20 @@
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -529,39 +539,45 @@
         <x:v>完成率</x:v>
       </x:c>
       <x:c r="F1" s="8" t="str">
+        <x:v>总接待人数</x:v>
+      </x:c>
+      <x:c r="G1" s="8" t="str">
         <x:v>新客数</x:v>
       </x:c>
-      <x:c r="G1" s="8" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>老客数</x:v>
       </x:c>
-      <x:c r="H1" s="8" t="str">
+      <x:c r="I1" s="8" t="str">
         <x:v>总办卡数</x:v>
       </x:c>
-      <x:c r="I1" s="8" t="str">
+      <x:c r="J1" s="8" t="str">
+        <x:v>新签卡数</x:v>
+      </x:c>
+      <x:c r="K1" s="8" t="str">
         <x:v>新签小卡数</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>新签中卡数</x:v>
       </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>新签大卡数</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>新签小卡率</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="O1" s="8" t="str">
         <x:v>新签中卡率</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="P1" s="8" t="str">
         <x:v>新签大卡率</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>续费率</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="R1" s="8" t="str">
         <x:v>续卡金额</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="S1" s="8" t="str">
         <x:v>总引流金额</x:v>
       </x:c>
     </x:row>
@@ -573,48 +589,54 @@
         <x:v>品牌总览</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>389260.07000000007</x:v>
+        <x:v>389746.07</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>529609</x:v>
       </x:c>
       <x:c r="E2" s="12" t="n">
-        <x:v>0.7349951945680683</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>待核</x:v>
+        <x:v>0.7359</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="n">
+        <x:v>9044</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="n">
+      <x:c r="H2" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="I2" s="4" t="n">
         <x:v>804</x:v>
       </x:c>
-      <x:c r="I2" s="4" t="n">
+      <x:c r="J2" s="4" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="n">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="J2" s="4" t="n">
+      <x:c r="L2" s="4" t="n">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="n">
+      <x:c r="M2" s="4" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="n">
+      <x:c r="N2" s="12" t="n">
         <x:v>0.5206349206349207</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="n">
+      <x:c r="O2" s="12" t="n">
         <x:v>0.3761904761904762</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="n">
+      <x:c r="P2" s="12" t="n">
         <x:v>0.10317460317460317</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="n">
+      <x:c r="Q2" s="12" t="n">
         <x:v>0.081</x:v>
       </x:c>
-      <x:c r="P2" s="11" t="n">
+      <x:c r="R2" s="11" t="n">
         <x:v>92111.15</x:v>
       </x:c>
-      <x:c r="Q2" s="11" t="n">
+      <x:c r="S2" s="11" t="n">
         <x:v>173051.7</x:v>
       </x:c>
     </x:row>
@@ -640,28 +662,34 @@
       <x:c r="G3" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="n">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="n">
-        <x:v>117</x:v>
+      <x:c r="H3" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="str">
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="J3" s="4" t="n">
-        <x:v>67</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="K3" s="4" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M3" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L3" s="12" t="n">
-        <x:v>0.5939086294416244</x:v>
-      </x:c>
-      <x:c r="M3" s="12"/>
-      <x:c r="N3" s="12"/>
-      <x:c r="O3" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="P3" s="11"/>
-      <x:c r="Q3" s="11"/>
+      <x:c r="N3" s="12" t="n">
+        <x:v>0.6386138613861386</x:v>
+      </x:c>
+      <x:c r="O3" s="12"/>
+      <x:c r="P3" s="12"/>
+      <x:c r="Q3" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="R3" s="11"/>
+      <x:c r="S3" s="11"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="str">
@@ -685,28 +713,34 @@
       <x:c r="G4" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="H4" s="4" t="n">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="n">
-        <x:v>98</x:v>
+      <x:c r="H4" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="str">
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="J4" s="4" t="n">
-        <x:v>90</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K4" s="4" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L4" s="12" t="n">
-        <x:v>0.46445497630331756</x:v>
-      </x:c>
-      <x:c r="M4" s="12"/>
-      <x:c r="N4" s="12"/>
-      <x:c r="O4" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="P4" s="11"/>
-      <x:c r="Q4" s="11"/>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N4" s="12" t="n">
+        <x:v>0.4553990610328638</x:v>
+      </x:c>
+      <x:c r="O4" s="12"/>
+      <x:c r="P4" s="12"/>
+      <x:c r="Q4" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="R4" s="11"/>
+      <x:c r="S4" s="11"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
@@ -730,33 +764,39 @@
       <x:c r="G5" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="H5" s="4" t="n">
+      <x:c r="H5" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="I5" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="n">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="n">
+      <x:c r="K5" s="4" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="J5" s="4" t="n">
+      <x:c r="L5" s="4" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="K5" s="4" t="n">
+      <x:c r="M5" s="4" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L5" s="12" t="n">
+      <x:c r="N5" s="12" t="n">
         <x:v>0.5263157894736842</x:v>
       </x:c>
-      <x:c r="M5" s="12"/>
-      <x:c r="N5" s="12"/>
-      <x:c r="O5" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="P5" s="11"/>
-      <x:c r="Q5" s="11"/>
+      <x:c r="O5" s="12"/>
+      <x:c r="P5" s="12"/>
+      <x:c r="Q5" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="R5" s="11"/>
+      <x:c r="S5" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd25dac6fd5524e72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f02075e58054f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -821,39 +861,48 @@
         <x:v>总办卡数</x:v>
       </x:c>
       <x:c r="K1" s="8" t="str">
+        <x:v>新签卡数</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
         <x:v>新签小卡数</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>新签中卡数</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>新签大卡数</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="O1" s="8" t="str">
         <x:v>新签小卡率</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="P1" s="8" t="str">
         <x:v>新签中卡率</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>新签大卡率</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="R1" s="8" t="str">
+        <x:v>新签办卡率</x:v>
+      </x:c>
+      <x:c r="S1" s="8" t="str">
+        <x:v>续卡数</x:v>
+      </x:c>
+      <x:c r="T1" s="8" t="str">
         <x:v>续费率</x:v>
       </x:c>
-      <x:c r="R1" s="8" t="str">
+      <x:c r="U1" s="8" t="str">
         <x:v>总续卡金额</x:v>
       </x:c>
-      <x:c r="S1" s="8" t="str">
+      <x:c r="V1" s="8" t="str">
         <x:v>总引流金额</x:v>
       </x:c>
-      <x:c r="T1" s="8" t="str">
+      <x:c r="W1" s="8" t="str">
         <x:v>扫楼金额</x:v>
       </x:c>
-      <x:c r="U1" s="8" t="str">
+      <x:c r="X1" s="8" t="str">
         <x:v>异常指标</x:v>
       </x:c>
-      <x:c r="V1" s="8" t="str">
+      <x:c r="Y1" s="8" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
@@ -874,7 +923,7 @@
         <x:v>0.9125015463024816</x:v>
       </x:c>
       <x:c r="F2" s="12" t="n">
-        <x:v>0.0012211654892511402</x:v>
+        <x:v>0.12211654892511403</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>待核</x:v>
@@ -882,47 +931,56 @@
       <x:c r="H2" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I2" s="11" t="n">
+        <x:v>15240</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="n">
+      <x:c r="L2" s="4" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L2" s="4" t="n">
+      <x:c r="M2" s="4" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="M2" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="13" t="n">
+      <x:c r="N2" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="n">
         <x:v>0.5476190476190477</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="n">
+      <x:c r="P2" s="12" t="n">
         <x:v>0.4523809523809524</x:v>
       </x:c>
-      <x:c r="P2" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q2" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R2" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S2" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T2" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U2" s="14" t="str">
+      <x:c r="Q2" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R2" s="12" t="n">
+        <x:v>0.5122</x:v>
+      </x:c>
+      <x:c r="S2" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="T2" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U2" s="15" t="n">
+        <x:v>17800</x:v>
+      </x:c>
+      <x:c r="V2" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W2" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X2" s="4" t="str">
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
-      <x:c r="V2" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y2" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -942,7 +1000,7 @@
         <x:v>0.7739704209328783</x:v>
       </x:c>
       <x:c r="F3" s="12" t="n">
-        <x:v>-0.004782983717375627</x:v>
+        <x:v>-0.47829837173756273</x:v>
       </x:c>
       <x:c r="G3" s="4" t="str">
         <x:v>待核</x:v>
@@ -950,47 +1008,56 @@
       <x:c r="H3" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I3" s="11" t="n">
+        <x:v>16461</x:v>
       </x:c>
       <x:c r="J3" s="4" t="n">
-        <x:v>43</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K3" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="L3" s="4" t="n">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M3" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N3" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N3" s="13" t="n">
-        <x:v>0.5348837209302325</x:v>
-      </x:c>
       <x:c r="O3" s="12" t="n">
-        <x:v>0.32558139534883723</x:v>
+        <x:v>0.5641025641025641</x:v>
       </x:c>
       <x:c r="P3" s="12" t="n">
-        <x:v>0.13953488372093023</x:v>
-      </x:c>
-      <x:c r="Q3" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R3" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S3" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T3" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U3" s="14" t="str">
-        <x:v>完成率77.40%&lt;100%；新签小卡率53.49%&gt;40%</x:v>
-      </x:c>
-      <x:c r="V3" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+        <x:v>0.28205128205128205</x:v>
+      </x:c>
+      <x:c r="Q3" s="12" t="n">
+        <x:v>0.15384615384615385</x:v>
+      </x:c>
+      <x:c r="R3" s="12" t="n">
+        <x:v>0.41490000000000005</x:v>
+      </x:c>
+      <x:c r="S3" s="4" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="T3" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U3" s="15" t="n">
+        <x:v>12299</x:v>
+      </x:c>
+      <x:c r="V3" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W3" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X3" s="4" t="str">
+        <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
+      </x:c>
+      <x:c r="Y3" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1010,7 +1077,7 @@
         <x:v>0.8902115631192448</x:v>
       </x:c>
       <x:c r="F4" s="12" t="n">
-        <x:v>0.0026773042287421673</x:v>
+        <x:v>0.2677304228742167</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
         <x:v>待核</x:v>
@@ -1018,47 +1085,56 @@
       <x:c r="H4" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I4" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I4" s="11" t="n">
+        <x:v>20415</x:v>
       </x:c>
       <x:c r="J4" s="4" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K4" s="4" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K4" s="4" t="n">
+      <x:c r="L4" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="L4" s="4" t="n">
+      <x:c r="M4" s="4" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="M4" s="4" t="n">
+      <x:c r="N4" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N4" s="13" t="n">
+      <x:c r="O4" s="12" t="n">
         <x:v>0.6274509803921569</x:v>
       </x:c>
-      <x:c r="O4" s="12" t="n">
+      <x:c r="P4" s="12" t="n">
         <x:v>0.33333333333333326</x:v>
       </x:c>
-      <x:c r="P4" s="12" t="n">
+      <x:c r="Q4" s="12" t="n">
         <x:v>0.0392156862745098</x:v>
       </x:c>
-      <x:c r="Q4" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R4" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S4" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T4" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U4" s="14" t="str">
+      <x:c r="R4" s="12" t="n">
+        <x:v>0.5204</x:v>
+      </x:c>
+      <x:c r="S4" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="T4" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U4" s="15" t="n">
+        <x:v>6900</x:v>
+      </x:c>
+      <x:c r="V4" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W4" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X4" s="4" t="str">
         <x:v>完成率89.02%&lt;100%；新签小卡率62.75%&gt;40%</x:v>
       </x:c>
-      <x:c r="V4" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y4" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1078,7 +1154,7 @@
         <x:v>0.6871246587807097</x:v>
       </x:c>
       <x:c r="F5" s="12" t="n">
-        <x:v>-0.001063842376190758</x:v>
+        <x:v>-0.1063842376190758</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>待核</x:v>
@@ -1086,47 +1162,56 @@
       <x:c r="H5" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I5" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I5" s="11" t="n">
+        <x:v>24256</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K5" s="4" t="n">
+      <x:c r="L5" s="4" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="L5" s="4" t="n">
+      <x:c r="M5" s="4" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="M5" s="4" t="n">
+      <x:c r="N5" s="14" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N5" s="13" t="n">
+      <x:c r="O5" s="12" t="n">
         <x:v>0.6491228070175439</x:v>
       </x:c>
-      <x:c r="O5" s="12" t="n">
+      <x:c r="P5" s="12" t="n">
         <x:v>0.24561403508771928</x:v>
       </x:c>
-      <x:c r="P5" s="12" t="n">
+      <x:c r="Q5" s="12" t="n">
         <x:v>0.10526315789473684</x:v>
       </x:c>
-      <x:c r="Q5" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R5" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S5" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T5" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U5" s="14" t="str">
+      <x:c r="R5" s="12" t="n">
+        <x:v>0.5938</x:v>
+      </x:c>
+      <x:c r="S5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T5" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U5" s="15" t="n">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="V5" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W5" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X5" s="4" t="str">
         <x:v>完成率68.71%&lt;100%；新签小卡率64.91%&gt;40%</x:v>
       </x:c>
-      <x:c r="V5" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y5" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1146,7 +1231,7 @@
         <x:v>0.7769876627827279</x:v>
       </x:c>
       <x:c r="F6" s="12" t="n">
-        <x:v>0.00034781781876961113</x:v>
+        <x:v>0.03478178187696111</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
         <x:v>待核</x:v>
@@ -1154,47 +1239,56 @@
       <x:c r="H6" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I6" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I6" s="11" t="n">
+        <x:v>21837</x:v>
       </x:c>
       <x:c r="J6" s="4" t="n">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K6" s="4" t="n">
-        <x:v>34</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L6" s="4" t="n">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M6" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N6" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N6" s="13" t="n">
-        <x:v>0.53125</x:v>
-      </x:c>
       <x:c r="O6" s="12" t="n">
-        <x:v>0.4375</x:v>
+        <x:v>0.6615384615384614</x:v>
       </x:c>
       <x:c r="P6" s="12" t="n">
-        <x:v>0.03125</x:v>
-      </x:c>
-      <x:c r="Q6" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R6" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S6" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T6" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U6" s="14" t="str">
-        <x:v>完成率77.70%&lt;100%；新签小卡率53.13%&gt;40%</x:v>
-      </x:c>
-      <x:c r="V6" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+        <x:v>0.3076923076923077</x:v>
+      </x:c>
+      <x:c r="Q6" s="12" t="n">
+        <x:v>0.03076923076923077</x:v>
+      </x:c>
+      <x:c r="R6" s="12" t="n">
+        <x:v>0.7558</x:v>
+      </x:c>
+      <x:c r="S6" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="T6" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U6" s="15" t="n">
+        <x:v>2768</x:v>
+      </x:c>
+      <x:c r="V6" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W6" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X6" s="4" t="str">
+        <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
+      </x:c>
+      <x:c r="Y6" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1214,7 +1308,7 @@
         <x:v>1.333182932810201</x:v>
       </x:c>
       <x:c r="F7" s="12" t="n">
-        <x:v>0.00858047053355388</x:v>
+        <x:v>0.858047053355388</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>待核</x:v>
@@ -1226,43 +1320,52 @@
         <x:v>待核</x:v>
       </x:c>
       <x:c r="J7" s="4" t="n">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K7" s="4" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L7" s="4" t="n">
+      <x:c r="M7" s="4" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="M7" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="N7" s="12" t="n">
-        <x:v>0.2647058823529412</x:v>
+      <x:c r="N7" s="4" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O7" s="12" t="n">
-        <x:v>0.6176470588235294</x:v>
+        <x:v>0.2571428571428571</x:v>
       </x:c>
       <x:c r="P7" s="12" t="n">
-        <x:v>0.1176470588235294</x:v>
-      </x:c>
-      <x:c r="Q7" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R7" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S7" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T7" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U7" s="15" t="str">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="Q7" s="12" t="n">
+        <x:v>0.14285714285714285</x:v>
+      </x:c>
+      <x:c r="R7" s="12" t="n">
+        <x:v>0.5146999999999999</x:v>
+      </x:c>
+      <x:c r="S7" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T7" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U7" s="16" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="V7" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W7" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X7" s="4" t="str">
         <x:v>当前已核指标无异常</x:v>
       </x:c>
-      <x:c r="V7" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y7" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1282,7 +1385,7 @@
         <x:v>0.7866563944530046</x:v>
       </x:c>
       <x:c r="F8" s="12" t="n">
-        <x:v>-0.0013928788185312562</x:v>
+        <x:v>-0.13928788185312563</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
         <x:v>待核</x:v>
@@ -1290,47 +1393,56 @@
       <x:c r="H8" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I8" s="11" t="n">
+        <x:v>17570</x:v>
       </x:c>
       <x:c r="J8" s="4" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K8" s="4" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K8" s="4" t="n">
+      <x:c r="L8" s="4" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="L8" s="4" t="n">
+      <x:c r="M8" s="4" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M8" s="4" t="n">
+      <x:c r="N8" s="14" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="N8" s="13" t="n">
+      <x:c r="O8" s="12" t="n">
         <x:v>0.42857142857142855</x:v>
       </x:c>
-      <x:c r="O8" s="12" t="n">
+      <x:c r="P8" s="12" t="n">
         <x:v>0.4761904761904761</x:v>
       </x:c>
-      <x:c r="P8" s="12" t="n">
+      <x:c r="Q8" s="12" t="n">
         <x:v>0.09523809523809523</x:v>
       </x:c>
-      <x:c r="Q8" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R8" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S8" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T8" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U8" s="14" t="str">
+      <x:c r="R8" s="12" t="n">
+        <x:v>0.4941</x:v>
+      </x:c>
+      <x:c r="S8" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="T8" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U8" s="15" t="n">
+        <x:v>3920</x:v>
+      </x:c>
+      <x:c r="V8" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W8" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X8" s="4" t="str">
         <x:v>完成率78.67%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
-      <x:c r="V8" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y8" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1350,7 +1462,7 @@
         <x:v>0.7036012861736335</x:v>
       </x:c>
       <x:c r="F9" s="12" t="n">
-        <x:v>0.00047186064318529864</x:v>
+        <x:v>0.04718606431852987</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
         <x:v>待核</x:v>
@@ -1362,43 +1474,50 @@
         <x:v>待核</x:v>
       </x:c>
       <x:c r="J9" s="4" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="n">
+      <x:c r="L9" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="L9" s="4" t="n">
+      <x:c r="M9" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M9" s="4" t="n">
+      <x:c r="N9" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N9" s="13" t="n">
+      <x:c r="O9" s="12" t="n">
         <x:v>0.5714285714285714</x:v>
       </x:c>
-      <x:c r="O9" s="12" t="n">
+      <x:c r="P9" s="12" t="n">
         <x:v>0.32142857142857145</x:v>
       </x:c>
-      <x:c r="P9" s="12" t="n">
+      <x:c r="Q9" s="12" t="n">
         <x:v>0.10714285714285714</x:v>
       </x:c>
-      <x:c r="Q9" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R9" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S9" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T9" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U9" s="14" t="str">
+      <x:c r="R9" s="12"/>
+      <x:c r="S9" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="T9" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U9" s="15" t="n">
+        <x:v>7400</x:v>
+      </x:c>
+      <x:c r="V9" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W9" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X9" s="4" t="str">
         <x:v>完成率70.36%&lt;100%；新签小卡率57.14%&gt;40%</x:v>
       </x:c>
-      <x:c r="V9" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y9" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1418,7 +1537,7 @@
         <x:v>0.539605614973262</x:v>
       </x:c>
       <x:c r="F10" s="12" t="n">
-        <x:v>-0.0011908334470058656</x:v>
+        <x:v>-0.11908334470058655</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
         <x:v>待核</x:v>
@@ -1426,47 +1545,56 @@
       <x:c r="H10" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I10" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I10" s="11" t="n">
+        <x:v>11529</x:v>
       </x:c>
       <x:c r="J10" s="4" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="n">
+      <x:c r="L10" s="4" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="L10" s="4" t="n">
+      <x:c r="M10" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="M10" s="4" t="n">
+      <x:c r="N10" s="14" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N10" s="13" t="n">
+      <x:c r="O10" s="12" t="n">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="O10" s="12" t="n">
+      <x:c r="P10" s="12" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="P10" s="12" t="n">
+      <x:c r="Q10" s="12" t="n">
         <x:v>0.0625</x:v>
       </x:c>
-      <x:c r="Q10" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R10" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S10" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T10" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U10" s="14" t="str">
+      <x:c r="R10" s="12" t="n">
+        <x:v>0.6154</x:v>
+      </x:c>
+      <x:c r="S10" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="T10" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U10" s="15" t="n">
+        <x:v>5949</x:v>
+      </x:c>
+      <x:c r="V10" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W10" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X10" s="4" t="str">
         <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
       </x:c>
-      <x:c r="V10" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y10" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1486,7 +1614,7 @@
         <x:v>0.766405682460247</x:v>
       </x:c>
       <x:c r="F11" s="12" t="n">
-        <x:v>0.00211174182026915</x:v>
+        <x:v>0.21117418202691499</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
         <x:v>待核</x:v>
@@ -1494,47 +1622,56 @@
       <x:c r="H11" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I11" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I11" s="11" t="n">
+        <x:v>14184</x:v>
       </x:c>
       <x:c r="J11" s="4" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K11" s="4" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="n">
+      <x:c r="L11" s="4" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="L11" s="4" t="n">
+      <x:c r="M11" s="4" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M11" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="13" t="n">
+      <x:c r="N11" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="n">
         <x:v>0.7446808510638298</x:v>
       </x:c>
-      <x:c r="O11" s="12" t="n">
+      <x:c r="P11" s="12" t="n">
         <x:v>0.2553191489361702</x:v>
       </x:c>
-      <x:c r="P11" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q11" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R11" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S11" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T11" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U11" s="14" t="str">
+      <x:c r="Q11" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="12" t="n">
+        <x:v>0.5802</x:v>
+      </x:c>
+      <x:c r="S11" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T11" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U11" s="15" t="n">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="V11" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W11" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X11" s="4" t="str">
         <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
       </x:c>
-      <x:c r="V11" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y11" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1566,43 +1703,52 @@
         <x:v>待核</x:v>
       </x:c>
       <x:c r="J12" s="4" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K12" s="4" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="n">
+      <x:c r="L12" s="4" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L12" s="4" t="n">
+      <x:c r="M12" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M12" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="13" t="n">
+      <x:c r="N12" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="12" t="n">
         <x:v>0.5769230769230769</x:v>
       </x:c>
-      <x:c r="O12" s="12" t="n">
+      <x:c r="P12" s="12" t="n">
         <x:v>0.4230769230769231</x:v>
       </x:c>
-      <x:c r="P12" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q12" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R12" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S12" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T12" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U12" s="14" t="str">
+      <x:c r="Q12" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="12" t="n">
+        <x:v>0.5778</x:v>
+      </x:c>
+      <x:c r="S12" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="T12" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U12" s="15" t="n">
+        <x:v>6280</x:v>
+      </x:c>
+      <x:c r="V12" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W12" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X12" s="4" t="str">
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
-      <x:c r="V12" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y12" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1622,7 +1768,7 @@
         <x:v>0.823913660891792</x:v>
       </x:c>
       <x:c r="F13" s="12" t="n">
-        <x:v>0.0012578219742905652</x:v>
+        <x:v>0.12578219742905652</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>待核</x:v>
@@ -1630,47 +1776,56 @@
       <x:c r="H13" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I13" s="11" t="n">
+        <x:v>7748</x:v>
       </x:c>
       <x:c r="J13" s="4" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="K13" s="4" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K13" s="4" t="n">
+      <x:c r="L13" s="4" t="n">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="L13" s="4" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="M13" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="N13" s="13" t="n">
+      <x:c r="N13" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O13" s="12" t="n">
         <x:v>0.5833333333333334</x:v>
-      </x:c>
-      <x:c r="O13" s="12" t="n">
-        <x:v>0.20833333333333337</x:v>
       </x:c>
       <x:c r="P13" s="12" t="n">
         <x:v>0.20833333333333337</x:v>
       </x:c>
-      <x:c r="Q13" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R13" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S13" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T13" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U13" s="14" t="str">
+      <x:c r="Q13" s="12" t="n">
+        <x:v>0.20833333333333337</x:v>
+      </x:c>
+      <x:c r="R13" s="12" t="n">
+        <x:v>0.6667000000000001</x:v>
+      </x:c>
+      <x:c r="S13" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="T13" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U13" s="15" t="n">
+        <x:v>7964</x:v>
+      </x:c>
+      <x:c r="V13" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W13" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X13" s="4" t="str">
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
-      <x:c r="V13" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y13" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1690,7 +1845,7 @@
         <x:v>0.8485184013497838</x:v>
       </x:c>
       <x:c r="F14" s="12" t="n">
-        <x:v>0.0015935451336359053</x:v>
+        <x:v>0.15935451336359052</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
         <x:v>待核</x:v>
@@ -1702,43 +1857,52 @@
         <x:v>待核</x:v>
       </x:c>
       <x:c r="J14" s="4" t="n">
-        <x:v>22</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K14" s="4" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L14" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="M14" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N14" s="12" t="n">
-        <x:v>0.045454545454545456</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="n">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="O14" s="12" t="n">
-        <x:v>0.4090909090909091</x:v>
+        <x:v>0.037037037037037035</x:v>
       </x:c>
       <x:c r="P14" s="12" t="n">
-        <x:v>0.5454545454545454</x:v>
-      </x:c>
-      <x:c r="Q14" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R14" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S14" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T14" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U14" s="14" t="str">
+        <x:v>0.3703703703703704</x:v>
+      </x:c>
+      <x:c r="Q14" s="12" t="n">
+        <x:v>0.5925925925925926</x:v>
+      </x:c>
+      <x:c r="R14" s="12" t="n">
+        <x:v>0.675</x:v>
+      </x:c>
+      <x:c r="S14" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="T14" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U14" s="15" t="n">
+        <x:v>4089</x:v>
+      </x:c>
+      <x:c r="V14" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W14" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X14" s="4" t="str">
         <x:v>完成率84.85%&lt;100%</x:v>
       </x:c>
-      <x:c r="V14" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y14" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1758,7 +1922,7 @@
         <x:v>0.49009291637526226</x:v>
       </x:c>
       <x:c r="F15" s="12" t="n">
-        <x:v>-0.004086722065063649</x:v>
+        <x:v>-0.4086722065063649</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
         <x:v>待核</x:v>
@@ -1770,43 +1934,52 @@
         <x:v>待核</x:v>
       </x:c>
       <x:c r="J15" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K15" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L15" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="M15" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N15" s="14" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N15" s="13" t="n">
-        <x:v>0.6521739130434783</x:v>
-      </x:c>
       <x:c r="O15" s="12" t="n">
-        <x:v>0.21739130434782608</x:v>
+        <x:v>0.6666666666666665</x:v>
       </x:c>
       <x:c r="P15" s="12" t="n">
-        <x:v>0.13043478260869565</x:v>
-      </x:c>
-      <x:c r="Q15" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R15" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S15" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T15" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U15" s="14" t="str">
-        <x:v>完成率49.01%&lt;100%；新签小卡率65.22%&gt;40%</x:v>
-      </x:c>
-      <x:c r="V15" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+        <x:v>0.2222222222222222</x:v>
+      </x:c>
+      <x:c r="Q15" s="12" t="n">
+        <x:v>0.1111111111111111</x:v>
+      </x:c>
+      <x:c r="R15" s="12" t="n">
+        <x:v>0.6429</x:v>
+      </x:c>
+      <x:c r="S15" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="T15" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U15" s="15" t="n">
+        <x:v>3399</x:v>
+      </x:c>
+      <x:c r="V15" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W15" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X15" s="4" t="str">
+        <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
+      </x:c>
+      <x:c r="Y15" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1826,7 +1999,7 @@
         <x:v>0.5644684584834211</x:v>
       </x:c>
       <x:c r="F16" s="12" t="n">
-        <x:v>-0.0029841539341946594</x:v>
+        <x:v>-0.29841539341946594</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
         <x:v>待核</x:v>
@@ -1837,44 +2010,53 @@
       <x:c r="I16" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="J16" s="4" t="n">
+      <x:c r="J16" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="K16" s="4" t="n">
+      <x:c r="L16" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L16" s="4" t="n">
+      <x:c r="M16" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M16" s="4" t="n">
+      <x:c r="N16" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N16" s="12" t="n">
+      <x:c r="O16" s="12" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="O16" s="12" t="n">
+      <x:c r="P16" s="12" t="n">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="P16" s="12" t="n">
+      <x:c r="Q16" s="12" t="n">
         <x:v>0.0625</x:v>
       </x:c>
-      <x:c r="Q16" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R16" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S16" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T16" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U16" s="14" t="str">
+      <x:c r="R16" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="S16" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="T16" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U16" s="15" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="V16" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W16" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X16" s="4" t="str">
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
-      <x:c r="V16" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y16" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1894,7 +2076,7 @@
         <x:v>0.6600747508305648</x:v>
       </x:c>
       <x:c r="F17" s="12" t="n">
-        <x:v>0.0011515488847001153</x:v>
+        <x:v>0.11515488847001155</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
         <x:v>待核</x:v>
@@ -1905,44 +2087,53 @@
       <x:c r="I17" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="J17" s="4" t="n">
+      <x:c r="J17" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="K17" s="4" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="K17" s="4" t="n">
+      <x:c r="L17" s="4" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="L17" s="4" t="n">
+      <x:c r="M17" s="4" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="M17" s="4" t="n">
+      <x:c r="N17" s="14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N17" s="13" t="n">
+      <x:c r="O17" s="12" t="n">
         <x:v>0.6071428571428571</x:v>
       </x:c>
-      <x:c r="O17" s="12" t="n">
+      <x:c r="P17" s="12" t="n">
         <x:v>0.35714285714285715</x:v>
       </x:c>
-      <x:c r="P17" s="12" t="n">
+      <x:c r="Q17" s="12" t="n">
         <x:v>0.03571428571428571</x:v>
       </x:c>
-      <x:c r="Q17" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R17" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S17" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T17" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U17" s="14" t="str">
+      <x:c r="R17" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="S17" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="T17" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U17" s="15" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="V17" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W17" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X17" s="4" t="str">
         <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
       </x:c>
-      <x:c r="V17" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y17" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1962,7 +2153,7 @@
         <x:v>0.6187668125956011</x:v>
       </x:c>
       <x:c r="F18" s="12" t="n">
-        <x:v>-0.0018782625552124727</x:v>
+        <x:v>-0.18782625552124727</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
         <x:v>待核</x:v>
@@ -1973,44 +2164,53 @@
       <x:c r="I18" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="J18" s="4" t="n">
+      <x:c r="J18" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="K18" s="4" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K18" s="4" t="n">
+      <x:c r="L18" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L18" s="4" t="n">
+      <x:c r="M18" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M18" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="13" t="n">
+      <x:c r="N18" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="12" t="n">
         <x:v>0.42857142857142855</x:v>
       </x:c>
-      <x:c r="O18" s="12" t="n">
+      <x:c r="P18" s="12" t="n">
         <x:v>0.5714285714285714</x:v>
       </x:c>
-      <x:c r="P18" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q18" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R18" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S18" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T18" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U18" s="14" t="str">
+      <x:c r="Q18" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="S18" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="T18" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U18" s="15" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="V18" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W18" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X18" s="4" t="str">
         <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
-      <x:c r="V18" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y18" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2041,44 +2241,53 @@
       <x:c r="I19" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="J19" s="4" t="n">
+      <x:c r="J19" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="K19" s="4" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K19" s="4" t="n">
+      <x:c r="L19" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L19" s="4" t="n">
+      <x:c r="M19" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="M19" s="4" t="n">
+      <x:c r="N19" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="N19" s="12" t="n">
+      <x:c r="O19" s="12" t="n">
         <x:v>0.16666666666666663</x:v>
       </x:c>
-      <x:c r="O19" s="12" t="n">
+      <x:c r="P19" s="12" t="n">
         <x:v>0.33333333333333326</x:v>
       </x:c>
-      <x:c r="P19" s="12" t="n">
+      <x:c r="Q19" s="12" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="Q19" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R19" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S19" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T19" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U19" s="14" t="str">
+      <x:c r="R19" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="S19" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="T19" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U19" s="15" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="V19" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W19" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X19" s="4" t="str">
         <x:v>完成率52.35%&lt;100%</x:v>
       </x:c>
-      <x:c r="V19" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y19" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2098,7 +2307,7 @@
         <x:v>0.4062967157417894</x:v>
       </x:c>
       <x:c r="F20" s="12" t="n">
-        <x:v>-0.0014468947431159854</x:v>
+        <x:v>-0.14468947431159854</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>待核</x:v>
@@ -2109,50 +2318,59 @@
       <x:c r="I20" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="J20" s="4" t="n">
+      <x:c r="J20" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="K20" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K20" s="4" t="n">
+      <x:c r="L20" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L20" s="4" t="n">
+      <x:c r="M20" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M20" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="12" t="n">
+      <x:c r="N20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="12" t="n">
         <x:v>0.3076923076923077</x:v>
       </x:c>
-      <x:c r="O20" s="12" t="n">
+      <x:c r="P20" s="12" t="n">
         <x:v>0.6923076923076923</x:v>
       </x:c>
-      <x:c r="P20" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="Q20" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R20" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S20" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T20" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U20" s="14" t="str">
+      <x:c r="Q20" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R20" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="S20" s="4" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="T20" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U20" s="15" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="V20" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W20" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="X20" s="4" t="str">
         <x:v>完成率40.63%&lt;100%</x:v>
       </x:c>
-      <x:c r="V20" s="4" t="str">
-        <x:v>本周门店营收截图 + 小程序办卡截图；新客/老客/续费率待飞书或门店汇总核对</x:v>
+      <x:c r="Y20" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97540eacea7a40db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R213cca3864c04e68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4466,7 +4684,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccf978e9c48b4ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46c05560a1584190"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rf8ca5c858eb94106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R63fcad1c82574fca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R82f29ea3d02e441c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R276474ebc1324d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R273f1cb1cabe4190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R591b948ae5a94e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R11441e77fc9a4efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Rdbfbcf3948c54976"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -93,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,10 +133,7 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -147,9 +144,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable1" displayName="WeeklyTable1" ref="A1:S5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:S5"/>
-  <x:tableColumns count="19">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable1" displayName="WeeklyTable1" ref="A1:W5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:W5"/>
+  <x:tableColumns count="23">
     <x:tableColumn id="1" name="层级"/>
     <x:tableColumn id="2" name="名称"/>
     <x:tableColumn id="3" name="总营收"/>
@@ -158,26 +155,30 @@
     <x:tableColumn id="6" name="总接待人数"/>
     <x:tableColumn id="7" name="新客数"/>
     <x:tableColumn id="8" name="老客数"/>
-    <x:tableColumn id="9" name="总办卡数"/>
-    <x:tableColumn id="10" name="新签卡数"/>
-    <x:tableColumn id="11" name="新签小卡数"/>
-    <x:tableColumn id="12" name="新签中卡数"/>
-    <x:tableColumn id="13" name="新签大卡数"/>
-    <x:tableColumn id="14" name="新签小卡率"/>
-    <x:tableColumn id="15" name="新签中卡率"/>
-    <x:tableColumn id="16" name="新签大卡率"/>
-    <x:tableColumn id="17" name="续费率"/>
-    <x:tableColumn id="18" name="续卡金额"/>
-    <x:tableColumn id="19" name="总引流金额"/>
+    <x:tableColumn id="9" name="新签营收"/>
+    <x:tableColumn id="10" name="总办卡数"/>
+    <x:tableColumn id="11" name="新签卡数"/>
+    <x:tableColumn id="12" name="新签小卡数"/>
+    <x:tableColumn id="13" name="新签中卡数"/>
+    <x:tableColumn id="14" name="新签大卡数"/>
+    <x:tableColumn id="15" name="新签办卡率"/>
+    <x:tableColumn id="16" name="新签小卡率"/>
+    <x:tableColumn id="17" name="新签中卡率"/>
+    <x:tableColumn id="18" name="新签大卡率"/>
+    <x:tableColumn id="19" name="大卡率"/>
+    <x:tableColumn id="20" name="续费率"/>
+    <x:tableColumn id="21" name="续卡金额"/>
+    <x:tableColumn id="22" name="总引流金额"/>
+    <x:tableColumn id="23" name="扫楼金额"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable2" displayName="WeeklyTable2" ref="A1:Y20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:Y20"/>
-  <x:tableColumns count="25">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable2" displayName="WeeklyTable2" ref="A1:Z20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:Z20"/>
+  <x:tableColumns count="26">
     <x:tableColumn id="1" name="区域"/>
     <x:tableColumn id="2" name="门店"/>
     <x:tableColumn id="3" name="总营收"/>
@@ -188,21 +189,22 @@
     <x:tableColumn id="8" name="老客数"/>
     <x:tableColumn id="9" name="新签营收"/>
     <x:tableColumn id="10" name="总办卡数"/>
-    <x:tableColumn id="11" name="新签卡数"/>
-    <x:tableColumn id="12" name="新签小卡数"/>
-    <x:tableColumn id="13" name="新签中卡数"/>
-    <x:tableColumn id="14" name="新签大卡数"/>
-    <x:tableColumn id="15" name="新签小卡率"/>
-    <x:tableColumn id="16" name="新签中卡率"/>
-    <x:tableColumn id="17" name="新签大卡率"/>
-    <x:tableColumn id="18" name="新签办卡率"/>
-    <x:tableColumn id="19" name="续卡数"/>
-    <x:tableColumn id="20" name="续费率"/>
-    <x:tableColumn id="21" name="总续卡金额"/>
-    <x:tableColumn id="22" name="总引流金额"/>
-    <x:tableColumn id="23" name="扫楼金额"/>
-    <x:tableColumn id="24" name="异常指标"/>
-    <x:tableColumn id="25" name="来源"/>
+    <x:tableColumn id="11" name="办卡率"/>
+    <x:tableColumn id="12" name="新签卡数"/>
+    <x:tableColumn id="13" name="新签小卡数"/>
+    <x:tableColumn id="14" name="新签中卡数"/>
+    <x:tableColumn id="15" name="新签大卡数"/>
+    <x:tableColumn id="16" name="新签小卡率"/>
+    <x:tableColumn id="17" name="新签中卡率"/>
+    <x:tableColumn id="18" name="新签大卡率"/>
+    <x:tableColumn id="19" name="新签办卡率"/>
+    <x:tableColumn id="20" name="续卡数"/>
+    <x:tableColumn id="21" name="续费率"/>
+    <x:tableColumn id="22" name="总续卡金额"/>
+    <x:tableColumn id="23" name="总引流金额"/>
+    <x:tableColumn id="24" name="扫楼金额"/>
+    <x:tableColumn id="25" name="异常指标"/>
+    <x:tableColumn id="26" name="来源"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -465,7 +467,7 @@
         <x:v>续费率</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>用户截图中的续费率原值；门店级本周原值未在可核截图中逐店确认，统一标记待核，不自行反算。</x:v>
+        <x:v>门店续费率使用最新小程序截图原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -473,22 +475,30 @@
         <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/识别到的新签卡数；本周门店卡型截图OCR合计617张，品牌截图为630张新签卡，差额13张待人工核对。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B8" s="4" t="str">
+      <x:c r="B9" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -509,17 +519,21 @@
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="14" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="14" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -548,37 +562,49 @@
         <x:v>老客数</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
+        <x:v>新签营收</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
         <x:v>总办卡数</x:v>
       </x:c>
-      <x:c r="J1" s="8" t="str">
+      <x:c r="K1" s="8" t="str">
         <x:v>新签卡数</x:v>
       </x:c>
-      <x:c r="K1" s="8" t="str">
+      <x:c r="L1" s="8" t="str">
         <x:v>新签小卡数</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>新签中卡数</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>新签大卡数</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="O1" s="8" t="str">
+        <x:v>新签办卡率</x:v>
+      </x:c>
+      <x:c r="P1" s="8" t="str">
         <x:v>新签小卡率</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>新签中卡率</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="R1" s="8" t="str">
         <x:v>新签大卡率</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="S1" s="8" t="str">
+        <x:v>大卡率</x:v>
+      </x:c>
+      <x:c r="T1" s="8" t="str">
         <x:v>续费率</x:v>
       </x:c>
-      <x:c r="R1" s="8" t="str">
+      <x:c r="U1" s="8" t="str">
         <x:v>续卡金额</x:v>
       </x:c>
-      <x:c r="S1" s="8" t="str">
+      <x:c r="V1" s="8" t="str">
         <x:v>总引流金额</x:v>
+      </x:c>
+      <x:c r="W1" s="8" t="str">
+        <x:v>扫楼金额</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -589,16 +615,16 @@
         <x:v>品牌总览</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>389746.07</x:v>
+        <x:v>389260.07</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>529609</x:v>
       </x:c>
       <x:c r="E2" s="12" t="n">
-        <x:v>0.7359</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="n">
-        <x:v>9044</x:v>
+        <x:v>0.7349951945680683</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="str">
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:v>待核</x:v>
@@ -606,38 +632,50 @@
       <x:c r="H2" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I2" s="4" t="n">
-        <x:v>804</x:v>
+      <x:c r="I2" s="11" t="n">
+        <x:v>247545.22</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
-        <x:v>630</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="K2" s="4" t="n">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="n">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="L2" s="4" t="n">
+      <x:c r="M2" s="4" t="n">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="M2" s="4" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="N2" s="12" t="n">
-        <x:v>0.5206349206349207</x:v>
+      <x:c r="N2" s="4" t="n">
+        <x:v>64</x:v>
       </x:c>
       <x:c r="O2" s="12" t="n">
-        <x:v>0.3761904761904762</x:v>
+        <x:v>0.5465</x:v>
       </x:c>
       <x:c r="P2" s="12" t="n">
-        <x:v>0.10317460317460317</x:v>
+        <x:v>0.5214626391096979</x:v>
       </x:c>
       <x:c r="Q2" s="12" t="n">
+        <x:v>0.3767885532591415</x:v>
+      </x:c>
+      <x:c r="R2" s="12" t="n">
+        <x:v>0.10174880763116058</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="n">
+        <x:v>0.5840597758405978</x:v>
+      </x:c>
+      <x:c r="T2" s="12" t="n">
         <x:v>0.081</x:v>
       </x:c>
-      <x:c r="R2" s="11" t="n">
+      <x:c r="U2" s="11" t="n">
         <x:v>92111.15</x:v>
       </x:c>
-      <x:c r="S2" s="11" t="n">
-        <x:v>173051.7</x:v>
+      <x:c r="V2" s="11" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="W2" s="11" t="n">
+        <x:v>68444.8</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -665,31 +703,47 @@
       <x:c r="H3" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I3" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I3" s="11" t="n">
+        <x:v>69224.62000000001</x:v>
       </x:c>
       <x:c r="J3" s="4" t="n">
-        <x:v>202</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K3" s="4" t="n">
-        <x:v>129</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="L3" s="4" t="n">
-        <x:v>60</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="M3" s="4" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N3" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="N3" s="12" t="n">
-        <x:v>0.6386138613861386</x:v>
-      </x:c>
       <x:c r="O3" s="12"/>
-      <x:c r="P3" s="12"/>
-      <x:c r="Q3" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R3" s="11"/>
-      <x:c r="S3" s="11"/>
+      <x:c r="P3" s="12" t="n">
+        <x:v>0.5970149253731343</x:v>
+      </x:c>
+      <x:c r="Q3" s="12" t="n">
+        <x:v>0.3383084577114428</x:v>
+      </x:c>
+      <x:c r="R3" s="12" t="n">
+        <x:v>0.06467661691542288</x:v>
+      </x:c>
+      <x:c r="S3" s="12" t="n">
+        <x:v>0.5283018867924528</x:v>
+      </x:c>
+      <x:c r="T3" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U3" s="11" t="n">
+        <x:v>27846.15</x:v>
+      </x:c>
+      <x:c r="V3" s="11"/>
+      <x:c r="W3" s="11" t="n">
+        <x:v>15909.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="4" t="str">
@@ -716,31 +770,47 @@
       <x:c r="H4" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I4" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I4" s="11" t="n">
+        <x:v>93064.6</x:v>
       </x:c>
       <x:c r="J4" s="4" t="n">
-        <x:v>213</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K4" s="4" t="n">
-        <x:v>97</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="L4" s="4" t="n">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="M4" s="4" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="N4" s="12" t="n">
-        <x:v>0.4553990610328638</x:v>
-      </x:c>
       <x:c r="O4" s="12"/>
-      <x:c r="P4" s="12"/>
-      <x:c r="Q4" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R4" s="11"/>
-      <x:c r="S4" s="11"/>
+      <x:c r="P4" s="12" t="n">
+        <x:v>0.4454545454545455</x:v>
+      </x:c>
+      <x:c r="Q4" s="12" t="n">
+        <x:v>0.42727272727272725</x:v>
+      </x:c>
+      <x:c r="R4" s="12" t="n">
+        <x:v>0.12727272727272726</x:v>
+      </x:c>
+      <x:c r="S4" s="12" t="n">
+        <x:v>0.6644067796610169</x:v>
+      </x:c>
+      <x:c r="T4" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U4" s="11" t="n">
+        <x:v>43588</x:v>
+      </x:c>
+      <x:c r="V4" s="11"/>
+      <x:c r="W4" s="11" t="n">
+        <x:v>30113.4</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
@@ -767,36 +837,52 @@
       <x:c r="H5" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I5" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I5" s="11" t="n">
+        <x:v>85256</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
-        <x:v>209</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="K5" s="4" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="L5" s="4" t="n">
+      <x:c r="M5" s="4" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="M5" s="4" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="N5" s="12" t="n">
-        <x:v>0.5263157894736842</x:v>
+      <x:c r="N5" s="4" t="n">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="O5" s="12"/>
-      <x:c r="P5" s="12"/>
-      <x:c r="Q5" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="R5" s="11"/>
-      <x:c r="S5" s="11"/>
+      <x:c r="P5" s="12" t="n">
+        <x:v>0.5288461538461539</x:v>
+      </x:c>
+      <x:c r="Q5" s="12" t="n">
+        <x:v>0.3605769230769231</x:v>
+      </x:c>
+      <x:c r="R5" s="12" t="n">
+        <x:v>0.11057692307692307</x:v>
+      </x:c>
+      <x:c r="S5" s="12" t="n">
+        <x:v>0.5473251028806584</x:v>
+      </x:c>
+      <x:c r="T5" s="12" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="U5" s="11" t="n">
+        <x:v>20677</x:v>
+      </x:c>
+      <x:c r="V5" s="11"/>
+      <x:c r="W5" s="11" t="n">
+        <x:v>22422</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f02075e58054f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3dd70d5c3d1448e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -861,48 +947,51 @@
         <x:v>总办卡数</x:v>
       </x:c>
       <x:c r="K1" s="8" t="str">
+        <x:v>办卡率</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
         <x:v>新签卡数</x:v>
       </x:c>
-      <x:c r="L1" s="8" t="str">
+      <x:c r="M1" s="8" t="str">
         <x:v>新签小卡数</x:v>
       </x:c>
-      <x:c r="M1" s="8" t="str">
+      <x:c r="N1" s="8" t="str">
         <x:v>新签中卡数</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="O1" s="8" t="str">
         <x:v>新签大卡数</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="P1" s="8" t="str">
         <x:v>新签小卡率</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>新签中卡率</x:v>
       </x:c>
-      <x:c r="Q1" s="8" t="str">
+      <x:c r="R1" s="8" t="str">
         <x:v>新签大卡率</x:v>
       </x:c>
-      <x:c r="R1" s="8" t="str">
+      <x:c r="S1" s="8" t="str">
         <x:v>新签办卡率</x:v>
       </x:c>
-      <x:c r="S1" s="8" t="str">
+      <x:c r="T1" s="8" t="str">
         <x:v>续卡数</x:v>
       </x:c>
-      <x:c r="T1" s="8" t="str">
+      <x:c r="U1" s="8" t="str">
         <x:v>续费率</x:v>
       </x:c>
-      <x:c r="U1" s="8" t="str">
+      <x:c r="V1" s="8" t="str">
         <x:v>总续卡金额</x:v>
       </x:c>
-      <x:c r="V1" s="8" t="str">
+      <x:c r="W1" s="8" t="str">
         <x:v>总引流金额</x:v>
       </x:c>
-      <x:c r="W1" s="8" t="str">
+      <x:c r="X1" s="8" t="str">
         <x:v>扫楼金额</x:v>
       </x:c>
-      <x:c r="X1" s="8" t="str">
+      <x:c r="Y1" s="8" t="str">
         <x:v>异常指标</x:v>
       </x:c>
-      <x:c r="Y1" s="8" t="str">
+      <x:c r="Z1" s="8" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
@@ -937,50 +1026,53 @@
       <x:c r="J2" s="4" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K2" s="4" t="n">
+      <x:c r="K2" s="12" t="n">
+        <x:v>0.5918</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="L2" s="4" t="n">
+      <x:c r="M2" s="4" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M2" s="4" t="n">
+      <x:c r="N2" s="4" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="N2" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O2" s="12" t="n">
+      <x:c r="O2" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P2" s="13" t="n">
         <x:v>0.5476190476190477</x:v>
       </x:c>
-      <x:c r="P2" s="12" t="n">
+      <x:c r="Q2" s="12" t="n">
         <x:v>0.4523809523809524</x:v>
       </x:c>
-      <x:c r="Q2" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="R2" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="n">
         <x:v>0.5122</x:v>
       </x:c>
-      <x:c r="S2" s="4" t="n">
+      <x:c r="T2" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="T2" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U2" s="15" t="n">
+      <x:c r="U2" s="12" t="n">
+        <x:v>0.07339999999999999</x:v>
+      </x:c>
+      <x:c r="V2" s="11" t="n">
         <x:v>17800</x:v>
       </x:c>
-      <x:c r="V2" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W2" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X2" s="4" t="str">
+      <x:c r="X2" s="11" t="n">
+        <x:v>8531.2</x:v>
+      </x:c>
+      <x:c r="Y2" s="14" t="str">
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y2" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z2" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1014,50 +1106,53 @@
       <x:c r="J3" s="4" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K3" s="4" t="n">
+      <x:c r="K3" s="12" t="n">
+        <x:v>0.5417000000000001</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="L3" s="4" t="n">
+      <x:c r="M3" s="4" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="M3" s="4" t="n">
+      <x:c r="N3" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="N3" s="14" t="n">
+      <x:c r="O3" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="O3" s="12" t="n">
+      <x:c r="P3" s="13" t="n">
         <x:v>0.5641025641025641</x:v>
       </x:c>
-      <x:c r="P3" s="12" t="n">
+      <x:c r="Q3" s="12" t="n">
         <x:v>0.28205128205128205</x:v>
       </x:c>
-      <x:c r="Q3" s="12" t="n">
+      <x:c r="R3" s="12" t="n">
         <x:v>0.15384615384615385</x:v>
       </x:c>
-      <x:c r="R3" s="12" t="n">
+      <x:c r="S3" s="12" t="n">
         <x:v>0.41490000000000005</x:v>
       </x:c>
-      <x:c r="S3" s="4" t="n">
+      <x:c r="T3" s="4" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="T3" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U3" s="15" t="n">
+      <x:c r="U3" s="12" t="n">
+        <x:v>0.12560000000000002</x:v>
+      </x:c>
+      <x:c r="V3" s="11" t="n">
         <x:v>12299</x:v>
       </x:c>
-      <x:c r="V3" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W3" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X3" s="4" t="str">
+      <x:c r="X3" s="11" t="n">
+        <x:v>8325</x:v>
+      </x:c>
+      <x:c r="Y3" s="14" t="str">
         <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y3" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z3" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1091,50 +1186,53 @@
       <x:c r="J4" s="4" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K4" s="4" t="n">
+      <x:c r="K4" s="12" t="n">
+        <x:v>0.5804</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L4" s="4" t="n">
+      <x:c r="M4" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="M4" s="4" t="n">
+      <x:c r="N4" s="4" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="N4" s="14" t="n">
+      <x:c r="O4" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O4" s="12" t="n">
+      <x:c r="P4" s="13" t="n">
         <x:v>0.6274509803921569</x:v>
       </x:c>
-      <x:c r="P4" s="12" t="n">
+      <x:c r="Q4" s="12" t="n">
         <x:v>0.33333333333333326</x:v>
       </x:c>
-      <x:c r="Q4" s="12" t="n">
+      <x:c r="R4" s="12" t="n">
         <x:v>0.0392156862745098</x:v>
       </x:c>
-      <x:c r="R4" s="12" t="n">
+      <x:c r="S4" s="12" t="n">
         <x:v>0.5204</x:v>
       </x:c>
-      <x:c r="S4" s="4" t="n">
+      <x:c r="T4" s="4" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="T4" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U4" s="15" t="n">
+      <x:c r="U4" s="12" t="n">
+        <x:v>0.11109999999999999</x:v>
+      </x:c>
+      <x:c r="V4" s="11" t="n">
         <x:v>6900</x:v>
       </x:c>
-      <x:c r="V4" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W4" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X4" s="4" t="str">
+      <x:c r="X4" s="11" t="n">
+        <x:v>9649</x:v>
+      </x:c>
+      <x:c r="Y4" s="14" t="str">
         <x:v>完成率89.02%&lt;100%；新签小卡率62.75%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y4" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z4" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1168,50 +1266,53 @@
       <x:c r="J5" s="4" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="K5" s="4" t="n">
+      <x:c r="K5" s="12" t="n">
+        <x:v>0.61</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="n">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="L5" s="4" t="n">
+      <x:c r="M5" s="4" t="n">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="M5" s="4" t="n">
+      <x:c r="N5" s="4" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="N5" s="14" t="n">
+      <x:c r="O5" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="O5" s="12" t="n">
+      <x:c r="P5" s="13" t="n">
         <x:v>0.6491228070175439</x:v>
       </x:c>
-      <x:c r="P5" s="12" t="n">
+      <x:c r="Q5" s="12" t="n">
         <x:v>0.24561403508771928</x:v>
       </x:c>
-      <x:c r="Q5" s="12" t="n">
+      <x:c r="R5" s="12" t="n">
         <x:v>0.10526315789473684</x:v>
       </x:c>
-      <x:c r="R5" s="12" t="n">
+      <x:c r="S5" s="12" t="n">
         <x:v>0.5938</x:v>
       </x:c>
-      <x:c r="S5" s="4" t="n">
+      <x:c r="T5" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="T5" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U5" s="15" t="n">
+      <x:c r="U5" s="12" t="n">
+        <x:v>0.0455</x:v>
+      </x:c>
+      <x:c r="V5" s="11" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="V5" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W5" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X5" s="4" t="str">
+      <x:c r="X5" s="11" t="n">
+        <x:v>7715</x:v>
+      </x:c>
+      <x:c r="Y5" s="14" t="str">
         <x:v>完成率68.71%&lt;100%；新签小卡率64.91%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y5" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z5" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1245,50 +1346,53 @@
       <x:c r="J6" s="4" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="K6" s="4" t="n">
+      <x:c r="K6" s="12" t="n">
+        <x:v>0.7742</x:v>
+      </x:c>
+      <x:c r="L6" s="4" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="L6" s="4" t="n">
+      <x:c r="M6" s="4" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="M6" s="4" t="n">
+      <x:c r="N6" s="4" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N6" s="14" t="n">
+      <x:c r="O6" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O6" s="12" t="n">
+      <x:c r="P6" s="13" t="n">
         <x:v>0.6615384615384614</x:v>
       </x:c>
-      <x:c r="P6" s="12" t="n">
+      <x:c r="Q6" s="12" t="n">
         <x:v>0.3076923076923077</x:v>
       </x:c>
-      <x:c r="Q6" s="12" t="n">
+      <x:c r="R6" s="12" t="n">
         <x:v>0.03076923076923077</x:v>
       </x:c>
-      <x:c r="R6" s="12" t="n">
+      <x:c r="S6" s="12" t="n">
         <x:v>0.7558</x:v>
       </x:c>
-      <x:c r="S6" s="4" t="n">
+      <x:c r="T6" s="4" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="T6" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U6" s="15" t="n">
+      <x:c r="U6" s="12" t="n">
+        <x:v>0.06480000000000001</x:v>
+      </x:c>
+      <x:c r="V6" s="11" t="n">
         <x:v>2768</x:v>
       </x:c>
-      <x:c r="V6" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W6" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X6" s="4" t="str">
+      <x:c r="X6" s="11" t="n">
+        <x:v>3923</x:v>
+      </x:c>
+      <x:c r="Y6" s="14" t="str">
         <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y6" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z6" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1316,56 +1420,59 @@
       <x:c r="H7" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I7" s="11" t="n">
+        <x:v>22422.6</x:v>
       </x:c>
       <x:c r="J7" s="4" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="K7" s="4" t="n">
+      <x:c r="K7" s="12" t="n">
+        <x:v>0.5478999999999999</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="L7" s="4" t="n">
+      <x:c r="M7" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M7" s="4" t="n">
+      <x:c r="N7" s="4" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="N7" s="4" t="n">
+      <x:c r="O7" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O7" s="12" t="n">
+      <x:c r="P7" s="12" t="n">
         <x:v>0.2571428571428571</x:v>
       </x:c>
-      <x:c r="P7" s="12" t="n">
+      <x:c r="Q7" s="12" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="Q7" s="12" t="n">
+      <x:c r="R7" s="12" t="n">
         <x:v>0.14285714285714285</x:v>
       </x:c>
-      <x:c r="R7" s="12" t="n">
+      <x:c r="S7" s="12" t="n">
         <x:v>0.5146999999999999</x:v>
       </x:c>
-      <x:c r="S7" s="4" t="n">
+      <x:c r="T7" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="T7" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U7" s="16" t="n">
+      <x:c r="U7" s="12" t="n">
+        <x:v>0.051</x:v>
+      </x:c>
+      <x:c r="V7" s="11" t="n">
         <x:v>1800</x:v>
       </x:c>
-      <x:c r="V7" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W7" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X7" s="4" t="str">
+      <x:c r="X7" s="11" t="n">
+        <x:v>1814</x:v>
+      </x:c>
+      <x:c r="Y7" s="15" t="str">
         <x:v>当前已核指标无异常</x:v>
       </x:c>
-      <x:c r="Y7" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z7" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1399,50 +1506,53 @@
       <x:c r="J8" s="4" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K8" s="4" t="n">
+      <x:c r="K8" s="12" t="n">
+        <x:v>0.5426</x:v>
+      </x:c>
+      <x:c r="L8" s="4" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="L8" s="4" t="n">
+      <x:c r="M8" s="4" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="M8" s="4" t="n">
+      <x:c r="N8" s="4" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N8" s="14" t="n">
+      <x:c r="O8" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O8" s="12" t="n">
+      <x:c r="P8" s="13" t="n">
         <x:v>0.42857142857142855</x:v>
       </x:c>
-      <x:c r="P8" s="12" t="n">
+      <x:c r="Q8" s="12" t="n">
         <x:v>0.4761904761904761</x:v>
       </x:c>
-      <x:c r="Q8" s="12" t="n">
+      <x:c r="R8" s="12" t="n">
         <x:v>0.09523809523809523</x:v>
       </x:c>
-      <x:c r="R8" s="12" t="n">
+      <x:c r="S8" s="12" t="n">
         <x:v>0.4941</x:v>
       </x:c>
-      <x:c r="S8" s="4" t="n">
+      <x:c r="T8" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="T8" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U8" s="15" t="n">
+      <x:c r="U8" s="12" t="n">
+        <x:v>0.0783</x:v>
+      </x:c>
+      <x:c r="V8" s="11" t="n">
         <x:v>3920</x:v>
       </x:c>
-      <x:c r="V8" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W8" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X8" s="4" t="str">
+      <x:c r="X8" s="11" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="Y8" s="14" t="str">
         <x:v>完成率78.67%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y8" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z8" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1470,54 +1580,59 @@
       <x:c r="H9" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I9" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I9" s="11" t="n">
+        <x:v>11554</x:v>
       </x:c>
       <x:c r="J9" s="4" t="n">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="K9" s="4" t="n">
+      <x:c r="K9" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="L9" s="4" t="n">
+      <x:c r="M9" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="M9" s="4" t="n">
+      <x:c r="N9" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="N9" s="14" t="n">
+      <x:c r="O9" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O9" s="12" t="n">
+      <x:c r="P9" s="13" t="n">
         <x:v>0.5714285714285714</x:v>
       </x:c>
-      <x:c r="P9" s="12" t="n">
+      <x:c r="Q9" s="12" t="n">
         <x:v>0.32142857142857145</x:v>
       </x:c>
-      <x:c r="Q9" s="12" t="n">
+      <x:c r="R9" s="12" t="n">
         <x:v>0.10714285714285714</x:v>
       </x:c>
-      <x:c r="R9" s="12"/>
-      <x:c r="S9" s="4" t="n">
+      <x:c r="S9" s="12" t="n">
+        <x:v>0.45899999999999996</x:v>
+      </x:c>
+      <x:c r="T9" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="T9" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U9" s="15" t="n">
+      <x:c r="U9" s="12" t="n">
+        <x:v>0.08929999999999999</x:v>
+      </x:c>
+      <x:c r="V9" s="11" t="n">
         <x:v>7400</x:v>
       </x:c>
-      <x:c r="V9" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W9" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X9" s="4" t="str">
+      <x:c r="X9" s="11" t="n">
+        <x:v>2287</x:v>
+      </x:c>
+      <x:c r="Y9" s="14" t="str">
         <x:v>完成率70.36%&lt;100%；新签小卡率57.14%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y9" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z9" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1551,50 +1666,53 @@
       <x:c r="J10" s="4" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="K10" s="4" t="n">
+      <x:c r="K10" s="12" t="n">
+        <x:v>0.6970000000000001</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="L10" s="4" t="n">
+      <x:c r="M10" s="4" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="M10" s="4" t="n">
+      <x:c r="N10" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="N10" s="14" t="n">
+      <x:c r="O10" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O10" s="12" t="n">
+      <x:c r="P10" s="13" t="n">
         <x:v>0.6875</x:v>
       </x:c>
-      <x:c r="P10" s="12" t="n">
+      <x:c r="Q10" s="12" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="Q10" s="12" t="n">
+      <x:c r="R10" s="12" t="n">
         <x:v>0.0625</x:v>
       </x:c>
-      <x:c r="R10" s="12" t="n">
+      <x:c r="S10" s="12" t="n">
         <x:v>0.6154</x:v>
       </x:c>
-      <x:c r="S10" s="4" t="n">
+      <x:c r="T10" s="4" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="T10" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U10" s="15" t="n">
+      <x:c r="U10" s="12" t="n">
+        <x:v>0.0795</x:v>
+      </x:c>
+      <x:c r="V10" s="11" t="n">
         <x:v>5949</x:v>
       </x:c>
-      <x:c r="V10" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W10" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X10" s="4" t="str">
+      <x:c r="X10" s="11" t="n">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="Y10" s="14" t="str">
         <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y10" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z10" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1628,50 +1746,53 @@
       <x:c r="J11" s="4" t="n">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="K11" s="4" t="n">
+      <x:c r="K11" s="12" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="L11" s="4" t="n">
+      <x:c r="M11" s="4" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="M11" s="4" t="n">
+      <x:c r="N11" s="4" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="N11" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="12" t="n">
+      <x:c r="O11" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="13" t="n">
         <x:v>0.7446808510638298</x:v>
       </x:c>
-      <x:c r="P11" s="12" t="n">
+      <x:c r="Q11" s="12" t="n">
         <x:v>0.2553191489361702</x:v>
       </x:c>
-      <x:c r="Q11" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="R11" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="12" t="n">
         <x:v>0.5802</x:v>
       </x:c>
-      <x:c r="S11" s="4" t="n">
+      <x:c r="T11" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="T11" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U11" s="15" t="n">
+      <x:c r="U11" s="12" t="n">
+        <x:v>0.043</x:v>
+      </x:c>
+      <x:c r="V11" s="11" t="n">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="V11" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W11" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X11" s="4" t="str">
+      <x:c r="X11" s="11" t="n">
+        <x:v>3349</x:v>
+      </x:c>
+      <x:c r="Y11" s="14" t="str">
         <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y11" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z11" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1699,56 +1820,59 @@
       <x:c r="H12" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I12" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I12" s="11" t="n">
+        <x:v>9243</x:v>
       </x:c>
       <x:c r="J12" s="4" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K12" s="4" t="n">
+      <x:c r="K12" s="12" t="n">
+        <x:v>0.6724</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="L12" s="4" t="n">
+      <x:c r="M12" s="4" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="M12" s="4" t="n">
+      <x:c r="N12" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="N12" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O12" s="12" t="n">
+      <x:c r="O12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="13" t="n">
         <x:v>0.5769230769230769</x:v>
       </x:c>
-      <x:c r="P12" s="12" t="n">
+      <x:c r="Q12" s="12" t="n">
         <x:v>0.4230769230769231</x:v>
       </x:c>
-      <x:c r="Q12" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="R12" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="12" t="n">
         <x:v>0.5778</x:v>
       </x:c>
-      <x:c r="S12" s="4" t="n">
+      <x:c r="T12" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="T12" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U12" s="15" t="n">
+      <x:c r="U12" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="V12" s="11" t="n">
         <x:v>6280</x:v>
       </x:c>
-      <x:c r="V12" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W12" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X12" s="4" t="str">
+      <x:c r="X12" s="11" t="n">
+        <x:v>3198</x:v>
+      </x:c>
+      <x:c r="Y12" s="14" t="str">
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y12" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z12" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1782,50 +1906,53 @@
       <x:c r="J13" s="4" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="K13" s="4" t="n">
+      <x:c r="K13" s="12" t="n">
+        <x:v>0.7818</x:v>
+      </x:c>
+      <x:c r="L13" s="4" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="L13" s="4" t="n">
+      <x:c r="M13" s="4" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="M13" s="4" t="n">
+      <x:c r="N13" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="N13" s="14" t="n">
+      <x:c r="O13" s="4" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O13" s="12" t="n">
+      <x:c r="P13" s="13" t="n">
         <x:v>0.5833333333333334</x:v>
-      </x:c>
-      <x:c r="P13" s="12" t="n">
-        <x:v>0.20833333333333337</x:v>
       </x:c>
       <x:c r="Q13" s="12" t="n">
         <x:v>0.20833333333333337</x:v>
       </x:c>
       <x:c r="R13" s="12" t="n">
+        <x:v>0.20833333333333337</x:v>
+      </x:c>
+      <x:c r="S13" s="12" t="n">
         <x:v>0.6667000000000001</x:v>
       </x:c>
-      <x:c r="S13" s="4" t="n">
+      <x:c r="T13" s="4" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="T13" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U13" s="15" t="n">
+      <x:c r="U13" s="12" t="n">
+        <x:v>0.1387</x:v>
+      </x:c>
+      <x:c r="V13" s="11" t="n">
         <x:v>7964</x:v>
       </x:c>
-      <x:c r="V13" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W13" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X13" s="4" t="str">
+      <x:c r="X13" s="11" t="n">
+        <x:v>2987</x:v>
+      </x:c>
+      <x:c r="Y13" s="14" t="str">
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y13" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z13" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1853,56 +1980,59 @@
       <x:c r="H14" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I14" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I14" s="11" t="n">
+        <x:v>11008</x:v>
       </x:c>
       <x:c r="J14" s="4" t="n">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="K14" s="4" t="n">
+      <x:c r="K14" s="12" t="n">
+        <x:v>0.7451000000000001</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="L14" s="4" t="n">
+      <x:c r="M14" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M14" s="4" t="n">
+      <x:c r="N14" s="4" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N14" s="4" t="n">
+      <x:c r="O14" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="O14" s="12" t="n">
+      <x:c r="P14" s="12" t="n">
         <x:v>0.037037037037037035</x:v>
       </x:c>
-      <x:c r="P14" s="12" t="n">
+      <x:c r="Q14" s="12" t="n">
         <x:v>0.3703703703703704</x:v>
       </x:c>
-      <x:c r="Q14" s="12" t="n">
+      <x:c r="R14" s="12" t="n">
         <x:v>0.5925925925925926</x:v>
       </x:c>
-      <x:c r="R14" s="12" t="n">
+      <x:c r="S14" s="12" t="n">
         <x:v>0.675</x:v>
       </x:c>
-      <x:c r="S14" s="4" t="n">
+      <x:c r="T14" s="4" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="T14" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U14" s="15" t="n">
+      <x:c r="U14" s="12" t="n">
+        <x:v>0.1375</x:v>
+      </x:c>
+      <x:c r="V14" s="11" t="n">
         <x:v>4089</x:v>
       </x:c>
-      <x:c r="V14" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W14" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X14" s="4" t="str">
+      <x:c r="X14" s="11" t="n">
+        <x:v>3069</x:v>
+      </x:c>
+      <x:c r="Y14" s="14" t="str">
         <x:v>完成率84.85%&lt;100%</x:v>
       </x:c>
-      <x:c r="Y14" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z14" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1930,56 +2060,59 @@
       <x:c r="H15" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I15" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="I15" s="11" t="n">
+        <x:v>9833.02</x:v>
       </x:c>
       <x:c r="J15" s="4" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="K15" s="4" t="n">
+      <x:c r="K15" s="12" t="n">
+        <x:v>0.6939</x:v>
+      </x:c>
+      <x:c r="L15" s="4" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="L15" s="4" t="n">
+      <x:c r="M15" s="4" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="M15" s="4" t="n">
+      <x:c r="N15" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N15" s="14" t="n">
+      <x:c r="O15" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O15" s="12" t="n">
+      <x:c r="P15" s="13" t="n">
         <x:v>0.6666666666666665</x:v>
       </x:c>
-      <x:c r="P15" s="12" t="n">
+      <x:c r="Q15" s="12" t="n">
         <x:v>0.2222222222222222</x:v>
       </x:c>
-      <x:c r="Q15" s="12" t="n">
+      <x:c r="R15" s="12" t="n">
         <x:v>0.1111111111111111</x:v>
       </x:c>
-      <x:c r="R15" s="12" t="n">
+      <x:c r="S15" s="12" t="n">
         <x:v>0.6429</x:v>
       </x:c>
-      <x:c r="S15" s="4" t="n">
+      <x:c r="T15" s="4" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="T15" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U15" s="15" t="n">
+      <x:c r="U15" s="12" t="n">
+        <x:v>0.042699999999999995</x:v>
+      </x:c>
+      <x:c r="V15" s="11" t="n">
         <x:v>3399</x:v>
       </x:c>
-      <x:c r="V15" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
       <x:c r="W15" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X15" s="4" t="str">
+      <x:c r="X15" s="11" t="n">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="Y15" s="14" t="str">
         <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
       </x:c>
-      <x:c r="Y15" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z15" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2007,56 +2140,59 @@
       <x:c r="H16" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I16" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="J16" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="K16" s="4" t="n">
-        <x:v>16</x:v>
+      <x:c r="I16" s="11" t="n">
+        <x:v>8912</x:v>
+      </x:c>
+      <x:c r="J16" s="4" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K16" s="12" t="n">
+        <x:v>0.8065000000000001</x:v>
       </x:c>
       <x:c r="L16" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="M16" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M16" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="N16" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O16" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O16" s="12" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
       <x:c r="P16" s="12" t="n">
-        <x:v>0.6875</x:v>
+        <x:v>0.2222222222222222</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="n">
-        <x:v>0.0625</x:v>
-      </x:c>
-      <x:c r="R16" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S16" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T16" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U16" s="15" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="V16" s="11" t="str">
-        <x:v>待核</x:v>
+        <x:v>0.7222222222222221</x:v>
+      </x:c>
+      <x:c r="R16" s="12" t="n">
+        <x:v>0.05555555555555555</x:v>
+      </x:c>
+      <x:c r="S16" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="T16" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="U16" s="12" t="n">
+        <x:v>0.0787</x:v>
+      </x:c>
+      <x:c r="V16" s="11" t="n">
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="W16" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X16" s="4" t="str">
+      <x:c r="X16" s="11" t="n">
+        <x:v>2782</x:v>
+      </x:c>
+      <x:c r="Y16" s="14" t="str">
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
-      <x:c r="Y16" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z16" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2084,56 +2220,59 @@
       <x:c r="H17" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I17" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="J17" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="K17" s="4" t="n">
-        <x:v>28</x:v>
+      <x:c r="I17" s="11" t="n">
+        <x:v>9034.6</x:v>
+      </x:c>
+      <x:c r="J17" s="4" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="K17" s="12" t="n">
+        <x:v>0.7045</x:v>
       </x:c>
       <x:c r="L17" s="4" t="n">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="M17" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N17" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="O17" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O17" s="12" t="n">
-        <x:v>0.6071428571428571</x:v>
-      </x:c>
       <x:c r="P17" s="12" t="n">
-        <x:v>0.35714285714285715</x:v>
+        <x:v>0.2962962962962963</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="n">
-        <x:v>0.03571428571428571</x:v>
-      </x:c>
-      <x:c r="R17" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S17" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T17" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U17" s="15" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="V17" s="11" t="str">
-        <x:v>待核</x:v>
+        <x:v>0.6666666666666665</x:v>
+      </x:c>
+      <x:c r="R17" s="12" t="n">
+        <x:v>0.037037037037037035</x:v>
+      </x:c>
+      <x:c r="S17" s="12" t="n">
+        <x:v>0.675</x:v>
+      </x:c>
+      <x:c r="T17" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="U17" s="12" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="V17" s="11" t="n">
+        <x:v>1486.15</x:v>
       </x:c>
       <x:c r="W17" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X17" s="4" t="str">
-        <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
-      </x:c>
-      <x:c r="Y17" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="X17" s="11" t="n">
+        <x:v>3279.4</x:v>
+      </x:c>
+      <x:c r="Y17" s="14" t="str">
+        <x:v>完成率66.01%&lt;100%</x:v>
+      </x:c>
+      <x:c r="Z17" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2161,56 +2300,59 @@
       <x:c r="H18" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I18" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="J18" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="K18" s="4" t="n">
-        <x:v>7</x:v>
+      <x:c r="I18" s="11" t="n">
+        <x:v>4837</x:v>
+      </x:c>
+      <x:c r="J18" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K18" s="12" t="n">
+        <x:v>0.2813</x:v>
       </x:c>
       <x:c r="L18" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M18" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="N18" s="14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O18" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+      <x:c r="N18" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O18" s="4" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="P18" s="12" t="n">
-        <x:v>0.5714285714285714</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R18" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S18" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T18" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U18" s="15" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="V18" s="11" t="str">
-        <x:v>待核</x:v>
+        <x:v>0.6666666666666665</x:v>
+      </x:c>
+      <x:c r="R18" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="12" t="n">
+        <x:v>0.2069</x:v>
+      </x:c>
+      <x:c r="T18" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="U18" s="12" t="n">
+        <x:v>0.0526</x:v>
+      </x:c>
+      <x:c r="V18" s="11" t="n">
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="W18" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X18" s="4" t="str">
-        <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
-      </x:c>
-      <x:c r="Y18" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="X18" s="11" t="n">
+        <x:v>2243.2</x:v>
+      </x:c>
+      <x:c r="Y18" s="14" t="str">
+        <x:v>完成率61.88%&lt;100%</x:v>
+      </x:c>
+      <x:c r="Z18" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2238,56 +2380,59 @@
       <x:c r="H19" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I19" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="J19" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="K19" s="4" t="n">
-        <x:v>18</x:v>
+      <x:c r="I19" s="11" t="n">
+        <x:v>5862</x:v>
+      </x:c>
+      <x:c r="J19" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K19" s="12" t="n">
+        <x:v>0.5405</x:v>
       </x:c>
       <x:c r="L19" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M19" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M19" s="4" t="n">
+      <x:c r="N19" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="N19" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="O19" s="12" t="n">
-        <x:v>0.16666666666666663</x:v>
+      <x:c r="O19" s="4" t="n">
+        <x:v>8</x:v>
       </x:c>
       <x:c r="P19" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
+        <x:v>0.17647058823529413</x:v>
       </x:c>
       <x:c r="Q19" s="12" t="n">
+        <x:v>0.35294117647058826</x:v>
+      </x:c>
+      <x:c r="R19" s="12" t="n">
+        <x:v>0.4705882352941176</x:v>
+      </x:c>
+      <x:c r="S19" s="12" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="R19" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S19" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T19" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U19" s="15" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="V19" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="T19" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="U19" s="12" t="n">
+        <x:v>0.0732</x:v>
+      </x:c>
+      <x:c r="V19" s="11" t="n">
+        <x:v>957</x:v>
       </x:c>
       <x:c r="W19" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X19" s="4" t="str">
+      <x:c r="X19" s="11" t="n">
+        <x:v>1771</x:v>
+      </x:c>
+      <x:c r="Y19" s="14" t="str">
         <x:v>完成率52.35%&lt;100%</x:v>
       </x:c>
-      <x:c r="Y19" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z19" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2315,62 +2460,65 @@
       <x:c r="H20" s="4" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="I20" s="11" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="J20" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="K20" s="4" t="n">
+      <x:c r="I20" s="11" t="n">
+        <x:v>5599</x:v>
+      </x:c>
+      <x:c r="J20" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="K20" s="12" t="n">
+        <x:v>0.4483</x:v>
+      </x:c>
       <x:c r="L20" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M20" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M20" s="4" t="n">
+      <x:c r="N20" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="N20" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O20" s="12" t="n">
+      <x:c r="O20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="12" t="n">
         <x:v>0.3076923076923077</x:v>
       </x:c>
-      <x:c r="P20" s="12" t="n">
+      <x:c r="Q20" s="12" t="n">
         <x:v>0.6923076923076923</x:v>
       </x:c>
-      <x:c r="Q20" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="R20" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="S20" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="T20" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="U20" s="15" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="V20" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="R20" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S20" s="12" t="n">
+        <x:v>0.4483</x:v>
+      </x:c>
+      <x:c r="T20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" s="11" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="W20" s="11" t="str">
         <x:v>待核</x:v>
       </x:c>
-      <x:c r="X20" s="4" t="str">
+      <x:c r="X20" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y20" s="14" t="str">
         <x:v>完成率40.63%&lt;100%</x:v>
       </x:c>
-      <x:c r="Y20" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值优先；未逐店读取的字段待从原截图补齐，不使用员工OCR替代门店总数</x:v>
+      <x:c r="Z20" s="4" t="str">
+        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R213cca3864c04e68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95803d64d94a4c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4684,7 +4832,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46c05560a1584190"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2577c795b24511"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R273f1cb1cabe4190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R591b948ae5a94e8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R11441e77fc9a4efb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Rdbfbcf3948c54976"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Re74f4611871d4228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R421ae5ea02c541c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R8ab97e03a33640df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R0c06ab6b7be840a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="5" r:id="Re92976bbd5a543ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -181,12 +182,12 @@
   <x:tableColumns count="26">
     <x:tableColumn id="1" name="区域"/>
     <x:tableColumn id="2" name="门店"/>
-    <x:tableColumn id="3" name="总营收"/>
-    <x:tableColumn id="4" name="目标"/>
-    <x:tableColumn id="5" name="完成率"/>
-    <x:tableColumn id="6" name="本周较上周"/>
-    <x:tableColumn id="7" name="新客数"/>
-    <x:tableColumn id="8" name="老客数"/>
+    <x:tableColumn id="3" name="新客数"/>
+    <x:tableColumn id="4" name="老客数"/>
+    <x:tableColumn id="5" name="总营收"/>
+    <x:tableColumn id="6" name="目标"/>
+    <x:tableColumn id="7" name="完成率"/>
+    <x:tableColumn id="8" name="本周较上周"/>
     <x:tableColumn id="9" name="新签营收"/>
     <x:tableColumn id="10" name="总办卡数"/>
     <x:tableColumn id="11" name="办卡率"/>
@@ -226,6 +227,31 @@
     <x:tableColumn id="10" name="新签中卡率"/>
     <x:tableColumn id="11" name="新签大卡率"/>
     <x:tableColumn id="12" name="续费率"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable4" displayName="WeeklyTable4" ref="A1:P22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:P22"/>
+  <x:tableColumns count="16">
+    <x:tableColumn id="1" name="本周排名"/>
+    <x:tableColumn id="2" name="上周排名"/>
+    <x:tableColumn id="3" name="排名变化"/>
+    <x:tableColumn id="4" name="区域"/>
+    <x:tableColumn id="5" name="门店"/>
+    <x:tableColumn id="6" name="员工"/>
+    <x:tableColumn id="7" name="本周总金额"/>
+    <x:tableColumn id="8" name="完成率"/>
+    <x:tableColumn id="9" name="上周总金额"/>
+    <x:tableColumn id="10" name="金额增减"/>
+    <x:tableColumn id="11" name="充值金额"/>
+    <x:tableColumn id="12" name="散单金额"/>
+    <x:tableColumn id="13" name="新签小卡数"/>
+    <x:tableColumn id="14" name="新签中卡数"/>
+    <x:tableColumn id="15" name="新签大卡数"/>
+    <x:tableColumn id="16" name="续费率"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -459,7 +485,7 @@
         <x:v>新客数/老客数</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>本周飞书原值未取得，统一标记待核；不得用累计人数、办卡数或其他字段推算。</x:v>
+        <x:v>新客数取飞书门店数据汇总-周原值；老客数取飞书账单流水，按门店+会员ID在本周内去重。品牌新客1,150人、老客2,149人。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -467,38 +493,46 @@
         <x:v>续费率</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>门店续费率使用最新小程序截图原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
+        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>卡型率</x:v>
+        <x:v>引流/扫楼</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
+        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>总办卡率</x:v>
+        <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="str">
+      <x:c r="B10" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -615,7 +649,7 @@
         <x:v>品牌总览</x:v>
       </x:c>
       <x:c r="C2" s="11" t="n">
-        <x:v>389260.07</x:v>
+        <x:v>389260.07000000007</x:v>
       </x:c>
       <x:c r="D2" s="11" t="n">
         <x:v>529609</x:v>
@@ -623,14 +657,14 @@
       <x:c r="E2" s="12" t="n">
         <x:v>0.7349951945680683</x:v>
       </x:c>
-      <x:c r="F2" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="F2" s="4" t="n">
+        <x:v>9035</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="n">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="n">
+        <x:v>2149</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
         <x:v>247545.22</x:v>
@@ -671,8 +705,8 @@
       <x:c r="U2" s="11" t="n">
         <x:v>92111.15</x:v>
       </x:c>
-      <x:c r="V2" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="V2" s="11" t="n">
+        <x:v>173051.7</x:v>
       </x:c>
       <x:c r="W2" s="11" t="n">
         <x:v>68444.8</x:v>
@@ -694,14 +728,14 @@
       <x:c r="E3" s="12" t="n">
         <x:v>0.657592109345061</x:v>
       </x:c>
-      <x:c r="F3" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="F3" s="4" t="n">
+        <x:v>2943</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="n">
+        <x:v>766</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
         <x:v>69224.62000000001</x:v>
@@ -721,7 +755,9 @@
       <x:c r="N3" s="4" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="O3" s="12"/>
+      <x:c r="O3" s="12" t="n">
+        <x:v>0.6677740863787376</x:v>
+      </x:c>
       <x:c r="P3" s="12" t="n">
         <x:v>0.5970149253731343</x:v>
       </x:c>
@@ -734,13 +770,15 @@
       <x:c r="S3" s="12" t="n">
         <x:v>0.5283018867924528</x:v>
       </x:c>
-      <x:c r="T3" s="12" t="str">
-        <x:v>待核</x:v>
+      <x:c r="T3" s="12" t="n">
+        <x:v>0.08355091383812012</x:v>
       </x:c>
       <x:c r="U3" s="11" t="n">
         <x:v>27846.15</x:v>
       </x:c>
-      <x:c r="V3" s="11"/>
+      <x:c r="V3" s="11" t="n">
+        <x:v>38430.5</x:v>
+      </x:c>
       <x:c r="W3" s="11" t="n">
         <x:v>15909.4</x:v>
       </x:c>
@@ -761,14 +799,14 @@
       <x:c r="E4" s="12" t="n">
         <x:v>0.8308086042428985</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="F4" s="4" t="n">
+        <x:v>3637</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="n">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="n">
+        <x:v>898</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
         <x:v>93064.6</x:v>
@@ -788,7 +826,9 @@
       <x:c r="N4" s="4" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="O4" s="12"/>
+      <x:c r="O4" s="12" t="n">
+        <x:v>0.49327354260089684</x:v>
+      </x:c>
       <x:c r="P4" s="12" t="n">
         <x:v>0.4454545454545455</x:v>
       </x:c>
@@ -801,13 +841,15 @@
       <x:c r="S4" s="12" t="n">
         <x:v>0.6644067796610169</x:v>
       </x:c>
-      <x:c r="T4" s="12" t="str">
-        <x:v>待核</x:v>
+      <x:c r="T4" s="12" t="n">
+        <x:v>0.08351893095768376</x:v>
       </x:c>
       <x:c r="U4" s="11" t="n">
         <x:v>43588</x:v>
       </x:c>
-      <x:c r="V4" s="11"/>
+      <x:c r="V4" s="11" t="n">
+        <x:v>62932.6</x:v>
+      </x:c>
       <x:c r="W4" s="11" t="n">
         <x:v>30113.4</x:v>
       </x:c>
@@ -828,14 +870,14 @@
       <x:c r="E5" s="12" t="n">
         <x:v>0.7043584181355623</x:v>
       </x:c>
-      <x:c r="F5" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>待核</x:v>
+      <x:c r="F5" s="4" t="n">
+        <x:v>2455</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="n">
+        <x:v>485</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
         <x:v>85256</x:v>
@@ -855,7 +897,9 @@
       <x:c r="N5" s="4" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="O5" s="12"/>
+      <x:c r="O5" s="12" t="n">
+        <x:v>0.5161290322580645</x:v>
+      </x:c>
       <x:c r="P5" s="12" t="n">
         <x:v>0.5288461538461539</x:v>
       </x:c>
@@ -868,13 +912,15 @@
       <x:c r="S5" s="12" t="n">
         <x:v>0.5473251028806584</x:v>
       </x:c>
-      <x:c r="T5" s="12" t="str">
-        <x:v>待核</x:v>
+      <x:c r="T5" s="12" t="n">
+        <x:v>0.07216494845360824</x:v>
       </x:c>
       <x:c r="U5" s="11" t="n">
         <x:v>20677</x:v>
       </x:c>
-      <x:c r="V5" s="11"/>
+      <x:c r="V5" s="11" t="n">
+        <x:v>71688.6</x:v>
+      </x:c>
       <x:c r="W5" s="11" t="n">
         <x:v>22422</x:v>
       </x:c>
@@ -882,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3dd70d5c3d1448e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc2aeb6e24ca440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -923,22 +969,22 @@
         <x:v>门店</x:v>
       </x:c>
       <x:c r="C1" s="8" t="str">
+        <x:v>新客数</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>老客数</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
         <x:v>总营收</x:v>
       </x:c>
-      <x:c r="D1" s="8" t="str">
+      <x:c r="F1" s="8" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="E1" s="8" t="str">
+      <x:c r="G1" s="8" t="str">
         <x:v>完成率</x:v>
       </x:c>
-      <x:c r="F1" s="8" t="str">
+      <x:c r="H1" s="8" t="str">
         <x:v>本周较上周</x:v>
-      </x:c>
-      <x:c r="G1" s="8" t="str">
-        <x:v>新客数</x:v>
-      </x:c>
-      <x:c r="H1" s="8" t="str">
-        <x:v>老客数</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
         <x:v>新签营收</x:v>
@@ -1002,23 +1048,23 @@
       <x:c r="B2" s="4" t="str">
         <x:v>焦作万达</x:v>
       </x:c>
-      <x:c r="C2" s="11" t="n">
+      <x:c r="C2" s="4" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="n">
         <x:v>36882.4</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="n">
+      <x:c r="F2" s="11" t="n">
         <x:v>40419</x:v>
       </x:c>
-      <x:c r="E2" s="13" t="n">
+      <x:c r="G2" s="13" t="n">
         <x:v>0.9125015463024816</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="n">
+      <x:c r="H2" s="12" t="n">
         <x:v>0.12211654892511403</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H2" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
         <x:v>15240</x:v>
@@ -1062,8 +1108,8 @@
       <x:c r="V2" s="11" t="n">
         <x:v>17800</x:v>
       </x:c>
-      <x:c r="W2" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W2" s="11" t="n">
+        <x:v>18561.2</x:v>
       </x:c>
       <x:c r="X2" s="11" t="n">
         <x:v>8531.2</x:v>
@@ -1072,7 +1118,7 @@
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
       <x:c r="Z2" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1082,23 +1128,23 @@
       <x:c r="B3" s="4" t="str">
         <x:v>洛阳泉舜</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="n">
+      <x:c r="C3" s="4" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="n">
         <x:v>34016</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="n">
+      <x:c r="F3" s="11" t="n">
         <x:v>43950</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="n">
+      <x:c r="G3" s="13" t="n">
         <x:v>0.7739704209328783</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="n">
+      <x:c r="H3" s="12" t="n">
         <x:v>-0.47829837173756273</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H3" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
         <x:v>16461</x:v>
@@ -1142,8 +1188,8 @@
       <x:c r="V3" s="11" t="n">
         <x:v>12299</x:v>
       </x:c>
-      <x:c r="W3" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W3" s="11" t="n">
+        <x:v>10002</x:v>
       </x:c>
       <x:c r="X3" s="11" t="n">
         <x:v>8325</x:v>
@@ -1152,7 +1198,7 @@
         <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
       </x:c>
       <x:c r="Z3" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1162,23 +1208,23 @@
       <x:c r="B4" s="4" t="str">
         <x:v>开封万达</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="n">
+      <x:c r="C4" s="4" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="n">
         <x:v>30548.5</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="n">
+      <x:c r="F4" s="11" t="n">
         <x:v>34316</x:v>
       </x:c>
-      <x:c r="E4" s="13" t="n">
+      <x:c r="G4" s="13" t="n">
         <x:v>0.8902115631192448</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="n">
+      <x:c r="H4" s="12" t="n">
         <x:v>0.2677304228742167</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
         <x:v>20415</x:v>
@@ -1222,8 +1268,8 @@
       <x:c r="V4" s="11" t="n">
         <x:v>6900</x:v>
       </x:c>
-      <x:c r="W4" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W4" s="11" t="n">
+        <x:v>21063.4</x:v>
       </x:c>
       <x:c r="X4" s="11" t="n">
         <x:v>9649</x:v>
@@ -1232,7 +1278,7 @@
         <x:v>完成率89.02%&lt;100%；新签小卡率62.75%&gt;40%</x:v>
       </x:c>
       <x:c r="Z4" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1242,23 +1288,23 @@
       <x:c r="B5" s="4" t="str">
         <x:v>武汉荟聚</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="n">
+      <x:c r="C5" s="4" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="n">
         <x:v>30206</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="n">
+      <x:c r="F5" s="11" t="n">
         <x:v>43960</x:v>
       </x:c>
-      <x:c r="E5" s="13" t="n">
+      <x:c r="G5" s="13" t="n">
         <x:v>0.6871246587807097</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="n">
+      <x:c r="H5" s="12" t="n">
         <x:v>-0.1063842376190758</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
         <x:v>24256</x:v>
@@ -1302,8 +1348,8 @@
       <x:c r="V5" s="11" t="n">
         <x:v>1500</x:v>
       </x:c>
-      <x:c r="W5" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W5" s="11" t="n">
+        <x:v>19288</x:v>
       </x:c>
       <x:c r="X5" s="11" t="n">
         <x:v>7715</x:v>
@@ -1312,7 +1358,7 @@
         <x:v>完成率68.71%&lt;100%；新签小卡率64.91%&gt;40%</x:v>
       </x:c>
       <x:c r="Z5" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1322,23 +1368,23 @@
       <x:c r="B6" s="4" t="str">
         <x:v>襄阳高新万达</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="n">
+      <x:c r="C6" s="4" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="n">
         <x:v>27207</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="n">
+      <x:c r="F6" s="11" t="n">
         <x:v>35016</x:v>
       </x:c>
-      <x:c r="E6" s="13" t="n">
+      <x:c r="G6" s="13" t="n">
         <x:v>0.7769876627827279</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="n">
+      <x:c r="H6" s="12" t="n">
         <x:v>0.03478178187696111</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
         <x:v>21837</x:v>
@@ -1382,8 +1428,8 @@
       <x:c r="V6" s="11" t="n">
         <x:v>2768</x:v>
       </x:c>
-      <x:c r="W6" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W6" s="11" t="n">
+        <x:v>9301</x:v>
       </x:c>
       <x:c r="X6" s="11" t="n">
         <x:v>3923</x:v>
@@ -1392,7 +1438,7 @@
         <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
       </x:c>
       <x:c r="Z6" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1402,23 +1448,23 @@
       <x:c r="B7" s="4" t="str">
         <x:v>周口万达</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="n">
+      <x:c r="C7" s="4" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="n">
         <x:v>27183.6</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="n">
+      <x:c r="F7" s="11" t="n">
         <x:v>20390</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="n">
+      <x:c r="G7" s="12" t="n">
         <x:v>1.333182932810201</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="n">
+      <x:c r="H7" s="12" t="n">
         <x:v>0.858047053355388</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
         <x:v>22422.6</x:v>
@@ -1462,8 +1508,8 @@
       <x:c r="V7" s="11" t="n">
         <x:v>1800</x:v>
       </x:c>
-      <x:c r="W7" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W7" s="11" t="n">
+        <x:v>5077.2</x:v>
       </x:c>
       <x:c r="X7" s="11" t="n">
         <x:v>1814</x:v>
@@ -1472,7 +1518,7 @@
         <x:v>当前已核指标无异常</x:v>
       </x:c>
       <x:c r="Z7" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1482,23 +1528,23 @@
       <x:c r="B8" s="4" t="str">
         <x:v>郑州二七万象城</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="n">
+      <x:c r="C8" s="4" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="n">
         <x:v>25527</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="n">
+      <x:c r="F8" s="11" t="n">
         <x:v>32450</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="n">
+      <x:c r="G8" s="13" t="n">
         <x:v>0.7866563944530046</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="n">
+      <x:c r="H8" s="12" t="n">
         <x:v>-0.13928788185312563</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H8" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
         <x:v>17570</x:v>
@@ -1542,8 +1588,8 @@
       <x:c r="V8" s="11" t="n">
         <x:v>3920</x:v>
       </x:c>
-      <x:c r="W8" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W8" s="11" t="n">
+        <x:v>6987</x:v>
       </x:c>
       <x:c r="X8" s="11" t="n">
         <x:v>1000</x:v>
@@ -1552,7 +1598,7 @@
         <x:v>完成率78.67%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
       <x:c r="Z8" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1562,23 +1608,23 @@
       <x:c r="B9" s="4" t="str">
         <x:v>郑州中原万达</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="n">
+      <x:c r="C9" s="4" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="n">
         <x:v>21882</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="n">
+      <x:c r="F9" s="11" t="n">
         <x:v>31100</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="n">
+      <x:c r="G9" s="13" t="n">
         <x:v>0.7036012861736335</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="n">
+      <x:c r="H9" s="12" t="n">
         <x:v>0.04718606431852987</x:v>
-      </x:c>
-      <x:c r="G9" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
         <x:v>11554</x:v>
@@ -1622,8 +1668,8 @@
       <x:c r="V9" s="11" t="n">
         <x:v>7400</x:v>
       </x:c>
-      <x:c r="W9" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W9" s="11" t="n">
+        <x:v>10079</x:v>
       </x:c>
       <x:c r="X9" s="11" t="n">
         <x:v>2287</x:v>
@@ -1632,7 +1678,7 @@
         <x:v>完成率70.36%&lt;100%；新签小卡率57.14%&gt;40%</x:v>
       </x:c>
       <x:c r="Z9" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1642,23 +1688,23 @@
       <x:c r="B10" s="4" t="str">
         <x:v>南阳吾悦</x:v>
       </x:c>
-      <x:c r="C10" s="11" t="n">
+      <x:c r="C10" s="4" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="n">
         <x:v>19374</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="n">
+      <x:c r="F10" s="11" t="n">
         <x:v>35904</x:v>
       </x:c>
-      <x:c r="E10" s="13" t="n">
+      <x:c r="G10" s="13" t="n">
         <x:v>0.539605614973262</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="n">
+      <x:c r="H10" s="12" t="n">
         <x:v>-0.11908334470058655</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
         <x:v>11529</x:v>
@@ -1702,8 +1748,8 @@
       <x:c r="V10" s="11" t="n">
         <x:v>5949</x:v>
       </x:c>
-      <x:c r="W10" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W10" s="11" t="n">
+        <x:v>4770</x:v>
       </x:c>
       <x:c r="X10" s="11" t="n">
         <x:v>2031</x:v>
@@ -1712,7 +1758,7 @@
         <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
       </x:c>
       <x:c r="Z10" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1722,23 +1768,23 @@
       <x:c r="B11" s="4" t="str">
         <x:v>洛阳中州万达</x:v>
       </x:c>
-      <x:c r="C11" s="11" t="n">
+      <x:c r="C11" s="4" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="n">
         <x:v>18990</x:v>
       </x:c>
-      <x:c r="D11" s="11" t="n">
+      <x:c r="F11" s="11" t="n">
         <x:v>24778</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="n">
+      <x:c r="G11" s="13" t="n">
         <x:v>0.766405682460247</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="n">
+      <x:c r="H11" s="12" t="n">
         <x:v>0.21117418202691499</x:v>
-      </x:c>
-      <x:c r="G11" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H11" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
         <x:v>14184</x:v>
@@ -1782,8 +1828,8 @@
       <x:c r="V11" s="11" t="n">
         <x:v>1600</x:v>
       </x:c>
-      <x:c r="W11" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W11" s="11" t="n">
+        <x:v>10781</x:v>
       </x:c>
       <x:c r="X11" s="11" t="n">
         <x:v>3349</x:v>
@@ -1792,7 +1838,7 @@
         <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
       </x:c>
       <x:c r="Z11" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1802,24 +1848,22 @@
       <x:c r="B12" s="4" t="str">
         <x:v>许昌魏都万达</x:v>
       </x:c>
-      <x:c r="C12" s="11" t="n">
+      <x:c r="C12" s="4" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="n">
         <x:v>17482.2</x:v>
       </x:c>
-      <x:c r="D12" s="11" t="n">
+      <x:c r="F12" s="11" t="n">
         <x:v>24264</x:v>
       </x:c>
-      <x:c r="E12" s="13" t="n">
+      <x:c r="G12" s="13" t="n">
         <x:v>0.7204995054401583</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G12" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H12" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
+      <x:c r="H12" s="12"/>
       <x:c r="I12" s="11" t="n">
         <x:v>9243</x:v>
       </x:c>
@@ -1862,8 +1906,8 @@
       <x:c r="V12" s="11" t="n">
         <x:v>6280</x:v>
       </x:c>
-      <x:c r="W12" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W12" s="11" t="n">
+        <x:v>6685</x:v>
       </x:c>
       <x:c r="X12" s="11" t="n">
         <x:v>3198</x:v>
@@ -1872,7 +1916,7 @@
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
       <x:c r="Z12" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1882,23 +1926,23 @@
       <x:c r="B13" s="4" t="str">
         <x:v>商丘万达</x:v>
       </x:c>
-      <x:c r="C13" s="11" t="n">
+      <x:c r="C13" s="4" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="n">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="n">
         <x:v>17406</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="n">
+      <x:c r="F13" s="11" t="n">
         <x:v>21126</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="n">
+      <x:c r="G13" s="13" t="n">
         <x:v>0.823913660891792</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="n">
+      <x:c r="H13" s="12" t="n">
         <x:v>0.12578219742905652</x:v>
-      </x:c>
-      <x:c r="G13" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H13" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
         <x:v>7748</x:v>
@@ -1942,8 +1986,8 @@
       <x:c r="V13" s="11" t="n">
         <x:v>7964</x:v>
       </x:c>
-      <x:c r="W13" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W13" s="11" t="n">
+        <x:v>8760</x:v>
       </x:c>
       <x:c r="X13" s="11" t="n">
         <x:v>2987</x:v>
@@ -1952,7 +1996,7 @@
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
       <x:c r="Z13" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1962,23 +2006,23 @@
       <x:c r="B14" s="4" t="str">
         <x:v>郑州信万</x:v>
       </x:c>
-      <x:c r="C14" s="11" t="n">
+      <x:c r="C14" s="4" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="n">
         <x:v>16093</x:v>
       </x:c>
-      <x:c r="D14" s="11" t="n">
+      <x:c r="F14" s="11" t="n">
         <x:v>18966</x:v>
       </x:c>
-      <x:c r="E14" s="13" t="n">
+      <x:c r="G14" s="13" t="n">
         <x:v>0.8485184013497838</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="n">
+      <x:c r="H14" s="12" t="n">
         <x:v>0.15935451336359052</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H14" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
         <x:v>11008</x:v>
@@ -2022,8 +2066,8 @@
       <x:c r="V14" s="11" t="n">
         <x:v>4089</x:v>
       </x:c>
-      <x:c r="W14" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W14" s="11" t="n">
+        <x:v>6403</x:v>
       </x:c>
       <x:c r="X14" s="11" t="n">
         <x:v>3069</x:v>
@@ -2032,7 +2076,7 @@
         <x:v>完成率84.85%&lt;100%</x:v>
       </x:c>
       <x:c r="Z14" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2042,23 +2086,23 @@
       <x:c r="B15" s="4" t="str">
         <x:v>南阳万达</x:v>
       </x:c>
-      <x:c r="C15" s="11" t="n">
+      <x:c r="C15" s="4" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="n">
         <x:v>14716.02</x:v>
       </x:c>
-      <x:c r="D15" s="11" t="n">
+      <x:c r="F15" s="11" t="n">
         <x:v>30027</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="n">
+      <x:c r="G15" s="13" t="n">
         <x:v>0.49009291637526226</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="n">
+      <x:c r="H15" s="12" t="n">
         <x:v>-0.4086722065063649</x:v>
-      </x:c>
-      <x:c r="G15" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H15" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
         <x:v>9833.02</x:v>
@@ -2102,8 +2146,8 @@
       <x:c r="V15" s="11" t="n">
         <x:v>3399</x:v>
       </x:c>
-      <x:c r="W15" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W15" s="11" t="n">
+        <x:v>4509</x:v>
       </x:c>
       <x:c r="X15" s="11" t="n">
         <x:v>491</x:v>
@@ -2112,7 +2156,7 @@
         <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
       </x:c>
       <x:c r="Z15" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2122,23 +2166,23 @@
       <x:c r="B16" s="4" t="str">
         <x:v>郑州惠济万达</x:v>
       </x:c>
-      <x:c r="C16" s="11" t="n">
+      <x:c r="C16" s="4" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="n">
         <x:v>12223</x:v>
       </x:c>
-      <x:c r="D16" s="11" t="n">
+      <x:c r="F16" s="11" t="n">
         <x:v>21654</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="n">
+      <x:c r="G16" s="13" t="n">
         <x:v>0.5644684584834211</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="n">
+      <x:c r="H16" s="12" t="n">
         <x:v>-0.29841539341946594</x:v>
-      </x:c>
-      <x:c r="G16" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H16" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
         <x:v>8912</x:v>
@@ -2182,8 +2226,8 @@
       <x:c r="V16" s="11" t="n">
         <x:v>3200</x:v>
       </x:c>
-      <x:c r="W16" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W16" s="11" t="n">
+        <x:v>4641</x:v>
       </x:c>
       <x:c r="X16" s="11" t="n">
         <x:v>2782</x:v>
@@ -2192,7 +2236,7 @@
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
       <x:c r="Z16" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2202,23 +2246,23 @@
       <x:c r="B17" s="4" t="str">
         <x:v>信阳万达</x:v>
       </x:c>
-      <x:c r="C17" s="11" t="n">
+      <x:c r="C17" s="4" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="n">
         <x:v>11920.95</x:v>
       </x:c>
-      <x:c r="D17" s="11" t="n">
+      <x:c r="F17" s="11" t="n">
         <x:v>18060</x:v>
       </x:c>
-      <x:c r="E17" s="13" t="n">
+      <x:c r="G17" s="13" t="n">
         <x:v>0.6600747508305648</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="n">
+      <x:c r="H17" s="12" t="n">
         <x:v>0.11515488847001155</x:v>
-      </x:c>
-      <x:c r="G17" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H17" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
         <x:v>9034.6</x:v>
@@ -2262,8 +2306,8 @@
       <x:c r="V17" s="11" t="n">
         <x:v>1486.15</x:v>
       </x:c>
-      <x:c r="W17" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W17" s="11" t="n">
+        <x:v>4405.5</x:v>
       </x:c>
       <x:c r="X17" s="11" t="n">
         <x:v>3279.4</x:v>
@@ -2272,7 +2316,7 @@
         <x:v>完成率66.01%&lt;100%</x:v>
       </x:c>
       <x:c r="Z17" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2282,23 +2326,23 @@
       <x:c r="B18" s="4" t="str">
         <x:v>新乡万达</x:v>
       </x:c>
-      <x:c r="C18" s="11" t="n">
+      <x:c r="C18" s="4" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="n">
         <x:v>11731.2</x:v>
       </x:c>
-      <x:c r="D18" s="11" t="n">
+      <x:c r="F18" s="11" t="n">
         <x:v>18959</x:v>
       </x:c>
-      <x:c r="E18" s="13" t="n">
+      <x:c r="G18" s="13" t="n">
         <x:v>0.6187668125956011</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="n">
+      <x:c r="H18" s="12" t="n">
         <x:v>-0.18782625552124727</x:v>
-      </x:c>
-      <x:c r="G18" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H18" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
         <x:v>4837</x:v>
@@ -2342,8 +2386,8 @@
       <x:c r="V18" s="11" t="n">
         <x:v>2800</x:v>
       </x:c>
-      <x:c r="W18" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W18" s="11" t="n">
+        <x:v>7467.2</x:v>
       </x:c>
       <x:c r="X18" s="11" t="n">
         <x:v>2243.2</x:v>
@@ -2352,7 +2396,7 @@
         <x:v>完成率61.88%&lt;100%</x:v>
       </x:c>
       <x:c r="Z18" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2362,24 +2406,22 @@
       <x:c r="B19" s="4" t="str">
         <x:v>安阳滑县吾悦</x:v>
       </x:c>
-      <x:c r="C19" s="11" t="n">
+      <x:c r="C19" s="4" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E19" s="11" t="n">
         <x:v>8696</x:v>
       </x:c>
-      <x:c r="D19" s="11" t="n">
+      <x:c r="F19" s="11" t="n">
         <x:v>16610</x:v>
       </x:c>
-      <x:c r="E19" s="13" t="n">
+      <x:c r="G19" s="13" t="n">
         <x:v>0.5235400361228176</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="G19" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H19" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
+      <x:c r="H19" s="12"/>
       <x:c r="I19" s="11" t="n">
         <x:v>5862</x:v>
       </x:c>
@@ -2422,8 +2464,8 @@
       <x:c r="V19" s="11" t="n">
         <x:v>957</x:v>
       </x:c>
-      <x:c r="W19" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W19" s="11" t="n">
+        <x:v>7096</x:v>
       </x:c>
       <x:c r="X19" s="11" t="n">
         <x:v>1771</x:v>
@@ -2432,7 +2474,7 @@
         <x:v>完成率52.35%&lt;100%</x:v>
       </x:c>
       <x:c r="Z19" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2442,23 +2484,23 @@
       <x:c r="B20" s="4" t="str">
         <x:v>安阳万达</x:v>
       </x:c>
-      <x:c r="C20" s="11" t="n">
+      <x:c r="C20" s="4" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E20" s="11" t="n">
         <x:v>7175.2</x:v>
       </x:c>
-      <x:c r="D20" s="11" t="n">
+      <x:c r="F20" s="11" t="n">
         <x:v>17660</x:v>
       </x:c>
-      <x:c r="E20" s="13" t="n">
+      <x:c r="G20" s="13" t="n">
         <x:v>0.4062967157417894</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="n">
+      <x:c r="H20" s="12" t="n">
         <x:v>-0.14468947431159854</x:v>
-      </x:c>
-      <x:c r="G20" s="4" t="str">
-        <x:v>待核</x:v>
-      </x:c>
-      <x:c r="H20" s="4" t="str">
-        <x:v>待核</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
         <x:v>5599</x:v>
@@ -2502,8 +2544,8 @@
       <x:c r="V20" s="11" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="W20" s="11" t="str">
-        <x:v>待核</x:v>
+      <x:c r="W20" s="11" t="n">
+        <x:v>7175.2</x:v>
       </x:c>
       <x:c r="X20" s="11" t="n">
         <x:v>0</x:v>
@@ -2512,13 +2554,13 @@
         <x:v>完成率40.63%&lt;100%</x:v>
       </x:c>
       <x:c r="Z20" s="4" t="str">
-        <x:v>2026-07-27小程序截图原值；新客数、老客数和总引流金额等待飞书原值</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95803d64d94a4c2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R985a80e3939c49a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4832,7 +4874,1137 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c2577c795b24511"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R326e4431f99e4146"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>本周排名</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>上周排名</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
+        <x:v>排名变化</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>区域</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>门店</x:v>
+      </x:c>
+      <x:c r="F1" s="8" t="str">
+        <x:v>员工</x:v>
+      </x:c>
+      <x:c r="G1" s="8" t="str">
+        <x:v>本周总金额</x:v>
+      </x:c>
+      <x:c r="H1" s="8" t="str">
+        <x:v>完成率</x:v>
+      </x:c>
+      <x:c r="I1" s="8" t="str">
+        <x:v>上周总金额</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
+        <x:v>金额增减</x:v>
+      </x:c>
+      <x:c r="K1" s="8" t="str">
+        <x:v>充值金额</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
+        <x:v>散单金额</x:v>
+      </x:c>
+      <x:c r="M1" s="8" t="str">
+        <x:v>新签小卡数</x:v>
+      </x:c>
+      <x:c r="N1" s="8" t="str">
+        <x:v>新签中卡数</x:v>
+      </x:c>
+      <x:c r="O1" s="8" t="str">
+        <x:v>新签大卡数</x:v>
+      </x:c>
+      <x:c r="P1" s="8" t="str">
+        <x:v>续费率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="str">
+        <x:v>开封万达</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="str">
+        <x:v>卢嘉诺</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="n">
+        <x:v>4029</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="n">
+        <x:v>0.5870000000000001</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>1266</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="n">
+        <x:v>2763</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="n">
+        <x:v>3951</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="M2" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N2" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O2" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="str">
+        <x:v>信阳万达</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="str">
+        <x:v>胡功海</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="n">
+        <x:v>1900.15</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="n">
+        <x:v>0.2691</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="n">
+        <x:v>4252.1</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="n">
+        <x:v>-2351.9500000000003</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="n">
+        <x:v>1607.15</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M3" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N3" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O3" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P3" s="12" t="n">
+        <x:v>0.0625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>武汉荟聚</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>周坤琪</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="n">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="n">
+        <x:v>0.6087</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="n">
+        <x:v>7638</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="n">
+        <x:v>-5933</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="n">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>蒋雪柯</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="n">
+        <x:v>1.9153</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="n">
+        <x:v>6137</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="n">
+        <x:v>-4831</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="L5" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O5" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" s="12" t="n">
+        <x:v>0.10869999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>安阳万达</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>宋宋</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="n">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="n">
+        <x:v>0.5017</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="n">
+        <x:v>4795</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>-3849</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="n">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O6" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>新乡万达</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>贵诗涵</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="n">
+        <x:v>0.4325</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="n">
+        <x:v>3697</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>-2831</x:v>
+      </x:c>
+      <x:c r="K7" s="11" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="12" t="n">
+        <x:v>0.075</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>焦作万达</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>张强</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="n">
+        <x:v>0.44770000000000004</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
+        <x:v>4711</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>-3955</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O8" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="12" t="n">
+        <x:v>0.09380000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>郑州中原万达</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>王嘉琦</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="n">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="n">
+        <x:v>0.8273999999999999</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
+        <x:v>5341</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>-4692</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="n">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" s="12" t="n">
+        <x:v>0.1176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>周口万达</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
+        <x:v>杨宁可</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="n">
+        <x:v>0.6564</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
+        <x:v>3513.2</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="n">
+        <x:v>-3042.2</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O10" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="n">
+        <x:v>0.037000000000000005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str">
+        <x:v>王若涵</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="n">
+        <x:v>0.45030000000000003</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
+        <x:v>6408</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="n">
+        <x:v>-5947</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="n">
+        <x:v>0.0851</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="str">
+        <x:v>安阳滑县吾悦</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str">
+        <x:v>汤明放</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="n">
+        <x:v>1.0974</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>5552.3</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="n">
+        <x:v>-5139.3</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N12" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O12" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P12" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>襄阳高新万达</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>王爽</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="n">
+        <x:v>1.1775</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>4303</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="n">
+        <x:v>-3903</x:v>
+      </x:c>
+      <x:c r="K13" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O13" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="12" t="n">
+        <x:v>0.23079999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>洛阳中州万达</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>霍亭芮</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="n">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="n">
+        <x:v>0.8713</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:v>1229</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="n">
+        <x:v>-983</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="n">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O14" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="12" t="n">
+        <x:v>0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="n">
+        <x:v>-13</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>许昌魏都万达</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>孙刘柱</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="n">
+        <x:v>225.2</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="n">
+        <x:v>0.37560000000000004</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:v>10073.2</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="n">
+        <x:v>-9848</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="n">
+        <x:v>225.2</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O15" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>商丘万达</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>李烨</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="n">
+        <x:v>0.7139</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:v>1247</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="n">
+        <x:v>-1071</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N16" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O16" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P16" s="12" t="n">
+        <x:v>0.23079999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="n">
+        <x:v>-10</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>南阳万达</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>王佳婷</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="n">
+        <x:v>0.4354</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>5879</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="n">
+        <x:v>-5729</x:v>
+      </x:c>
+      <x:c r="K17" s="11" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O17" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17" s="12" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="n">
+        <x:v>-13</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>郑州惠济万达</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>张运倩</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="n">
+        <x:v>0.7475</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>6199</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="n">
+        <x:v>-6199</x:v>
+      </x:c>
+      <x:c r="K18" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N18" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>郑州二七万象城</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>郑金原</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="n">
+        <x:v>0.5396</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="n">
+        <x:v>1787</x:v>
+      </x:c>
+      <x:c r="J19" s="11" t="n">
+        <x:v>-1787</x:v>
+      </x:c>
+      <x:c r="K19" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O19" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P19" s="12" t="n">
+        <x:v>0.3333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>郑州信万</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>司聪慧</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="n">
+        <x:v>0.48829999999999996</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
+        <x:v>3146</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="n">
+        <x:v>-3146</x:v>
+      </x:c>
+      <x:c r="K20" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="12" t="n">
+        <x:v>0.16670000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="n">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>南阳吾悦</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>齐继凤</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="n">
+        <x:v>0.16949999999999998</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="n">
+        <x:v>3542</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="n">
+        <x:v>-3542</x:v>
+      </x:c>
+      <x:c r="K21" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="12" t="n">
+        <x:v>0.0196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>南阳万达</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>蔺海芬</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>2088</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="n">
+        <x:v>-2088</x:v>
+      </x:c>
+      <x:c r="K22" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0756a03d3e64a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Re74f4611871d4228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="R421ae5ea02c541c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R8ab97e03a33640df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R0c06ab6b7be840a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="5" r:id="Re92976bbd5a543ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R4aaadbd9f1a94053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rcf839dd6e2aa45fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R1474e56ec2444a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R390751f0abbd4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="5" r:id="Rf7fbae548db24f66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -212,8 +212,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable3" displayName="WeeklyTable3" ref="A1:L61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:L61"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable3" displayName="WeeklyTable3" ref="A1:L40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:L40"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="排名"/>
     <x:tableColumn id="2" name="区域"/>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc2aeb6e24ca440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52aae7e623f4c26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2560,7 +2560,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R985a80e3939c49a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racc2cd85254249ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3231,349 +3231,349 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="4" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>襄阳高新万达</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>王爽</x:v>
+        <x:v>邵娜娜</x:v>
       </x:c>
       <x:c r="E18" s="4" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F18" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G18" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H18" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="12" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.5625</x:v>
       </x:c>
       <x:c r="J18" s="12" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.4375</x:v>
       </x:c>
       <x:c r="K18" s="12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L18" s="12" t="n">
-        <x:v>0.23079999999999998</x:v>
+        <x:v>0.0263</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="4" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
+        <x:v>南阳吾悦</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>邵娜娜</x:v>
+        <x:v>朱玫卉</x:v>
       </x:c>
       <x:c r="E19" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G19" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H19" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="12" t="n">
-        <x:v>0.5625</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="J19" s="12" t="n">
-        <x:v>0.4375</x:v>
+        <x:v>0.2727272727272727</x:v>
       </x:c>
       <x:c r="K19" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="L19" s="12" t="n">
-        <x:v>0.0263</x:v>
+        <x:v>0.087</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="4" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>南阳吾悦</x:v>
+        <x:v>周口万达</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>朱玫卉</x:v>
+        <x:v>冯瀚文</x:v>
       </x:c>
       <x:c r="E20" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G20" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="12" t="n">
-        <x:v>0.6363636363636364</x:v>
+        <x:v>0.35714285714285715</x:v>
       </x:c>
       <x:c r="J20" s="12" t="n">
-        <x:v>0.2727272727272727</x:v>
+        <x:v>0.5714285714285714</x:v>
       </x:c>
       <x:c r="K20" s="12" t="n">
-        <x:v>0.09090909090909091</x:v>
+        <x:v>0.07142857142857142</x:v>
       </x:c>
       <x:c r="L20" s="12" t="n">
-        <x:v>0.087</x:v>
+        <x:v>0.08109999999999999</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>周口万达</x:v>
+        <x:v>洛阳中州万达</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>冯瀚文</x:v>
+        <x:v>党蕊蕊</x:v>
       </x:c>
       <x:c r="E21" s="4" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G21" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H21" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I21" s="12" t="n">
-        <x:v>0.35714285714285715</x:v>
+        <x:v>0.7647058823529411</x:v>
       </x:c>
       <x:c r="J21" s="12" t="n">
-        <x:v>0.5714285714285714</x:v>
+        <x:v>0.2352941176470588</x:v>
       </x:c>
       <x:c r="K21" s="12" t="n">
-        <x:v>0.07142857142857142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L21" s="12" t="n">
-        <x:v>0.08109999999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="4" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>洛阳中州万达</x:v>
+        <x:v>郑州信万</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>党蕊蕊</x:v>
+        <x:v>余心如</x:v>
       </x:c>
       <x:c r="E22" s="4" t="n">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H22" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I22" s="12" t="n">
-        <x:v>0.7647058823529411</x:v>
+        <x:v>0.07142857142857142</x:v>
       </x:c>
       <x:c r="J22" s="12" t="n">
-        <x:v>0.2352941176470588</x:v>
+        <x:v>0.5714285714285714</x:v>
       </x:c>
       <x:c r="K22" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.35714285714285715</x:v>
       </x:c>
       <x:c r="L22" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0385</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="4" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>郑州信万</x:v>
+        <x:v>郑州中原万达</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>余心如</x:v>
+        <x:v>殷翔坤</x:v>
       </x:c>
       <x:c r="E23" s="4" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F23" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G23" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H23" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="I23" s="12" t="n">
-        <x:v>0.07142857142857142</x:v>
+        <x:v>0.6153846153846154</x:v>
       </x:c>
       <x:c r="J23" s="12" t="n">
-        <x:v>0.5714285714285714</x:v>
+        <x:v>0.3076923076923077</x:v>
       </x:c>
       <x:c r="K23" s="12" t="n">
-        <x:v>0.35714285714285715</x:v>
+        <x:v>0.07692307692307693</x:v>
       </x:c>
       <x:c r="L23" s="12" t="n">
-        <x:v>0.0385</x:v>
+        <x:v>0.07690000000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
+        <x:v>洛阳泉舜</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>殷翔坤</x:v>
+        <x:v>王佳琳</x:v>
       </x:c>
       <x:c r="E24" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F24" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G24" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H24" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="12" t="n">
-        <x:v>0.6153846153846154</x:v>
+        <x:v>0.42857142857142855</x:v>
       </x:c>
       <x:c r="J24" s="12" t="n">
-        <x:v>0.3076923076923077</x:v>
+        <x:v>0.42857142857142855</x:v>
       </x:c>
       <x:c r="K24" s="12" t="n">
-        <x:v>0.07692307692307693</x:v>
+        <x:v>0.14285714285714285</x:v>
       </x:c>
       <x:c r="L24" s="12" t="n">
-        <x:v>0.07690000000000001</x:v>
+        <x:v>0.0909</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="4" t="n">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>洛阳泉舜</x:v>
+        <x:v>郑州信万</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>蒋雪柯</x:v>
+        <x:v>薛飘飘</x:v>
       </x:c>
       <x:c r="E25" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F25" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G25" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H25" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I25" s="12" t="n">
-        <x:v>0.5555555555555556</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J25" s="12" t="n">
-        <x:v>0.4444444444444444</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="K25" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.875</x:v>
       </x:c>
       <x:c r="L25" s="12" t="n">
-        <x:v>0.10869999999999999</x:v>
+        <x:v>0.17859999999999998</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="4" t="n">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>安阳滑县吾悦</x:v>
+        <x:v>周口万达</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>汤明放</x:v>
+        <x:v>郑梦婷</x:v>
       </x:c>
       <x:c r="E26" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G26" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H26" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G26" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H26" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="I26" s="12" t="n">
-        <x:v>0.16666666666666663</x:v>
+        <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="J26" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
+        <x:v>0.7272727272727273</x:v>
       </x:c>
       <x:c r="K26" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="L26" s="12" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.0294</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="4" t="n">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
         <x:v>2区</x:v>
@@ -3582,139 +3582,139 @@
         <x:v>洛阳泉舜</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>王佳琳</x:v>
+        <x:v>杨翠鸽</x:v>
       </x:c>
       <x:c r="E27" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F27" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G27" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H27" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.625</x:v>
       </x:c>
       <x:c r="J27" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="K27" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="L27" s="12" t="n">
-        <x:v>0.0909</x:v>
+        <x:v>0.0968</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="4" t="n">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>郑州信万</x:v>
+        <x:v>郑州惠济万达</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>薛飘飘</x:v>
+        <x:v>张赛宁</x:v>
       </x:c>
       <x:c r="E28" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F28" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G28" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H28" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I28" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="J28" s="12" t="n">
-        <x:v>0.125</x:v>
+        <x:v>0.6666666666666665</x:v>
       </x:c>
       <x:c r="K28" s="12" t="n">
-        <x:v>0.875</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L28" s="12" t="n">
-        <x:v>0.17859999999999998</x:v>
+        <x:v>0.027000000000000003</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="4" t="n">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>商丘万达</x:v>
+        <x:v>新乡万达</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>李烨</x:v>
+        <x:v>李淑艳</x:v>
       </x:c>
       <x:c r="E29" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G29" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H29" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I29" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="J29" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.6666666666666665</x:v>
       </x:c>
       <x:c r="K29" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L29" s="12" t="n">
-        <x:v>0.23079999999999998</x:v>
+        <x:v>0.0167</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="4" t="n">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
         <x:v>3区</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
+        <x:v>安阳万达</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>周坤琪</x:v>
+        <x:v>杨晶晶</x:v>
       </x:c>
       <x:c r="E30" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F30" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G30" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H30" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I30" s="12" t="n">
-        <x:v>0.8333333333333335</x:v>
+        <x:v>0.2857142857142857</x:v>
       </x:c>
       <x:c r="J30" s="12" t="n">
-        <x:v>0.16666666666666663</x:v>
+        <x:v>0.7142857142857143</x:v>
       </x:c>
       <x:c r="K30" s="12" t="n">
         <x:v>0</x:v>
@@ -3725,75 +3725,75 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="4" t="n">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>周口万达</x:v>
+        <x:v>安阳滑县吾悦</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>郑梦婷</x:v>
+        <x:v>范超凡</x:v>
       </x:c>
       <x:c r="E31" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F31" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G31" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H31" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I31" s="12" t="n">
-        <x:v>0.09090909090909091</x:v>
+        <x:v>0.16666666666666663</x:v>
       </x:c>
       <x:c r="J31" s="12" t="n">
-        <x:v>0.7272727272727273</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="K31" s="12" t="n">
-        <x:v>0.18181818181818182</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="L31" s="12" t="n">
-        <x:v>0.0294</x:v>
+        <x:v>0.0435</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="4" t="n">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
         <x:v>3区</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>开封万达</x:v>
+        <x:v>郑州中原万达</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>卢嘉诺</x:v>
+        <x:v>杨依梦</x:v>
       </x:c>
       <x:c r="E32" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F32" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G32" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H32" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="J32" s="12" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="K32" s="12" t="n">
-        <x:v>0.08333333333333331</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="L32" s="12" t="n">
         <x:v>0</x:v>
@@ -3801,98 +3801,92 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="4" t="n">
-        <x:v>32</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>洛阳中州万达</x:v>
+        <x:v>郑州惠济万达</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>霍亭芮</x:v>
+        <x:v>杜珂源</x:v>
       </x:c>
       <x:c r="E33" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="12" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="J33" s="12" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K33" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I33" s="12"/>
+      <x:c r="J33" s="12"/>
+      <x:c r="K33" s="12"/>
       <x:c r="L33" s="12" t="n">
-        <x:v>0.0909</x:v>
+        <x:v>0.0833</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="4" t="n">
-        <x:v>33</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>洛阳泉舜</x:v>
+        <x:v>郑州中原万达</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>杨翠鸽</x:v>
+        <x:v>张茹</x:v>
       </x:c>
       <x:c r="E34" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F34" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G34" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H34" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H34" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I34" s="12" t="n">
-        <x:v>0.625</x:v>
-      </x:c>
-      <x:c r="J34" s="12" t="n">
-        <x:v>0.125</x:v>
-      </x:c>
       <x:c r="K34" s="12" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L34" s="12" t="n">
-        <x:v>0.0968</x:v>
+        <x:v>0.0909</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="4" t="n">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>洛阳泉舜</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>王若涵</x:v>
+        <x:v>代紫霞</x:v>
       </x:c>
       <x:c r="E35" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F35" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G35" s="4" t="n">
         <x:v>0</x:v>
@@ -3901,147 +3895,147 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="12" t="n">
-        <x:v>0.8571428571428571</x:v>
+        <x:v>0.6666666666666665</x:v>
       </x:c>
       <x:c r="J35" s="12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K35" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="L35" s="12" t="n">
-        <x:v>0.0851</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="4" t="n">
-        <x:v>35</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>郑州惠济万达</x:v>
+        <x:v>南阳万达</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>张运倩</x:v>
+        <x:v>徐瑞迎</x:v>
       </x:c>
       <x:c r="E36" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F36" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G36" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H36" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I36" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
       <x:c r="J36" s="12" t="n">
-        <x:v>0.7142857142857143</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K36" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L36" s="12" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="4" t="n">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
         <x:v>3区</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>郑州二七万象城</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>郑金原</x:v>
+        <x:v>严诗仪</x:v>
       </x:c>
       <x:c r="E37" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H37" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I37" s="12" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J37" s="12" t="n">
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="12" t="n">
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="12" t="n">
-        <x:v>0.3333</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="4" t="n">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>郑州惠济万达</x:v>
+        <x:v>新乡万达</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
-        <x:v>张赛宁</x:v>
+        <x:v>徐彬淼</x:v>
       </x:c>
       <x:c r="E38" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F38" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H38" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I38" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J38" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K38" s="12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="L38" s="12" t="n">
-        <x:v>0.027000000000000003</x:v>
+        <x:v>0.0435</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="4" t="n">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>郑州信万</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>司聪慧</x:v>
+        <x:v>郭文宇</x:v>
       </x:c>
       <x:c r="E39" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F39" s="4" t="n">
         <x:v>0</x:v>
@@ -4050,831 +4044,57 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H39" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="12"/>
-      <x:c r="J39" s="12"/>
-      <x:c r="K39" s="12"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="L39" s="12" t="n">
-        <x:v>0.16670000000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="4" t="n">
-        <x:v>39</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>周口万达</x:v>
+        <x:v>郑州中原万达</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>杨宁可</x:v>
+        <x:v>聂梦梦</x:v>
       </x:c>
       <x:c r="E40" s="4" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F40" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G40" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H40" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I40" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="J40" s="12" t="n">
-        <x:v>0.5555555555555556</x:v>
-      </x:c>
-      <x:c r="K40" s="12" t="n">
-        <x:v>0.1111111111111111</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="12"/>
+      <x:c r="J40" s="12"/>
+      <x:c r="K40" s="12"/>
       <x:c r="L40" s="12" t="n">
-        <x:v>0.037000000000000005</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="4" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B41" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C41" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
-      </x:c>
-      <x:c r="D41" s="4" t="str">
-        <x:v>王嘉琦</x:v>
-      </x:c>
-      <x:c r="E41" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F41" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G41" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H41" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I41" s="12" t="n">
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="J41" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
-      <x:c r="K41" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
-      <x:c r="L41" s="12" t="n">
-        <x:v>0.1176</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="4" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B42" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="C42" s="4" t="str">
-        <x:v>焦作万达</x:v>
-      </x:c>
-      <x:c r="D42" s="4" t="str">
-        <x:v>张强</x:v>
-      </x:c>
-      <x:c r="E42" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F42" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G42" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H42" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I42" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
-      </x:c>
-      <x:c r="J42" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="K42" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L42" s="12" t="n">
-        <x:v>0.09380000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="4" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B43" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C43" s="4" t="str">
-        <x:v>许昌魏都万达</x:v>
-      </x:c>
-      <x:c r="D43" s="4" t="str">
-        <x:v>孙刘柱</x:v>
-      </x:c>
-      <x:c r="E43" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F43" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G43" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H43" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I43" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="J43" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
-      </x:c>
-      <x:c r="K43" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L43" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="4" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B44" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C44" s="4" t="str">
-        <x:v>南阳万达</x:v>
-      </x:c>
-      <x:c r="D44" s="4" t="str">
-        <x:v>王佳婷</x:v>
-      </x:c>
-      <x:c r="E44" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F44" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G44" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H44" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I44" s="12" t="n">
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="J44" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
-      <x:c r="K44" s="12" t="n">
-        <x:v>0.14285714285714285</x:v>
-      </x:c>
-      <x:c r="L44" s="12" t="n">
-        <x:v>0.02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="4" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B45" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="C45" s="4" t="str">
-        <x:v>新乡万达</x:v>
-      </x:c>
-      <x:c r="D45" s="4" t="str">
-        <x:v>李淑艳</x:v>
-      </x:c>
-      <x:c r="E45" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F45" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G45" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H45" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I45" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="J45" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
-      </x:c>
-      <x:c r="K45" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L45" s="12" t="n">
-        <x:v>0.0167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="4" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B46" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C46" s="4" t="str">
-        <x:v>安阳万达</x:v>
-      </x:c>
-      <x:c r="D46" s="4" t="str">
-        <x:v>杨晶晶</x:v>
-      </x:c>
-      <x:c r="E46" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F46" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G46" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H46" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I46" s="12" t="n">
-        <x:v>0.2857142857142857</x:v>
-      </x:c>
-      <x:c r="J46" s="12" t="n">
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="K46" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L46" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="4" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B47" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C47" s="4" t="str">
-        <x:v>安阳滑县吾悦</x:v>
-      </x:c>
-      <x:c r="D47" s="4" t="str">
-        <x:v>范超凡</x:v>
-      </x:c>
-      <x:c r="E47" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F47" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H47" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I47" s="12" t="n">
-        <x:v>0.16666666666666663</x:v>
-      </x:c>
-      <x:c r="J47" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="K47" s="12" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="L47" s="12" t="n">
-        <x:v>0.0435</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="4" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B48" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C48" s="4" t="str">
-        <x:v>安阳万达</x:v>
-      </x:c>
-      <x:c r="D48" s="4" t="str">
-        <x:v>宋宋</x:v>
-      </x:c>
-      <x:c r="E48" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F48" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G48" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H48" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I48" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="J48" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
-      </x:c>
-      <x:c r="K48" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L48" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="4" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B49" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C49" s="4" t="str">
-        <x:v>南阳吾悦</x:v>
-      </x:c>
-      <x:c r="D49" s="4" t="str">
-        <x:v>齐继凤</x:v>
-      </x:c>
-      <x:c r="E49" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F49" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G49" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H49" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I49" s="12" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="J49" s="12" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K49" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L49" s="12" t="n">
-        <x:v>0.0196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="4" t="n">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B50" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C50" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
-      </x:c>
-      <x:c r="D50" s="4" t="str">
-        <x:v>杨依梦</x:v>
-      </x:c>
-      <x:c r="E50" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F50" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G50" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H50" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I50" s="12" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="J50" s="12" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="K50" s="12" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="L50" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="4" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B51" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="C51" s="4" t="str">
-        <x:v>郑州惠济万达</x:v>
-      </x:c>
-      <x:c r="D51" s="4" t="str">
-        <x:v>杜珂源</x:v>
-      </x:c>
-      <x:c r="E51" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F51" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G51" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H51" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I51" s="12"/>
-      <x:c r="J51" s="12"/>
-      <x:c r="K51" s="12"/>
-      <x:c r="L51" s="12" t="n">
-        <x:v>0.0833</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="4" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B52" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C52" s="4" t="str">
-        <x:v>信阳万达</x:v>
-      </x:c>
-      <x:c r="D52" s="4" t="str">
-        <x:v>胡功海</x:v>
-      </x:c>
-      <x:c r="E52" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F52" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G52" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H52" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I52" s="12" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="J52" s="12" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="K52" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L52" s="12" t="n">
-        <x:v>0.0625</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="4" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B53" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C53" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
-      </x:c>
-      <x:c r="D53" s="4" t="str">
-        <x:v>张茹</x:v>
-      </x:c>
-      <x:c r="E53" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F53" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G53" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H53" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I53" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J53" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K53" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L53" s="12" t="n">
-        <x:v>0.0909</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="4" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B54" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="C54" s="4" t="str">
-        <x:v>新乡万达</x:v>
-      </x:c>
-      <x:c r="D54" s="4" t="str">
-        <x:v>贵诗涵</x:v>
-      </x:c>
-      <x:c r="E54" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F54" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G54" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H54" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I54" s="12"/>
-      <x:c r="J54" s="12"/>
-      <x:c r="K54" s="12"/>
-      <x:c r="L54" s="12" t="n">
-        <x:v>0.075</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="4" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B55" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C55" s="4" t="str">
-        <x:v>南阳万达</x:v>
-      </x:c>
-      <x:c r="D55" s="4" t="str">
-        <x:v>蔺海芬</x:v>
-      </x:c>
-      <x:c r="E55" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F55" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G55" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H55" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I55" s="12"/>
-      <x:c r="J55" s="12"/>
-      <x:c r="K55" s="12"/>
-      <x:c r="L55" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="4" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B56" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C56" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
-      </x:c>
-      <x:c r="D56" s="4" t="str">
-        <x:v>代紫霞</x:v>
-      </x:c>
-      <x:c r="E56" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F56" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G56" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H56" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I56" s="12" t="n">
-        <x:v>0.6666666666666665</x:v>
-      </x:c>
-      <x:c r="J56" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
-      </x:c>
-      <x:c r="L56" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="4" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B57" s="4" t="str">
-        <x:v>1区</x:v>
-      </x:c>
-      <x:c r="C57" s="4" t="str">
-        <x:v>南阳万达</x:v>
-      </x:c>
-      <x:c r="D57" s="4" t="str">
-        <x:v>徐瑞迎</x:v>
-      </x:c>
-      <x:c r="E57" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F57" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G57" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H57" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I57" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J57" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L57" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="4" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B58" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C58" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
-      </x:c>
-      <x:c r="D58" s="4" t="str">
-        <x:v>严诗仪</x:v>
-      </x:c>
-      <x:c r="E58" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F58" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G58" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H58" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I58" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J58" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K58" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L58" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="4" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B59" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="C59" s="4" t="str">
-        <x:v>新乡万达</x:v>
-      </x:c>
-      <x:c r="D59" s="4" t="str">
-        <x:v>徐彬淼</x:v>
-      </x:c>
-      <x:c r="E59" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F59" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G59" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H59" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I59" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J59" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L59" s="12" t="n">
-        <x:v>0.0435</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="4" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B60" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C60" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
-      </x:c>
-      <x:c r="D60" s="4" t="str">
-        <x:v>郭文宇</x:v>
-      </x:c>
-      <x:c r="E60" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F60" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G60" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H60" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I60" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J60" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K60" s="12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L60" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="4" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B61" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="C61" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
-      </x:c>
-      <x:c r="D61" s="4" t="str">
-        <x:v>聂梦梦</x:v>
-      </x:c>
-      <x:c r="E61" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F61" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G61" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H61" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I61" s="12"/>
-      <x:c r="J61" s="12"/>
-      <x:c r="K61" s="12"/>
-      <x:c r="L61" s="12" t="n">
         <x:v>0.125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R326e4431f99e4146"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb78ea2ad23fb4e10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6004,7 +5224,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0756a03d3e64a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf050a06bc54f27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R4aaadbd9f1a94053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rcf839dd6e2aa45fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R1474e56ec2444a76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R390751f0abbd4e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="5" r:id="Rf7fbae548db24f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R50da8e0c297848eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rc07d5eba41314fd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R5ce8ff399df34f65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Re6f0fb77c2a64362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R12614d5ca4d44c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Ref80f24deea24f0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -233,9 +234,38 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable4" displayName="WeeklyTable4" ref="A1:P22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:P22"/>
-  <x:tableColumns count="16">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable4" displayName="WeeklyTable4" ref="A1:T40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:T40"/>
+  <x:tableColumns count="20">
+    <x:tableColumn id="1" name="本周排名"/>
+    <x:tableColumn id="2" name="上周排名"/>
+    <x:tableColumn id="3" name="排名变化"/>
+    <x:tableColumn id="4" name="区域"/>
+    <x:tableColumn id="5" name="门店"/>
+    <x:tableColumn id="6" name="员工"/>
+    <x:tableColumn id="7" name="本周总金额"/>
+    <x:tableColumn id="8" name="完成率"/>
+    <x:tableColumn id="9" name="上周总金额"/>
+    <x:tableColumn id="10" name="金额增减"/>
+    <x:tableColumn id="11" name="充值金额"/>
+    <x:tableColumn id="12" name="本周办卡数"/>
+    <x:tableColumn id="13" name="本周新签卡数"/>
+    <x:tableColumn id="14" name="本周续卡数"/>
+    <x:tableColumn id="15" name="新签办卡率"/>
+    <x:tableColumn id="16" name="新签小卡数"/>
+    <x:tableColumn id="17" name="新签中卡数"/>
+    <x:tableColumn id="18" name="新签大卡数"/>
+    <x:tableColumn id="19" name="续费率"/>
+    <x:tableColumn id="20" name="续卡金额"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="WeeklyTable5" displayName="WeeklyTable5" ref="A1:T22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:T22"/>
+  <x:tableColumns count="20">
     <x:tableColumn id="1" name="本周排名"/>
     <x:tableColumn id="2" name="上周排名"/>
     <x:tableColumn id="3" name="排名变化"/>
@@ -248,10 +278,14 @@
     <x:tableColumn id="10" name="金额增减"/>
     <x:tableColumn id="11" name="充值金额"/>
     <x:tableColumn id="12" name="散单金额"/>
-    <x:tableColumn id="13" name="新签小卡数"/>
-    <x:tableColumn id="14" name="新签中卡数"/>
-    <x:tableColumn id="15" name="新签大卡数"/>
-    <x:tableColumn id="16" name="续费率"/>
+    <x:tableColumn id="13" name="本周办卡数"/>
+    <x:tableColumn id="14" name="本周新签卡数"/>
+    <x:tableColumn id="15" name="本周续卡数"/>
+    <x:tableColumn id="16" name="新签办卡率"/>
+    <x:tableColumn id="17" name="新签小卡数"/>
+    <x:tableColumn id="18" name="新签中卡数"/>
+    <x:tableColumn id="19" name="新签大卡数"/>
+    <x:tableColumn id="20" name="续费率"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -928,7 +962,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52aae7e623f4c26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d3e6eee7dfd4988"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2560,7 +2594,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racc2cd85254249ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfabfa93de7f24384"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2778,37 +2812,37 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
+        <x:v>襄阳高新万达</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>李茁壮</x:v>
+        <x:v>倪书馨</x:v>
       </x:c>
       <x:c r="E6" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F6" s="4" t="n">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H6" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="12" t="n">
-        <x:v>0.6086956521739131</x:v>
+        <x:v>0.625</x:v>
       </x:c>
       <x:c r="J6" s="12" t="n">
-        <x:v>0.21739130434782608</x:v>
+        <x:v>0.33333333333333326</x:v>
       </x:c>
       <x:c r="K6" s="12" t="n">
-        <x:v>0.17391304347826086</x:v>
+        <x:v>0.04166666666666666</x:v>
       </x:c>
       <x:c r="L6" s="12" t="n">
-        <x:v>0.1304</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2822,31 +2856,31 @@
         <x:v>信阳万达</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>倪书馨</x:v>
+        <x:v>李立</x:v>
       </x:c>
       <x:c r="E7" s="4" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G7" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I7" s="12" t="n">
-        <x:v>0.625</x:v>
+        <x:v>0.2608695652173913</x:v>
       </x:c>
       <x:c r="J7" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
+        <x:v>0.6956521739130435</x:v>
       </x:c>
       <x:c r="K7" s="12" t="n">
-        <x:v>0.04166666666666666</x:v>
+        <x:v>0.043478260869565216</x:v>
       </x:c>
       <x:c r="L7" s="12" t="n">
-        <x:v>0.0625</x:v>
+        <x:v>0.1875</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2854,37 +2888,37 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>襄阳高新万达</x:v>
+        <x:v>焦作万达</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>李立</x:v>
+        <x:v>王梓恬</x:v>
       </x:c>
       <x:c r="E8" s="4" t="n">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G8" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H8" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="12" t="n">
-        <x:v>0.2608695652173913</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="J8" s="12" t="n">
-        <x:v>0.6956521739130435</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="K8" s="12" t="n">
-        <x:v>0.043478260869565216</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="12" t="n">
-        <x:v>0.1875</x:v>
+        <x:v>0.050499999999999996</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2892,37 +2926,37 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>焦作万达</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>王梓恬</x:v>
+        <x:v>李茁壮</x:v>
       </x:c>
       <x:c r="E9" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I9" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="J9" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="K9" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.18181818181818182</x:v>
       </x:c>
       <x:c r="L9" s="12" t="n">
-        <x:v>0.050499999999999996</x:v>
+        <x:v>0.1304</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3243,22 +3277,22 @@
         <x:v>邵娜娜</x:v>
       </x:c>
       <x:c r="E18" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G18" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H18" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I18" s="12" t="n">
-        <x:v>0.5625</x:v>
+        <x:v>0.5294117647058824</x:v>
       </x:c>
       <x:c r="J18" s="12" t="n">
-        <x:v>0.4375</x:v>
+        <x:v>0.4705882352941176</x:v>
       </x:c>
       <x:c r="K18" s="12" t="n">
         <x:v>0</x:v>
@@ -3535,7 +3569,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="4" t="n">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
         <x:v>2区</x:v>
@@ -3725,7 +3759,7 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="4" t="n">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
         <x:v>3区</x:v>
@@ -3737,7 +3771,7 @@
         <x:v>范超凡</x:v>
       </x:c>
       <x:c r="E31" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F31" s="4" t="n">
         <x:v>1</x:v>
@@ -3746,16 +3780,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H31" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I31" s="12" t="n">
-        <x:v>0.16666666666666663</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="J31" s="12" t="n">
-        <x:v>0.33333333333333326</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="K31" s="12" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="L31" s="12" t="n">
         <x:v>0.0435</x:v>
@@ -3813,20 +3847,26 @@
         <x:v>杜珂源</x:v>
       </x:c>
       <x:c r="E33" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F33" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G33" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H33" s="4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="12"/>
-      <x:c r="J33" s="12"/>
-      <x:c r="K33" s="12"/>
+      <x:c r="I33" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K33" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="L33" s="12" t="n">
         <x:v>0.0833</x:v>
       </x:c>
@@ -3950,19 +3990,19 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>2区</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
+        <x:v>新乡万达</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>严诗仪</x:v>
+        <x:v>徐彬淼</x:v>
       </x:c>
       <x:c r="E37" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F37" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G37" s="4" t="n">
         <x:v>0</x:v>
@@ -3980,7 +4020,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L37" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0435</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3988,19 +4028,19 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>新乡万达</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
-        <x:v>徐彬淼</x:v>
+        <x:v>严诗仪</x:v>
       </x:c>
       <x:c r="E38" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G38" s="4" t="n">
         <x:v>0</x:v>
@@ -4018,7 +4058,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L38" s="12" t="n">
-        <x:v>0.0435</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -4094,7 +4134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb78ea2ad23fb4e10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56d7fc05d79c4ff2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4114,11 +4154,15 @@
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -4156,19 +4200,31 @@
         <x:v>充值金额</x:v>
       </x:c>
       <x:c r="L1" s="8" t="str">
-        <x:v>散单金额</x:v>
+        <x:v>本周办卡数</x:v>
       </x:c>
       <x:c r="M1" s="8" t="str">
+        <x:v>本周新签卡数</x:v>
+      </x:c>
+      <x:c r="N1" s="8" t="str">
+        <x:v>本周续卡数</x:v>
+      </x:c>
+      <x:c r="O1" s="8" t="str">
+        <x:v>新签办卡率</x:v>
+      </x:c>
+      <x:c r="P1" s="8" t="str">
         <x:v>新签小卡数</x:v>
       </x:c>
-      <x:c r="N1" s="8" t="str">
+      <x:c r="Q1" s="8" t="str">
         <x:v>新签中卡数</x:v>
       </x:c>
-      <x:c r="O1" s="8" t="str">
+      <x:c r="R1" s="8" t="str">
         <x:v>新签大卡数</x:v>
       </x:c>
-      <x:c r="P1" s="8" t="str">
+      <x:c r="S1" s="8" t="str">
         <x:v>续费率</x:v>
+      </x:c>
+      <x:c r="T1" s="8" t="str">
+        <x:v>续卡金额</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -4176,10 +4232,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="4" t="n">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="4" t="n">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="4" t="str">
         <x:v>3区</x:v>
@@ -4188,37 +4244,49 @@
         <x:v>开封万达</x:v>
       </x:c>
       <x:c r="F2" s="4" t="str">
-        <x:v>卢嘉诺</x:v>
+        <x:v>易梦婷</x:v>
       </x:c>
       <x:c r="G2" s="11" t="n">
-        <x:v>4029</x:v>
+        <x:v>14525.2</x:v>
       </x:c>
       <x:c r="H2" s="12" t="n">
-        <x:v>0.5870000000000001</x:v>
+        <x:v>1.0581</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>1266</x:v>
+        <x:v>11043</x:v>
       </x:c>
       <x:c r="J2" s="11" t="n">
-        <x:v>2763</x:v>
+        <x:v>3482.2000000000007</x:v>
       </x:c>
       <x:c r="K2" s="11" t="n">
-        <x:v>3951</x:v>
-      </x:c>
-      <x:c r="L2" s="11" t="n">
-        <x:v>78</x:v>
+        <x:v>12784</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="n">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M2" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N2" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O2" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P2" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="n">
+        <x:v>0.561</x:v>
+      </x:c>
+      <x:c r="P2" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q2" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R2" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="n">
+        <x:v>0.2069</x:v>
+      </x:c>
+      <x:c r="T2" s="11" t="n">
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4226,49 +4294,61 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D3" s="4" t="str">
         <x:v>1区</x:v>
       </x:c>
       <x:c r="E3" s="4" t="str">
-        <x:v>信阳万达</x:v>
+        <x:v>许昌魏都万达</x:v>
       </x:c>
       <x:c r="F3" s="4" t="str">
-        <x:v>胡功海</x:v>
+        <x:v>吉祥</x:v>
       </x:c>
       <x:c r="G3" s="11" t="n">
-        <x:v>1900.15</x:v>
+        <x:v>13309</x:v>
       </x:c>
       <x:c r="H3" s="12" t="n">
-        <x:v>0.2691</x:v>
+        <x:v>1.0022</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>4252.1</x:v>
+        <x:v>13954.210000000001</x:v>
       </x:c>
       <x:c r="J3" s="11" t="n">
-        <x:v>-2351.9500000000003</x:v>
+        <x:v>-645.210000000001</x:v>
       </x:c>
       <x:c r="K3" s="11" t="n">
-        <x:v>1607.15</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="n">
-        <x:v>293</x:v>
+        <x:v>11701</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="n">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M3" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O3" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P3" s="12" t="n">
-        <x:v>0.0625</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O3" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="P3" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="Q3" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R3" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S3" s="12" t="n">
+        <x:v>0.1548</x:v>
+      </x:c>
+      <x:c r="T3" s="11" t="n">
+        <x:v>6280</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4276,49 +4356,61 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="4" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="n">
-        <x:v>-1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>3区</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>武汉荟聚</x:v>
+        <x:v>开封万达</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>周坤琪</x:v>
+        <x:v>李紫琪</x:v>
       </x:c>
       <x:c r="G4" s="11" t="n">
-        <x:v>1705</x:v>
+        <x:v>12906.4</x:v>
       </x:c>
       <x:c r="H4" s="12" t="n">
-        <x:v>0.6087</x:v>
+        <x:v>0.9423</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>7638</x:v>
+        <x:v>11780</x:v>
       </x:c>
       <x:c r="J4" s="11" t="n">
-        <x:v>-5933</x:v>
+        <x:v>1126.3999999999996</x:v>
       </x:c>
       <x:c r="K4" s="11" t="n">
-        <x:v>1705</x:v>
-      </x:c>
-      <x:c r="L4" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>10354</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="n">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="M4" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N4" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O4" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P4" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O4" s="12" t="n">
+        <x:v>0.3636</x:v>
+      </x:c>
+      <x:c r="P4" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q4" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S4" s="12" t="n">
+        <x:v>0.15380000000000002</x:v>
+      </x:c>
+      <x:c r="T4" s="11" t="n">
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4326,49 +4418,61 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>洛阳泉舜</x:v>
+        <x:v>商丘万达</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>蒋雪柯</x:v>
+        <x:v>谢航宇</x:v>
       </x:c>
       <x:c r="G5" s="11" t="n">
-        <x:v>1306</x:v>
+        <x:v>12008</x:v>
       </x:c>
       <x:c r="H5" s="12" t="n">
-        <x:v>1.9153</x:v>
+        <x:v>0.8608</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>6137</x:v>
+        <x:v>14139.25</x:v>
       </x:c>
       <x:c r="J5" s="11" t="n">
-        <x:v>-4831</x:v>
+        <x:v>-2131.25</x:v>
       </x:c>
       <x:c r="K5" s="11" t="n">
-        <x:v>1306</x:v>
-      </x:c>
-      <x:c r="L5" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>11408</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="n">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M5" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="O5" s="12" t="n">
+        <x:v>0.7082999999999999</x:v>
+      </x:c>
+      <x:c r="P5" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="Q5" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R5" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O5" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5" s="12" t="n">
-        <x:v>0.10869999999999999</x:v>
+      <x:c r="S5" s="12" t="n">
+        <x:v>0.2407</x:v>
+      </x:c>
+      <x:c r="T5" s="11" t="n">
+        <x:v>5424</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4376,49 +4480,61 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>关旭阁</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="n">
+        <x:v>11755</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="n">
+        <x:v>0.7099</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="n">
+        <x:v>7481</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>4274</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="n">
+        <x:v>10097</x:v>
+      </x:c>
+      <x:c r="L6" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="M6" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C6" s="4" t="n">
+      <x:c r="O6" s="12" t="n">
+        <x:v>0.4138</x:v>
+      </x:c>
+      <x:c r="P6" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="str">
-        <x:v>安阳万达</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="str">
-        <x:v>宋宋</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="n">
-        <x:v>946</x:v>
-      </x:c>
-      <x:c r="H6" s="12" t="n">
-        <x:v>0.5017</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="n">
-        <x:v>4795</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="n">
-        <x:v>-3849</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="n">
-        <x:v>946</x:v>
-      </x:c>
-      <x:c r="L6" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M6" s="4" t="n">
+      <x:c r="Q6" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R6" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="N6" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O6" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="12" t="n">
-        <x:v>0</x:v>
+      <x:c r="S6" s="12" t="n">
+        <x:v>0.1268</x:v>
+      </x:c>
+      <x:c r="T6" s="11" t="n">
+        <x:v>4299</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4426,49 +4542,61 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="4" t="n">
-        <x:v>13</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="4" t="n">
-        <x:v>7</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>新乡万达</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>贵诗涵</x:v>
+        <x:v>李茁壮</x:v>
       </x:c>
       <x:c r="G7" s="11" t="n">
-        <x:v>866</x:v>
+        <x:v>11732</x:v>
       </x:c>
       <x:c r="H7" s="12" t="n">
-        <x:v>0.4325</x:v>
+        <x:v>0.7874</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>3697</x:v>
+        <x:v>13928</x:v>
       </x:c>
       <x:c r="J7" s="11" t="n">
-        <x:v>-2831</x:v>
+        <x:v>-2196</x:v>
       </x:c>
       <x:c r="K7" s="11" t="n">
-        <x:v>866</x:v>
-      </x:c>
-      <x:c r="L7" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>10473</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M7" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="N7" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="12" t="n">
-        <x:v>0.075</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O7" s="12" t="n">
+        <x:v>0.6875</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q7" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R7" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S7" s="12" t="n">
+        <x:v>0.1304</x:v>
+      </x:c>
+      <x:c r="T7" s="11" t="n">
+        <x:v>900</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4476,10 +4604,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="4" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>2区</x:v>
@@ -4488,37 +4616,49 @@
         <x:v>焦作万达</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>张强</x:v>
+        <x:v>王梓恬</x:v>
       </x:c>
       <x:c r="G8" s="11" t="n">
-        <x:v>756</x:v>
+        <x:v>11397.2</x:v>
       </x:c>
       <x:c r="H8" s="12" t="n">
-        <x:v>0.44770000000000004</x:v>
+        <x:v>0.8056</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>4711</x:v>
+        <x:v>13116.6</x:v>
       </x:c>
       <x:c r="J8" s="11" t="n">
-        <x:v>-3955</x:v>
+        <x:v>-1719.3999999999996</x:v>
       </x:c>
       <x:c r="K8" s="11" t="n">
-        <x:v>756</x:v>
-      </x:c>
-      <x:c r="L8" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>9957</x:v>
+      </x:c>
+      <x:c r="L8" s="4" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M8" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N8" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O8" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="12" t="n">
-        <x:v>0.09380000000000001</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O8" s="12" t="n">
+        <x:v>0.5556</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="Q8" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="R8" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="12" t="n">
+        <x:v>0.050499999999999996</x:v>
+      </x:c>
+      <x:c r="T8" s="11" t="n">
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4526,49 +4666,61 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>襄阳高新万达</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>吴嘉丽</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="n">
+        <x:v>10738</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="n">
+        <x:v>0.7245999999999999</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
+        <x:v>13350</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>-2612</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="n">
+        <x:v>9560</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O9" s="12" t="n">
+        <x:v>0.7143</x:v>
+      </x:c>
+      <x:c r="P9" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C9" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="str">
-        <x:v>郑州中原万达</x:v>
-      </x:c>
-      <x:c r="F9" s="4" t="str">
-        <x:v>王嘉琦</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="n">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="H9" s="12" t="n">
-        <x:v>0.8273999999999999</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="n">
-        <x:v>5341</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="n">
-        <x:v>-4692</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="n">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="L9" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M9" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P9" s="12" t="n">
-        <x:v>0.1176</x:v>
+      <x:c r="R9" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S9" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="T9" s="11" t="n">
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4576,49 +4728,61 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="4" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="4" t="n">
+        <x:v>-8</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>郑州二七万象城</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
+        <x:v>橙子</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="n">
+        <x:v>10678</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="n">
+        <x:v>0.8542000000000001</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
+        <x:v>14975</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="n">
+        <x:v>-4297</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="n">
+        <x:v>8436</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M10" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O10" s="12" t="n">
+        <x:v>0.439</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="str">
-        <x:v>2区</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="str">
-        <x:v>周口万达</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="str">
-        <x:v>杨宁可</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="n">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="H10" s="12" t="n">
-        <x:v>0.6564</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="n">
-        <x:v>3513.2</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="n">
-        <x:v>-3042.2</x:v>
-      </x:c>
-      <x:c r="K10" s="11" t="n">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="L10" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M10" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N10" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="O10" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P10" s="12" t="n">
-        <x:v>0.037000000000000005</x:v>
+      <x:c r="Q10" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="R10" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S10" s="12" t="n">
+        <x:v>0.0294</x:v>
+      </x:c>
+      <x:c r="T10" s="11" t="n">
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4626,49 +4790,61 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C11" s="4" t="n">
-        <x:v>-7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>洛阳泉舜</x:v>
+        <x:v>郑州中原万达</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>王若涵</x:v>
+        <x:v>殷翔坤</x:v>
       </x:c>
       <x:c r="G11" s="11" t="n">
-        <x:v>461</x:v>
+        <x:v>10637</x:v>
       </x:c>
       <x:c r="H11" s="12" t="n">
-        <x:v>0.45030000000000003</x:v>
+        <x:v>1.0854000000000001</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>6408</x:v>
+        <x:v>7745</x:v>
       </x:c>
       <x:c r="J11" s="11" t="n">
-        <x:v>-5947</x:v>
+        <x:v>2892</x:v>
       </x:c>
       <x:c r="K11" s="11" t="n">
-        <x:v>461</x:v>
-      </x:c>
-      <x:c r="L11" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>10065</x:v>
+      </x:c>
+      <x:c r="L11" s="4" t="n">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M11" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N11" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P11" s="12" t="n">
-        <x:v>0.0851</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O11" s="12" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="P11" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S11" s="12" t="n">
+        <x:v>0.07690000000000001</x:v>
+      </x:c>
+      <x:c r="T11" s="11" t="n">
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4676,49 +4852,61 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="n">
+        <x:v>-9</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="str">
+        <x:v>焦作万达</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str">
+        <x:v>朱笛</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>10584</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="n">
+        <x:v>0.6545000000000001</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>14897</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="n">
+        <x:v>-4313</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="n">
+        <x:v>9392</x:v>
+      </x:c>
+      <x:c r="L12" s="4" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M12" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N12" s="4" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C12" s="4" t="n">
-        <x:v>-4</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="str">
-        <x:v>3区</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="str">
-        <x:v>安阳滑县吾悦</x:v>
-      </x:c>
-      <x:c r="F12" s="4" t="str">
-        <x:v>汤明放</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="n">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="H12" s="12" t="n">
-        <x:v>1.0974</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="n">
-        <x:v>5552.3</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="n">
-        <x:v>-5139.3</x:v>
-      </x:c>
-      <x:c r="K12" s="11" t="n">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="L12" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M12" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="N12" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O12" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="P12" s="12" t="n">
-        <x:v>0.1</x:v>
+      <x:c r="O12" s="12" t="n">
+        <x:v>0.5161</x:v>
+      </x:c>
+      <x:c r="P12" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q12" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="12" t="n">
+        <x:v>0.068</x:v>
+      </x:c>
+      <x:c r="T12" s="11" t="n">
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4726,10 +4914,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="4" t="n">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="4" t="n">
-        <x:v>-1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
         <x:v>1区</x:v>
@@ -4738,37 +4926,49 @@
         <x:v>襄阳高新万达</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>王爽</x:v>
+        <x:v>倪书馨</x:v>
       </x:c>
       <x:c r="G13" s="11" t="n">
-        <x:v>400</x:v>
+        <x:v>10139</x:v>
       </x:c>
       <x:c r="H13" s="12" t="n">
-        <x:v>1.1775</x:v>
+        <x:v>0.6840999999999999</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>4303</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="J13" s="11" t="n">
-        <x:v>-3903</x:v>
+        <x:v>4139</x:v>
       </x:c>
       <x:c r="K13" s="11" t="n">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="L13" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>9115</x:v>
+      </x:c>
+      <x:c r="L13" s="4" t="n">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M13" s="4" t="n">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="N13" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O13" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13" s="12" t="n">
-        <x:v>0.23079999999999998</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O13" s="12" t="n">
+        <x:v>0.7742</x:v>
+      </x:c>
+      <x:c r="P13" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S13" s="12" t="n">
+        <x:v>0.0625</x:v>
+      </x:c>
+      <x:c r="T13" s="11" t="n">
+        <x:v>969</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4776,49 +4976,61 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="4" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C14" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>2区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>洛阳中州万达</x:v>
+        <x:v>信阳万达</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>霍亭芮</x:v>
+        <x:v>李立</x:v>
       </x:c>
       <x:c r="G14" s="11" t="n">
-        <x:v>246</x:v>
+        <x:v>10020.800000000001</x:v>
       </x:c>
       <x:c r="H14" s="12" t="n">
-        <x:v>0.8713</x:v>
+        <x:v>0.8351000000000001</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>1229</x:v>
+        <x:v>6437.849999999999</x:v>
       </x:c>
       <x:c r="J14" s="11" t="n">
-        <x:v>-983</x:v>
+        <x:v>3582.9500000000016</x:v>
       </x:c>
       <x:c r="K14" s="11" t="n">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="L14" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>8991.6</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="n">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M14" s="4" t="n">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N14" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O14" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14" s="12" t="n">
-        <x:v>0.0909</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O14" s="12" t="n">
+        <x:v>0.6970000000000001</x:v>
+      </x:c>
+      <x:c r="P14" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R14" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S14" s="12" t="n">
+        <x:v>0.1875</x:v>
+      </x:c>
+      <x:c r="T14" s="11" t="n">
+        <x:v>1107.1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4826,49 +5038,61 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C15" s="4" t="n">
-        <x:v>-13</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>许昌魏都万达</x:v>
+        <x:v>郑州二七万象城</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
-        <x:v>孙刘柱</x:v>
+        <x:v>夏佳静</x:v>
       </x:c>
       <x:c r="G15" s="11" t="n">
-        <x:v>225.2</x:v>
+        <x:v>9950</x:v>
       </x:c>
       <x:c r="H15" s="12" t="n">
-        <x:v>0.37560000000000004</x:v>
+        <x:v>0.8690000000000001</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>10073.2</x:v>
+        <x:v>12096</x:v>
       </x:c>
       <x:c r="J15" s="11" t="n">
-        <x:v>-9848</x:v>
+        <x:v>-2146</x:v>
       </x:c>
       <x:c r="K15" s="11" t="n">
-        <x:v>225.2</x:v>
-      </x:c>
-      <x:c r="L15" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>8567</x:v>
+      </x:c>
+      <x:c r="L15" s="4" t="n">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="M15" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N15" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="O15" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O15" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="P15" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S15" s="12" t="n">
+        <x:v>0.0741</x:v>
+      </x:c>
+      <x:c r="T15" s="11" t="n">
+        <x:v>1600</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4876,49 +5100,61 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="4" t="n">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
         <x:v>1区</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>商丘万达</x:v>
+        <x:v>南阳吾悦</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>李烨</x:v>
+        <x:v>樊鑫</x:v>
       </x:c>
       <x:c r="G16" s="11" t="n">
-        <x:v>176</x:v>
+        <x:v>9661</x:v>
       </x:c>
       <x:c r="H16" s="12" t="n">
-        <x:v>0.7139</x:v>
+        <x:v>0.7729</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>1247</x:v>
+        <x:v>9840</x:v>
       </x:c>
       <x:c r="J16" s="11" t="n">
-        <x:v>-1071</x:v>
+        <x:v>-179</x:v>
       </x:c>
       <x:c r="K16" s="11" t="n">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="L16" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>8771</x:v>
+      </x:c>
+      <x:c r="L16" s="4" t="n">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="M16" s="4" t="n">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="N16" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O16" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P16" s="12" t="n">
-        <x:v>0.23079999999999998</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O16" s="12" t="n">
+        <x:v>0.6154</x:v>
+      </x:c>
+      <x:c r="P16" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="Q16" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R16" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S16" s="12" t="n">
+        <x:v>0.0909</x:v>
+      </x:c>
+      <x:c r="T16" s="11" t="n">
+        <x:v>3100</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4926,10 +5162,10 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="4" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C17" s="4" t="n">
-        <x:v>-10</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>1区</x:v>
@@ -4938,37 +5174,49 @@
         <x:v>南阳万达</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>王佳婷</x:v>
+        <x:v>李想</x:v>
       </x:c>
       <x:c r="G17" s="11" t="n">
-        <x:v>150</x:v>
+        <x:v>8560</x:v>
       </x:c>
       <x:c r="H17" s="12" t="n">
-        <x:v>0.4354</x:v>
+        <x:v>0.6903</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>5879</x:v>
+        <x:v>12439.400000000001</x:v>
       </x:c>
       <x:c r="J17" s="11" t="n">
-        <x:v>-5729</x:v>
+        <x:v>-3879.4000000000015</x:v>
       </x:c>
       <x:c r="K17" s="11" t="n">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="L17" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>8078</x:v>
+      </x:c>
+      <x:c r="L17" s="4" t="n">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="M17" s="4" t="n">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N17" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P17" s="12" t="n">
-        <x:v>0.02</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O17" s="12" t="n">
+        <x:v>0.7646999999999999</x:v>
+      </x:c>
+      <x:c r="P17" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q17" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S17" s="12" t="n">
+        <x:v>0.087</x:v>
+      </x:c>
+      <x:c r="T17" s="11" t="n">
+        <x:v>2799</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4976,49 +5224,61 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="n">
-        <x:v>-13</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>郑州惠济万达</x:v>
+        <x:v>洛阳中州万达</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>张运倩</x:v>
+        <x:v>张笑怡</x:v>
       </x:c>
       <x:c r="G18" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>8523</x:v>
       </x:c>
       <x:c r="H18" s="12" t="n">
-        <x:v>0.7475</x:v>
+        <x:v>0.7411</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>6199</x:v>
+        <x:v>6410</x:v>
       </x:c>
       <x:c r="J18" s="11" t="n">
-        <x:v>-6199</x:v>
+        <x:v>2113</x:v>
       </x:c>
       <x:c r="K18" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L18" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>6839</x:v>
+      </x:c>
+      <x:c r="L18" s="4" t="n">
+        <x:v>22</x:v>
       </x:c>
       <x:c r="M18" s="4" t="n">
-        <x:v>1</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="N18" s="4" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="O18" s="4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P18" s="12" t="n">
-        <x:v>0.1</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O18" s="12" t="n">
+        <x:v>0.5263</x:v>
+      </x:c>
+      <x:c r="P18" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="Q18" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R18" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="12" t="n">
+        <x:v>0.0339</x:v>
+      </x:c>
+      <x:c r="T18" s="11" t="n">
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5026,49 +5286,61 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="4" t="n">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>3区</x:v>
+        <x:v>1区</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>郑州二七万象城</x:v>
+        <x:v>南阳吾悦</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>郑金原</x:v>
+        <x:v>朱玫卉</x:v>
       </x:c>
       <x:c r="G19" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7787</x:v>
       </x:c>
       <x:c r="H19" s="12" t="n">
-        <x:v>0.5396</x:v>
+        <x:v>0.623</x:v>
       </x:c>
       <x:c r="I19" s="11" t="n">
-        <x:v>1787</x:v>
+        <x:v>7494</x:v>
       </x:c>
       <x:c r="J19" s="11" t="n">
-        <x:v>-1787</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K19" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L19" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>6937</x:v>
+      </x:c>
+      <x:c r="L19" s="4" t="n">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M19" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O19" s="12" t="n">
+        <x:v>0.5238</x:v>
+      </x:c>
+      <x:c r="P19" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="Q19" s="4" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="N19" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="O19" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P19" s="12" t="n">
-        <x:v>0.3333</x:v>
+      <x:c r="R19" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S19" s="12" t="n">
+        <x:v>0.087</x:v>
+      </x:c>
+      <x:c r="T19" s="11" t="n">
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5076,49 +5348,61 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="4" t="n">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="4" t="n">
-        <x:v>-3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
         <x:v>2区</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>郑州信万</x:v>
+        <x:v>周口万达</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>司聪慧</x:v>
+        <x:v>冯瀚文</x:v>
       </x:c>
       <x:c r="G20" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7664.2</x:v>
       </x:c>
       <x:c r="H20" s="12" t="n">
-        <x:v>0.48829999999999996</x:v>
+        <x:v>1.0743</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>3146</x:v>
+        <x:v>6466</x:v>
       </x:c>
       <x:c r="J20" s="11" t="n">
-        <x:v>-3146</x:v>
+        <x:v>1198.1999999999998</x:v>
       </x:c>
       <x:c r="K20" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L20" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>5909.2</x:v>
+      </x:c>
+      <x:c r="L20" s="4" t="n">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M20" s="4" t="n">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N20" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O20" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P20" s="12" t="n">
-        <x:v>0.16670000000000001</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O20" s="12" t="n">
+        <x:v>0.4242</x:v>
+      </x:c>
+      <x:c r="P20" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q20" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S20" s="12" t="n">
+        <x:v>0.08109999999999999</x:v>
+      </x:c>
+      <x:c r="T20" s="11" t="n">
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5132,43 +5416,55 @@
         <x:v>-6</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>1区</x:v>
+        <x:v>3区</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>南阳吾悦</x:v>
+        <x:v>武汉荟聚</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>齐继凤</x:v>
+        <x:v>邵娜娜</x:v>
       </x:c>
       <x:c r="G21" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>7443</x:v>
       </x:c>
       <x:c r="H21" s="12" t="n">
-        <x:v>0.16949999999999998</x:v>
+        <x:v>0.49950000000000006</x:v>
       </x:c>
       <x:c r="I21" s="11" t="n">
-        <x:v>3542</x:v>
+        <x:v>8655</x:v>
       </x:c>
       <x:c r="J21" s="11" t="n">
-        <x:v>-3542</x:v>
+        <x:v>-1212</x:v>
       </x:c>
       <x:c r="K21" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L21" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>6593</x:v>
+      </x:c>
+      <x:c r="L21" s="4" t="n">
+        <x:v>18</x:v>
       </x:c>
       <x:c r="M21" s="4" t="n">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N21" s="4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="O21" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P21" s="12" t="n">
-        <x:v>0.0196</x:v>
+      <x:c r="O21" s="12" t="n">
+        <x:v>0.68</x:v>
+      </x:c>
+      <x:c r="P21" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="Q21" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S21" s="12" t="n">
+        <x:v>0.0263</x:v>
+      </x:c>
+      <x:c r="T21" s="11" t="n">
+        <x:v>600</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -5176,55 +5472,2549 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="n">
+        <x:v>-12</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>王佳琳</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="n">
+        <x:v>7117</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="n">
+        <x:v>0.4336</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>12388</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="n">
+        <x:v>-5271</x:v>
+      </x:c>
+      <x:c r="K22" s="11" t="n">
+        <x:v>6184</x:v>
+      </x:c>
+      <x:c r="L22" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M22" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O22" s="12" t="n">
+        <x:v>0.4118</x:v>
+      </x:c>
+      <x:c r="P22" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q22" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S22" s="12" t="n">
+        <x:v>0.0909</x:v>
+      </x:c>
+      <x:c r="T22" s="11" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="4" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>洛阳中州万达</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str">
+        <x:v>党蕊蕊</x:v>
+      </x:c>
+      <x:c r="G23" s="11" t="n">
+        <x:v>6546</x:v>
+      </x:c>
+      <x:c r="H23" s="12" t="n">
+        <x:v>0.5692</x:v>
+      </x:c>
+      <x:c r="I23" s="11" t="n">
+        <x:v>7905</x:v>
+      </x:c>
+      <x:c r="J23" s="11" t="n">
+        <x:v>-1359</x:v>
+      </x:c>
+      <x:c r="K23" s="11" t="n">
+        <x:v>5361</x:v>
+      </x:c>
+      <x:c r="L23" s="4" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C22" s="4" t="n">
+      <x:c r="M23" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O23" s="12" t="n">
+        <x:v>0.5484</x:v>
+      </x:c>
+      <x:c r="P23" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="Q23" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S23" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T23" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="4" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="str">
+        <x:v>郑州信万</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str">
+        <x:v>余心如</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="n">
+        <x:v>5985</x:v>
+      </x:c>
+      <x:c r="H24" s="12" t="n">
+        <x:v>0.6505</x:v>
+      </x:c>
+      <x:c r="I24" s="11" t="n">
+        <x:v>4046</x:v>
+      </x:c>
+      <x:c r="J24" s="11" t="n">
+        <x:v>1939</x:v>
+      </x:c>
+      <x:c r="K24" s="11" t="n">
+        <x:v>5246</x:v>
+      </x:c>
+      <x:c r="L24" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M24" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N24" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O24" s="12" t="n">
+        <x:v>0.6087</x:v>
+      </x:c>
+      <x:c r="P24" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q24" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R24" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S24" s="12" t="n">
+        <x:v>0.0385</x:v>
+      </x:c>
+      <x:c r="T24" s="11" t="n">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="4" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>周口万达</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str">
+        <x:v>郑梦婷</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="n">
+        <x:v>5831.4</x:v>
+      </x:c>
+      <x:c r="H25" s="12" t="n">
+        <x:v>0.8173999999999999</x:v>
+      </x:c>
+      <x:c r="I25" s="11" t="n">
+        <x:v>4719</x:v>
+      </x:c>
+      <x:c r="J25" s="11" t="n">
+        <x:v>1112.3999999999996</x:v>
+      </x:c>
+      <x:c r="K25" s="11" t="n">
+        <x:v>5000.4</x:v>
+      </x:c>
+      <x:c r="L25" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M25" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N25" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O25" s="12" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P25" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q25" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R25" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S25" s="12" t="n">
+        <x:v>0.0294</x:v>
+      </x:c>
+      <x:c r="T25" s="11" t="n">
+        <x:v>450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="4" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C26" s="4" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="str">
+        <x:v>杨翠鸽</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="n">
+        <x:v>5827</x:v>
+      </x:c>
+      <x:c r="H26" s="12" t="n">
+        <x:v>0.4401</x:v>
+      </x:c>
+      <x:c r="I26" s="11" t="n">
+        <x:v>6135</x:v>
+      </x:c>
+      <x:c r="J26" s="11" t="n">
+        <x:v>-308</x:v>
+      </x:c>
+      <x:c r="K26" s="11" t="n">
+        <x:v>4798</x:v>
+      </x:c>
+      <x:c r="L26" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M26" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N26" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O26" s="12" t="n">
+        <x:v>0.4211</x:v>
+      </x:c>
+      <x:c r="P26" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="Q26" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R26" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S26" s="12" t="n">
+        <x:v>0.0968</x:v>
+      </x:c>
+      <x:c r="T26" s="11" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="4" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E27" s="4" t="str">
+        <x:v>郑州信万</x:v>
+      </x:c>
+      <x:c r="F27" s="4" t="str">
+        <x:v>薛飘飘</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="n">
+        <x:v>5794</x:v>
+      </x:c>
+      <x:c r="H27" s="12" t="n">
+        <x:v>0.5912</x:v>
+      </x:c>
+      <x:c r="I27" s="11" t="n">
+        <x:v>6086</x:v>
+      </x:c>
+      <x:c r="J27" s="11" t="n">
+        <x:v>-292</x:v>
+      </x:c>
+      <x:c r="K27" s="11" t="n">
+        <x:v>5749</x:v>
+      </x:c>
+      <x:c r="L27" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M27" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N27" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O27" s="12" t="n">
+        <x:v>0.8889</x:v>
+      </x:c>
+      <x:c r="P27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q27" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R27" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S27" s="12" t="n">
+        <x:v>0.17859999999999998</x:v>
+      </x:c>
+      <x:c r="T27" s="11" t="n">
+        <x:v>1995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="4" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D28" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E28" s="4" t="str">
+        <x:v>新乡万达</x:v>
+      </x:c>
+      <x:c r="F28" s="4" t="str">
+        <x:v>李淑艳</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="n">
+        <x:v>5017.2</x:v>
+      </x:c>
+      <x:c r="H28" s="12" t="n">
+        <x:v>0.7066</x:v>
+      </x:c>
+      <x:c r="I28" s="11" t="n">
+        <x:v>5822</x:v>
+      </x:c>
+      <x:c r="J28" s="11" t="n">
+        <x:v>-804.8000000000002</x:v>
+      </x:c>
+      <x:c r="K28" s="11" t="n">
+        <x:v>2867</x:v>
+      </x:c>
+      <x:c r="L28" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M28" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N28" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O28" s="12" t="n">
+        <x:v>0.22219999999999998</x:v>
+      </x:c>
+      <x:c r="P28" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q28" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R28" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S28" s="12" t="n">
+        <x:v>0.0167</x:v>
+      </x:c>
+      <x:c r="T28" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="4" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="str">
+        <x:v>郑州惠济万达</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="str">
+        <x:v>张赛宁</x:v>
+      </x:c>
+      <x:c r="G29" s="11" t="n">
+        <x:v>4537</x:v>
+      </x:c>
+      <x:c r="H29" s="12" t="n">
+        <x:v>0.6712</x:v>
+      </x:c>
+      <x:c r="I29" s="11" t="n">
+        <x:v>4362.99</x:v>
+      </x:c>
+      <x:c r="J29" s="11" t="n">
+        <x:v>174.01000000000022</x:v>
+      </x:c>
+      <x:c r="K29" s="11" t="n">
+        <x:v>4289</x:v>
+      </x:c>
+      <x:c r="L29" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M29" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O29" s="12" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="P29" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q29" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R29" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" s="12" t="n">
+        <x:v>0.027000000000000003</x:v>
+      </x:c>
+      <x:c r="T29" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="4" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" s="4" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C30" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E30" s="4" t="str">
+        <x:v>安阳万达</x:v>
+      </x:c>
+      <x:c r="F30" s="4" t="str">
+        <x:v>杨晶晶</x:v>
+      </x:c>
+      <x:c r="G30" s="11" t="n">
+        <x:v>3629.2</x:v>
+      </x:c>
+      <x:c r="H30" s="12" t="n">
+        <x:v>0.3425</x:v>
+      </x:c>
+      <x:c r="I30" s="11" t="n">
+        <x:v>3594</x:v>
+      </x:c>
+      <x:c r="J30" s="11" t="n">
+        <x:v>35.19999999999982</x:v>
+      </x:c>
+      <x:c r="K30" s="11" t="n">
+        <x:v>2999</x:v>
+      </x:c>
+      <x:c r="L30" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="M30" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N30" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O30" s="12" t="n">
+        <x:v>0.5385</x:v>
+      </x:c>
+      <x:c r="P30" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q30" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R30" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S30" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T30" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="4" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E31" s="4" t="str">
+        <x:v>安阳滑县吾悦</x:v>
+      </x:c>
+      <x:c r="F31" s="4" t="str">
+        <x:v>范超凡</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="n">
+        <x:v>3319</x:v>
+      </x:c>
+      <x:c r="H31" s="12" t="n">
+        <x:v>0.5811</x:v>
+      </x:c>
+      <x:c r="I31" s="11" t="n">
+        <x:v>2370</x:v>
+      </x:c>
+      <x:c r="J31" s="11" t="n">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="K31" s="11" t="n">
+        <x:v>2390</x:v>
+      </x:c>
+      <x:c r="L31" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="M31" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N31" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O31" s="12" t="n">
+        <x:v>0.35710000000000003</x:v>
+      </x:c>
+      <x:c r="P31" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q31" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R31" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S31" s="12" t="n">
+        <x:v>0.0435</x:v>
+      </x:c>
+      <x:c r="T31" s="11" t="n">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="4" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" s="4" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C32" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E32" s="4" t="str">
+        <x:v>郑州中原万达</x:v>
+      </x:c>
+      <x:c r="F32" s="4" t="str">
+        <x:v>张茹</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="n">
+        <x:v>3163</x:v>
+      </x:c>
+      <x:c r="H32" s="12" t="n">
+        <x:v>0.41619999999999996</x:v>
+      </x:c>
+      <x:c r="I32" s="11" t="n">
+        <x:v>3378</x:v>
+      </x:c>
+      <x:c r="J32" s="11" t="n">
+        <x:v>-215</x:v>
+      </x:c>
+      <x:c r="K32" s="11" t="n">
+        <x:v>2098</x:v>
+      </x:c>
+      <x:c r="L32" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M32" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N32" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O32" s="12" t="n">
+        <x:v>0.23079999999999998</x:v>
+      </x:c>
+      <x:c r="P32" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q32" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R32" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S32" s="12" t="n">
+        <x:v>0.0909</x:v>
+      </x:c>
+      <x:c r="T32" s="11" t="n">
+        <x:v>600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="4" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" s="4"/>
+      <x:c r="C33" s="4"/>
+      <x:c r="D33" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E33" s="4" t="str">
+        <x:v>武汉荟聚</x:v>
+      </x:c>
+      <x:c r="F33" s="4" t="str">
+        <x:v>郭文宇</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="H33" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="11"/>
+      <x:c r="J33" s="11"/>
+      <x:c r="K33" s="11" t="n">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="L33" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M33" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O33" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R33" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S33" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T33" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="4" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" s="4" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="n">
         <x:v>-4</x:v>
       </x:c>
-      <x:c r="D22" s="4" t="str">
+      <x:c r="D34" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E34" s="4" t="str">
+        <x:v>郑州中原万达</x:v>
+      </x:c>
+      <x:c r="F34" s="4" t="str">
+        <x:v>杨依梦</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="n">
+        <x:v>2845</x:v>
+      </x:c>
+      <x:c r="H34" s="12" t="n">
+        <x:v>0.36119999999999997</x:v>
+      </x:c>
+      <x:c r="I34" s="11" t="n">
+        <x:v>4432</x:v>
+      </x:c>
+      <x:c r="J34" s="11" t="n">
+        <x:v>-1587</x:v>
+      </x:c>
+      <x:c r="K34" s="11" t="n">
+        <x:v>2203</x:v>
+      </x:c>
+      <x:c r="L34" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M34" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N34" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="12" t="n">
+        <x:v>0.4167</x:v>
+      </x:c>
+      <x:c r="P34" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q34" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R34" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S34" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T34" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="4" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="n">
+        <x:v>-10</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E35" s="4" t="str">
+        <x:v>郑州惠济万达</x:v>
+      </x:c>
+      <x:c r="F35" s="4" t="str">
+        <x:v>杜珂源</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="n">
+        <x:v>2523</x:v>
+      </x:c>
+      <x:c r="H35" s="12" t="n">
+        <x:v>0.3732</x:v>
+      </x:c>
+      <x:c r="I35" s="11" t="n">
+        <x:v>6005</x:v>
+      </x:c>
+      <x:c r="J35" s="11" t="n">
+        <x:v>-3482</x:v>
+      </x:c>
+      <x:c r="K35" s="11" t="n">
+        <x:v>2393</x:v>
+      </x:c>
+      <x:c r="L35" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M35" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N35" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="O35" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="P35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S35" s="12" t="n">
+        <x:v>0.0833</x:v>
+      </x:c>
+      <x:c r="T35" s="11" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="4" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" s="4"/>
+      <x:c r="C36" s="4"/>
+      <x:c r="D36" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E36" s="4" t="str">
+        <x:v>武汉荟聚</x:v>
+      </x:c>
+      <x:c r="F36" s="4" t="str">
+        <x:v>代紫霞</x:v>
+      </x:c>
+      <x:c r="G36" s="11" t="n">
+        <x:v>1697</x:v>
+      </x:c>
+      <x:c r="H36" s="12" t="n">
+        <x:v>0.6171</x:v>
+      </x:c>
+      <x:c r="I36" s="11"/>
+      <x:c r="J36" s="11"/>
+      <x:c r="K36" s="11" t="n">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="L36" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M36" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="12" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="P36" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R36" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S36" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T36" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="4" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="n">
+        <x:v>-9</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="str">
         <x:v>1区</x:v>
       </x:c>
-      <x:c r="E22" s="4" t="str">
+      <x:c r="E37" s="4" t="str">
         <x:v>南阳万达</x:v>
       </x:c>
-      <x:c r="F22" s="4" t="str">
-        <x:v>蔺海芬</x:v>
-      </x:c>
-      <x:c r="G22" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="11" t="n">
-        <x:v>2088</x:v>
-      </x:c>
-      <x:c r="J22" s="11" t="n">
-        <x:v>-2088</x:v>
-      </x:c>
-      <x:c r="K22" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L22" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M22" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O22" s="4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P22" s="12" t="n">
-        <x:v>0</x:v>
+      <x:c r="F37" s="4" t="str">
+        <x:v>徐瑞迎</x:v>
+      </x:c>
+      <x:c r="G37" s="11" t="n">
+        <x:v>1340.02</x:v>
+      </x:c>
+      <x:c r="H37" s="12" t="n">
+        <x:v>0.1675</x:v>
+      </x:c>
+      <x:c r="I37" s="11" t="n">
+        <x:v>5768</x:v>
+      </x:c>
+      <x:c r="J37" s="11" t="n">
+        <x:v>-4427.98</x:v>
+      </x:c>
+      <x:c r="K37" s="11" t="n">
+        <x:v>722.02</x:v>
+      </x:c>
+      <x:c r="L37" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M37" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O37" s="12" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="P37" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="Q37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S37" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T37" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="4" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="4"/>
+      <x:c r="C38" s="4"/>
+      <x:c r="D38" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E38" s="4" t="str">
+        <x:v>新乡万达</x:v>
+      </x:c>
+      <x:c r="F38" s="4" t="str">
+        <x:v>徐彬淼</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="n">
+        <x:v>862</x:v>
+      </x:c>
+      <x:c r="H38" s="12" t="n">
+        <x:v>0.1351</x:v>
+      </x:c>
+      <x:c r="I38" s="11"/>
+      <x:c r="J38" s="11"/>
+      <x:c r="K38" s="11" t="n">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="L38" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M38" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N38" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O38" s="12" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="P38" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q38" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R38" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S38" s="12" t="n">
+        <x:v>0.0435</x:v>
+      </x:c>
+      <x:c r="T38" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="4" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E39" s="4" t="str">
+        <x:v>武汉荟聚</x:v>
+      </x:c>
+      <x:c r="F39" s="4" t="str">
+        <x:v>严诗仪</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="n">
+        <x:v>856</x:v>
+      </x:c>
+      <x:c r="H39" s="12" t="n">
+        <x:v>0.31129999999999997</x:v>
+      </x:c>
+      <x:c r="I39" s="11" t="n">
+        <x:v>2804</x:v>
+      </x:c>
+      <x:c r="J39" s="11" t="n">
+        <x:v>-1948</x:v>
+      </x:c>
+      <x:c r="K39" s="11" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L39" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M39" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="12" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="P39" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S39" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T39" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="4" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="4"/>
+      <x:c r="C40" s="4"/>
+      <x:c r="D40" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E40" s="4" t="str">
+        <x:v>郑州中原万达</x:v>
+      </x:c>
+      <x:c r="F40" s="4" t="str">
+        <x:v>聂梦梦</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H40" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="11"/>
+      <x:c r="J40" s="11"/>
+      <x:c r="K40" s="11" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="L40" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O40" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S40" s="12" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="T40" s="11" t="n">
+        <x:v>600</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf050a06bc54f27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27f8a0d9b7442e4"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="14" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="12" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>本周排名</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>上周排名</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
+        <x:v>排名变化</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>区域</x:v>
+      </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>门店</x:v>
+      </x:c>
+      <x:c r="F1" s="8" t="str">
+        <x:v>员工</x:v>
+      </x:c>
+      <x:c r="G1" s="8" t="str">
+        <x:v>本周总金额</x:v>
+      </x:c>
+      <x:c r="H1" s="8" t="str">
+        <x:v>完成率</x:v>
+      </x:c>
+      <x:c r="I1" s="8" t="str">
+        <x:v>上周总金额</x:v>
+      </x:c>
+      <x:c r="J1" s="8" t="str">
+        <x:v>金额增减</x:v>
+      </x:c>
+      <x:c r="K1" s="8" t="str">
+        <x:v>充值金额</x:v>
+      </x:c>
+      <x:c r="L1" s="8" t="str">
+        <x:v>散单金额</x:v>
+      </x:c>
+      <x:c r="M1" s="8" t="str">
+        <x:v>本周办卡数</x:v>
+      </x:c>
+      <x:c r="N1" s="8" t="str">
+        <x:v>本周新签卡数</x:v>
+      </x:c>
+      <x:c r="O1" s="8" t="str">
+        <x:v>本周续卡数</x:v>
+      </x:c>
+      <x:c r="P1" s="8" t="str">
+        <x:v>新签办卡率</x:v>
+      </x:c>
+      <x:c r="Q1" s="8" t="str">
+        <x:v>新签小卡数</x:v>
+      </x:c>
+      <x:c r="R1" s="8" t="str">
+        <x:v>新签中卡数</x:v>
+      </x:c>
+      <x:c r="S1" s="8" t="str">
+        <x:v>新签大卡数</x:v>
+      </x:c>
+      <x:c r="T1" s="8" t="str">
+        <x:v>续费率</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="str">
+        <x:v>蒋雪柯</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="n">
+        <x:v>6866</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="n">
+        <x:v>1.9153</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="n">
+        <x:v>6137</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="n">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="n">
+        <x:v>5560</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="n">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="M2" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N2" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O2" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="n">
+        <x:v>0.36</x:v>
+      </x:c>
+      <x:c r="Q2" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R2" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S2" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T2" s="12" t="n">
+        <x:v>0.10869999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="str">
+        <x:v>襄阳高新万达</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="str">
+        <x:v>王爽</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="n">
+        <x:v>6330</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="n">
+        <x:v>1.1775</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="n">
+        <x:v>4303</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="n">
+        <x:v>5930</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="M3" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N3" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="O3" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P3" s="12" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="Q3" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="R3" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S3" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T3" s="12" t="n">
+        <x:v>0.23079999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>武汉荟聚</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>周坤琪</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="n">
+        <x:v>5395</x:v>
+      </x:c>
+      <x:c r="H4" s="12" t="n">
+        <x:v>0.6087</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="n">
+        <x:v>7638</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="n">
+        <x:v>-2243</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="n">
+        <x:v>3690</x:v>
+      </x:c>
+      <x:c r="L4" s="11" t="n">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P4" s="12" t="n">
+        <x:v>0.44439999999999996</x:v>
+      </x:c>
+      <x:c r="Q4" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="R4" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T4" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>安阳滑县吾悦</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>汤明放</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="n">
+        <x:v>5241</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="n">
+        <x:v>1.0974</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="n">
+        <x:v>5552.3</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="n">
+        <x:v>-311.3000000000002</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="n">
+        <x:v>4828</x:v>
+      </x:c>
+      <x:c r="L5" s="11" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O5" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P5" s="12" t="n">
+        <x:v>0.6667000000000001</x:v>
+      </x:c>
+      <x:c r="Q5" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R5" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S5" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="T5" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>商丘万达</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>李烨</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="n">
+        <x:v>5123</x:v>
+      </x:c>
+      <x:c r="H6" s="12" t="n">
+        <x:v>0.7139</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="n">
+        <x:v>1247</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="n">
+        <x:v>3876</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="n">
+        <x:v>4947</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="M6" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O6" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="P6" s="12" t="n">
+        <x:v>0.7778</x:v>
+      </x:c>
+      <x:c r="Q6" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R6" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S6" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T6" s="12" t="n">
+        <x:v>0.23079999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="str">
+        <x:v>洛阳泉舜</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="str">
+        <x:v>王若涵</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="n">
+        <x:v>5061</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="n">
+        <x:v>0.45030000000000003</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="n">
+        <x:v>6408</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>-1347</x:v>
+      </x:c>
+      <x:c r="K7" s="11" t="n">
+        <x:v>4600</x:v>
+      </x:c>
+      <x:c r="L7" s="11" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="M7" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O7" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="P7" s="12" t="n">
+        <x:v>0.5385</x:v>
+      </x:c>
+      <x:c r="Q7" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="R7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T7" s="12" t="n">
+        <x:v>0.0851</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>郑州惠济万达</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>张运倩</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="n">
+        <x:v>5053</x:v>
+      </x:c>
+      <x:c r="H8" s="12" t="n">
+        <x:v>0.7475</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="n">
+        <x:v>6199</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>-1146</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="n">
+        <x:v>5053</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O8" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P8" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q8" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R8" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S8" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T8" s="12" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>郑州中原万达</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>王嘉琦</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="n">
+        <x:v>4637</x:v>
+      </x:c>
+      <x:c r="H9" s="12" t="n">
+        <x:v>0.8273999999999999</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
+        <x:v>5341</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>-704</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="n">
+        <x:v>3988</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="n">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O9" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P9" s="12" t="n">
+        <x:v>0.4375</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S9" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T9" s="12" t="n">
+        <x:v>0.1176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>焦作万达</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
+        <x:v>张强</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="n">
+        <x:v>4525</x:v>
+      </x:c>
+      <x:c r="H10" s="12" t="n">
+        <x:v>0.44770000000000004</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="n">
+        <x:v>4711</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="n">
+        <x:v>-186</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="n">
+        <x:v>3769</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="n">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="M10" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O10" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P10" s="12" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="Q10" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R10" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S10" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T10" s="12" t="n">
+        <x:v>0.09380000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="str">
+        <x:v>郑州二七万象城</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="str">
+        <x:v>郑金原</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="n">
+        <x:v>4487</x:v>
+      </x:c>
+      <x:c r="H11" s="12" t="n">
+        <x:v>0.5396</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="n">
+        <x:v>1787</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="n">
+        <x:v>2700</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="n">
+        <x:v>4487</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O11" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P11" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S11" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T11" s="12" t="n">
+        <x:v>0.3333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="4" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="n">
+        <x:v>-10</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="str">
+        <x:v>许昌魏都万达</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="str">
+        <x:v>孙刘柱</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>4125.2</x:v>
+      </x:c>
+      <x:c r="H12" s="12" t="n">
+        <x:v>0.37560000000000004</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="n">
+        <x:v>10073.2</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="n">
+        <x:v>-5948.000000000001</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="n">
+        <x:v>3900</x:v>
+      </x:c>
+      <x:c r="L12" s="11" t="n">
+        <x:v>225.2</x:v>
+      </x:c>
+      <x:c r="M12" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N12" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="12" t="n">
+        <x:v>0.8181999999999999</x:v>
+      </x:c>
+      <x:c r="Q12" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="S12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T12" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>郑州信万</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>司聪慧</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>4102</x:v>
+      </x:c>
+      <x:c r="H13" s="12" t="n">
+        <x:v>0.48829999999999996</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="n">
+        <x:v>3146</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="n">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="K13" s="11" t="n">
+        <x:v>4102</x:v>
+      </x:c>
+      <x:c r="L13" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O13" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="P13" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S13" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="T13" s="12" t="n">
+        <x:v>0.16670000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>开封万达</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>卢嘉诺</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="n">
+        <x:v>4029</x:v>
+      </x:c>
+      <x:c r="H14" s="12" t="n">
+        <x:v>0.5870000000000001</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="n">
+        <x:v>1266</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="n">
+        <x:v>2763</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="n">
+        <x:v>3951</x:v>
+      </x:c>
+      <x:c r="L14" s="11" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="M14" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="O14" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="12" t="n">
+        <x:v>0.9231</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R14" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="S14" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T14" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="str">
+        <x:v>周口万达</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>杨宁可</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="n">
+        <x:v>4015</x:v>
+      </x:c>
+      <x:c r="H15" s="12" t="n">
+        <x:v>0.6564</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="n">
+        <x:v>3513.2</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="n">
+        <x:v>501.8000000000002</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="n">
+        <x:v>3544</x:v>
+      </x:c>
+      <x:c r="L15" s="11" t="n">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="M15" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="O15" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" s="12" t="n">
+        <x:v>0.6429</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="S15" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T15" s="12" t="n">
+        <x:v>0.037000000000000005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="4" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>洛阳中州万达</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>霍亭芮</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="n">
+        <x:v>3921</x:v>
+      </x:c>
+      <x:c r="H16" s="12" t="n">
+        <x:v>0.8713</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="n">
+        <x:v>1229</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="n">
+        <x:v>2692</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="n">
+        <x:v>3675</x:v>
+      </x:c>
+      <x:c r="L16" s="11" t="n">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="M16" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N16" s="4" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="O16" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P16" s="12" t="n">
+        <x:v>0.8332999999999999</x:v>
+      </x:c>
+      <x:c r="Q16" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="R16" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S16" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T16" s="12" t="n">
+        <x:v>0.0909</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="4" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
+        <x:v>3区</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>安阳万达</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>宋宋</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
+        <x:v>3546</x:v>
+      </x:c>
+      <x:c r="H17" s="12" t="n">
+        <x:v>0.5017</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="n">
+        <x:v>4795</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="n">
+        <x:v>-1249</x:v>
+      </x:c>
+      <x:c r="K17" s="11" t="n">
+        <x:v>2600</x:v>
+      </x:c>
+      <x:c r="L17" s="11" t="n">
+        <x:v>946</x:v>
+      </x:c>
+      <x:c r="M17" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="O17" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="12" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="Q17" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="S17" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T17" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="n">
+        <x:v>-11</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>南阳万达</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>王佳婷</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="n">
+        <x:v>3483</x:v>
+      </x:c>
+      <x:c r="H18" s="12" t="n">
+        <x:v>0.4354</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="n">
+        <x:v>5879</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="n">
+        <x:v>-2396</x:v>
+      </x:c>
+      <x:c r="K18" s="11" t="n">
+        <x:v>3333</x:v>
+      </x:c>
+      <x:c r="L18" s="11" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="M18" s="4" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N18" s="4" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="O18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="12" t="n">
+        <x:v>0.7778</x:v>
+      </x:c>
+      <x:c r="Q18" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S18" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T18" s="12" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="4" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="n">
+        <x:v>-5</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="str">
+        <x:v>2区</x:v>
+      </x:c>
+      <x:c r="E19" s="4" t="str">
+        <x:v>新乡万达</x:v>
+      </x:c>
+      <x:c r="F19" s="4" t="str">
+        <x:v>贵诗涵</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="n">
+        <x:v>2760</x:v>
+      </x:c>
+      <x:c r="H19" s="12" t="n">
+        <x:v>0.4325</x:v>
+      </x:c>
+      <x:c r="I19" s="11" t="n">
+        <x:v>3697</x:v>
+      </x:c>
+      <x:c r="J19" s="11" t="n">
+        <x:v>-937</x:v>
+      </x:c>
+      <x:c r="K19" s="11" t="n">
+        <x:v>1894</x:v>
+      </x:c>
+      <x:c r="L19" s="11" t="n">
+        <x:v>866</x:v>
+      </x:c>
+      <x:c r="M19" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O19" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P19" s="12" t="n">
+        <x:v>0.11109999999999999</x:v>
+      </x:c>
+      <x:c r="Q19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T19" s="12" t="n">
+        <x:v>0.075</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="4" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="n">
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E20" s="4" t="str">
+        <x:v>信阳万达</x:v>
+      </x:c>
+      <x:c r="F20" s="4" t="str">
+        <x:v>胡功海</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="n">
+        <x:v>1900.15</x:v>
+      </x:c>
+      <x:c r="H20" s="12" t="n">
+        <x:v>0.2691</x:v>
+      </x:c>
+      <x:c r="I20" s="11" t="n">
+        <x:v>4252.1</x:v>
+      </x:c>
+      <x:c r="J20" s="11" t="n">
+        <x:v>-2351.9500000000003</x:v>
+      </x:c>
+      <x:c r="K20" s="11" t="n">
+        <x:v>1607.15</x:v>
+      </x:c>
+      <x:c r="L20" s="11" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="M20" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N20" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O20" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P20" s="12" t="n">
+        <x:v>0.5714</x:v>
+      </x:c>
+      <x:c r="Q20" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="R20" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="S20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T20" s="12" t="n">
+        <x:v>0.0625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="4" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="n">
+        <x:v>-6</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>南阳吾悦</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>齐继凤</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="n">
+        <x:v>1848</x:v>
+      </x:c>
+      <x:c r="H21" s="12" t="n">
+        <x:v>0.16949999999999998</x:v>
+      </x:c>
+      <x:c r="I21" s="11" t="n">
+        <x:v>3542</x:v>
+      </x:c>
+      <x:c r="J21" s="11" t="n">
+        <x:v>-1694</x:v>
+      </x:c>
+      <x:c r="K21" s="11" t="n">
+        <x:v>1848</x:v>
+      </x:c>
+      <x:c r="L21" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="4" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O21" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P21" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q21" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="R21" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T21" s="12" t="n">
+        <x:v>0.0196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="4" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="n">
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>1区</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>南阳万达</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>蔺海芬</x:v>
+      </x:c>
+      <x:c r="G22" s="11" t="n">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="H22" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="11" t="n">
+        <x:v>2088</x:v>
+      </x:c>
+      <x:c r="J22" s="11" t="n">
+        <x:v>-933</x:v>
+      </x:c>
+      <x:c r="K22" s="11" t="n">
+        <x:v>1155</x:v>
+      </x:c>
+      <x:c r="L22" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q22" s="4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T22" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea8ff2c1bf348be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R50da8e0c297848eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rc07d5eba41314fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R5ce8ff399df34f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Re6f0fb77c2a64362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R12614d5ca4d44c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Ref80f24deea24f0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8264b7ce0ebc445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rf7bdbe41001846ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="Re62e9e92fd644219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Re9e898aa9de8467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="Rf3e1c037d41b46b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="R6061861cc42943ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -737,7 +737,7 @@
         <x:v>0.081</x:v>
       </x:c>
       <x:c r="U2" s="11" t="n">
-        <x:v>92111.15</x:v>
+        <x:v>94211.15</x:v>
       </x:c>
       <x:c r="V2" s="11" t="n">
         <x:v>173051.7</x:v>
@@ -950,7 +950,7 @@
         <x:v>0.07216494845360824</x:v>
       </x:c>
       <x:c r="U5" s="11" t="n">
-        <x:v>20677</x:v>
+        <x:v>22777</x:v>
       </x:c>
       <x:c r="V5" s="11" t="n">
         <x:v>71688.6</x:v>
@@ -962,7 +962,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d3e6eee7dfd4988"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37236193628d4b40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1380,7 +1380,7 @@
         <x:v>0.0455</x:v>
       </x:c>
       <x:c r="V5" s="11" t="n">
-        <x:v>1500</x:v>
+        <x:v>3600</x:v>
       </x:c>
       <x:c r="W5" s="11" t="n">
         <x:v>19288</x:v>
@@ -2531,7 +2531,7 @@
         <x:v>17660</x:v>
       </x:c>
       <x:c r="G20" s="13" t="n">
-        <x:v>0.4062967157417894</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="H20" s="12" t="n">
         <x:v>-0.14468947431159854</x:v>
@@ -2585,7 +2585,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="Y20" s="14" t="str">
-        <x:v>完成率40.63%&lt;100%</x:v>
+        <x:v>完成率41.00%&lt;100%</x:v>
       </x:c>
       <x:c r="Z20" s="4" t="str">
         <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
@@ -2594,7 +2594,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfabfa93de7f24384"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfedc45b8c5034456"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4134,7 +4134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56d7fc05d79c4ff2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966129c7eb7c45cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6616,7 +6616,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re27f8a0d9b7442e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R246763a39fee4b1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8014,7 +8014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea8ff2c1bf348be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0826d0cb6ee44a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8264b7ce0ebc445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rf7bdbe41001846ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="Re62e9e92fd644219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="Re9e898aa9de8467c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="Rf3e1c037d41b46b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="R6061861cc42943ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R35123d1a7f4c45cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rf0800e62a453475e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R1cd8fb98b04e4d7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R8bf44e3e63c94138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R4eb45ce5757644b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Re36adc5cc16041fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -962,7 +962,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37236193628d4b40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R748804b74ac448c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1152,7 +1152,7 @@
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
       <x:c r="Z2" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1552,7 +1552,7 @@
         <x:v>当前已核指标无异常</x:v>
       </x:c>
       <x:c r="Z7" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2594,7 +2594,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfedc45b8c5034456"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93099a333e8843f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4134,7 +4134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R966129c7eb7c45cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d39292ad14744a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6616,7 +6616,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R246763a39fee4b1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc90f075bd24a2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8014,7 +8014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0826d0cb6ee44a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re779da2461fd4469"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R35123d1a7f4c45cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rf0800e62a453475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R1cd8fb98b04e4d7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R8bf44e3e63c94138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R4eb45ce5757644b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Re36adc5cc16041fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R9b200fcbff6947ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rbadbd42794144178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R3b534e3a9f6845bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R7d6f0525120b4d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R4d71e09404904d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Rfb442a23d5c3414f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -719,7 +719,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="O2" s="12" t="n">
-        <x:v>0.5465</x:v>
+        <x:v>0.5469565217391305</x:v>
       </x:c>
       <x:c r="P2" s="12" t="n">
         <x:v>0.5214626391096979</x:v>
@@ -962,7 +962,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R748804b74ac448c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c056c128eb4804"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2594,7 +2594,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93099a333e8843f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83c572f26dda4643"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4134,7 +4134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d39292ad14744a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0596783d884072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6616,7 +6616,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdc90f075bd24a2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26eb5c5676c54c65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8014,7 +8014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re779da2461fd4469"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R880d75b5a85749a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
+++ b/reports/20260720-20260726/熊猫密室周报核对底表_20260720-20260726.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R9b200fcbff6947ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rbadbd42794144178"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="R3b534e3a9f6845bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R7d6f0525120b4d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R4d71e09404904d82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Rfb442a23d5c3414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R1dc77b91eaac49b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌区域" sheetId="2" r:id="Rdad45047aafa4474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门店核心数据" sheetId="3" r:id="Rb1c4f1568161493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工卡型结构" sheetId="4" r:id="R2741e39323964d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店员全员排名" sheetId="5" r:id="R7dd7e6e98f474210"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="店长排名" sheetId="6" r:id="Rb1d9d720d48a4a56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -524,49 +524,57 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
-        <x:v>续费率</x:v>
+        <x:v>新签营收</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
+        <x:v>新签营收=总营收-总续卡金额；小程序截图“新卡金额”只作为办卡模块原始值留档，不能替代新签营收。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>引流/扫楼</x:v>
+        <x:v>续费率</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
+        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>卡型率</x:v>
+        <x:v>引流/扫楼</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
+        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>总办卡率</x:v>
+        <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B10" s="4" t="str">
+      <x:c r="B11" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -701,7 +709,7 @@
         <x:v>2149</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>247545.22</x:v>
+        <x:v>295048.92000000004</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
         <x:v>803</x:v>
@@ -772,7 +780,7 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>69224.62000000001</x:v>
+        <x:v>80260.02</x:v>
       </x:c>
       <x:c r="J3" s="4" t="n">
         <x:v>265</x:v>
@@ -843,7 +851,7 @@
         <x:v>898</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>93064.6</x:v>
+        <x:v>113531.2</x:v>
       </x:c>
       <x:c r="J4" s="4" t="n">
         <x:v>295</x:v>
@@ -914,7 +922,7 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>85256</x:v>
+        <x:v>101257.7</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
         <x:v>243</x:v>
@@ -962,7 +970,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c056c128eb4804"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb8fc01807f6432f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1101,7 +1109,7 @@
         <x:v>0.12211654892511403</x:v>
       </x:c>
       <x:c r="I2" s="11" t="n">
-        <x:v>15240</x:v>
+        <x:v>19082.4</x:v>
       </x:c>
       <x:c r="J2" s="4" t="n">
         <x:v>58</x:v>
@@ -1152,7 +1160,7 @@
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
       <x:c r="Z2" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1181,7 +1189,7 @@
         <x:v>-0.47829837173756273</x:v>
       </x:c>
       <x:c r="I3" s="11" t="n">
-        <x:v>16461</x:v>
+        <x:v>21717</x:v>
       </x:c>
       <x:c r="J3" s="4" t="n">
         <x:v>65</x:v>
@@ -1232,7 +1240,7 @@
         <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
       </x:c>
       <x:c r="Z3" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1261,7 +1269,7 @@
         <x:v>0.2677304228742167</x:v>
       </x:c>
       <x:c r="I4" s="11" t="n">
-        <x:v>20415</x:v>
+        <x:v>23648.5</x:v>
       </x:c>
       <x:c r="J4" s="4" t="n">
         <x:v>65</x:v>
@@ -1312,7 +1320,7 @@
         <x:v>完成率89.02%&lt;100%；新签小卡率62.75%&gt;40%</x:v>
       </x:c>
       <x:c r="Z4" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1341,7 +1349,7 @@
         <x:v>-0.1063842376190758</x:v>
       </x:c>
       <x:c r="I5" s="11" t="n">
-        <x:v>24256</x:v>
+        <x:v>26606</x:v>
       </x:c>
       <x:c r="J5" s="4" t="n">
         <x:v>61</x:v>
@@ -1392,7 +1400,7 @@
         <x:v>完成率68.71%&lt;100%；新签小卡率64.91%&gt;40%</x:v>
       </x:c>
       <x:c r="Z5" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1421,7 +1429,7 @@
         <x:v>0.03478178187696111</x:v>
       </x:c>
       <x:c r="I6" s="11" t="n">
-        <x:v>21837</x:v>
+        <x:v>24439</x:v>
       </x:c>
       <x:c r="J6" s="4" t="n">
         <x:v>72</x:v>
@@ -1472,7 +1480,7 @@
         <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
       </x:c>
       <x:c r="Z6" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1501,7 +1509,7 @@
         <x:v>0.858047053355388</x:v>
       </x:c>
       <x:c r="I7" s="11" t="n">
-        <x:v>22422.6</x:v>
+        <x:v>25383.6</x:v>
       </x:c>
       <x:c r="J7" s="4" t="n">
         <x:v>40</x:v>
@@ -1552,7 +1560,7 @@
         <x:v>当前已核指标无异常</x:v>
       </x:c>
       <x:c r="Z7" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图；占比分母已剔除团单10000元</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1581,7 +1589,7 @@
         <x:v>-0.13928788185312563</x:v>
       </x:c>
       <x:c r="I8" s="11" t="n">
-        <x:v>17570</x:v>
+        <x:v>21607</x:v>
       </x:c>
       <x:c r="J8" s="4" t="n">
         <x:v>51</x:v>
@@ -1632,7 +1640,7 @@
         <x:v>完成率78.67%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
       <x:c r="Z8" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1661,7 +1669,7 @@
         <x:v>0.04718606431852987</x:v>
       </x:c>
       <x:c r="I9" s="11" t="n">
-        <x:v>11554</x:v>
+        <x:v>14482</x:v>
       </x:c>
       <x:c r="J9" s="4" t="n">
         <x:v>33</x:v>
@@ -1712,7 +1720,7 @@
         <x:v>完成率70.36%&lt;100%；新签小卡率57.14%&gt;40%</x:v>
       </x:c>
       <x:c r="Z9" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1741,7 +1749,7 @@
         <x:v>-0.11908334470058655</x:v>
       </x:c>
       <x:c r="I10" s="11" t="n">
-        <x:v>11529</x:v>
+        <x:v>13425</x:v>
       </x:c>
       <x:c r="J10" s="4" t="n">
         <x:v>46</x:v>
@@ -1792,7 +1800,7 @@
         <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
       </x:c>
       <x:c r="Z10" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1821,7 +1829,7 @@
         <x:v>0.21117418202691499</x:v>
       </x:c>
       <x:c r="I11" s="11" t="n">
-        <x:v>14184</x:v>
+        <x:v>17390</x:v>
       </x:c>
       <x:c r="J11" s="4" t="n">
         <x:v>51</x:v>
@@ -1872,7 +1880,7 @@
         <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
       </x:c>
       <x:c r="Z11" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1899,7 +1907,7 @@
       </x:c>
       <x:c r="H12" s="12"/>
       <x:c r="I12" s="11" t="n">
-        <x:v>9243</x:v>
+        <x:v>11202.2</x:v>
       </x:c>
       <x:c r="J12" s="4" t="n">
         <x:v>39</x:v>
@@ -1950,7 +1958,7 @@
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
       <x:c r="Z12" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1979,7 +1987,7 @@
         <x:v>0.12578219742905652</x:v>
       </x:c>
       <x:c r="I13" s="11" t="n">
-        <x:v>7748</x:v>
+        <x:v>9442</x:v>
       </x:c>
       <x:c r="J13" s="4" t="n">
         <x:v>43</x:v>
@@ -2030,7 +2038,7 @@
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
       <x:c r="Z13" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -2059,7 +2067,7 @@
         <x:v>0.15935451336359052</x:v>
       </x:c>
       <x:c r="I14" s="11" t="n">
-        <x:v>11008</x:v>
+        <x:v>12004</x:v>
       </x:c>
       <x:c r="J14" s="4" t="n">
         <x:v>38</x:v>
@@ -2110,7 +2118,7 @@
         <x:v>完成率84.85%&lt;100%</x:v>
       </x:c>
       <x:c r="Z14" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -2139,7 +2147,7 @@
         <x:v>-0.4086722065063649</x:v>
       </x:c>
       <x:c r="I15" s="11" t="n">
-        <x:v>9833.02</x:v>
+        <x:v>11317.02</x:v>
       </x:c>
       <x:c r="J15" s="4" t="n">
         <x:v>34</x:v>
@@ -2190,7 +2198,7 @@
         <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
       </x:c>
       <x:c r="Z15" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2219,7 +2227,7 @@
         <x:v>-0.29841539341946594</x:v>
       </x:c>
       <x:c r="I16" s="11" t="n">
-        <x:v>8912</x:v>
+        <x:v>9023</x:v>
       </x:c>
       <x:c r="J16" s="4" t="n">
         <x:v>25</x:v>
@@ -2270,7 +2278,7 @@
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
       <x:c r="Z16" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -2299,7 +2307,7 @@
         <x:v>0.11515488847001155</x:v>
       </x:c>
       <x:c r="I17" s="11" t="n">
-        <x:v>9034.6</x:v>
+        <x:v>10434.800000000001</x:v>
       </x:c>
       <x:c r="J17" s="4" t="n">
         <x:v>31</x:v>
@@ -2350,7 +2358,7 @@
         <x:v>完成率66.01%&lt;100%</x:v>
       </x:c>
       <x:c r="Z17" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2379,7 +2387,7 @@
         <x:v>-0.18782625552124727</x:v>
       </x:c>
       <x:c r="I18" s="11" t="n">
-        <x:v>4837</x:v>
+        <x:v>8931.2</x:v>
       </x:c>
       <x:c r="J18" s="4" t="n">
         <x:v>18</x:v>
@@ -2430,7 +2438,7 @@
         <x:v>完成率61.88%&lt;100%</x:v>
       </x:c>
       <x:c r="Z18" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2457,7 +2465,7 @@
       </x:c>
       <x:c r="H19" s="12"/>
       <x:c r="I19" s="11" t="n">
-        <x:v>5862</x:v>
+        <x:v>7739</x:v>
       </x:c>
       <x:c r="J19" s="4" t="n">
         <x:v>20</x:v>
@@ -2508,7 +2516,7 @@
         <x:v>完成率52.35%&lt;100%</x:v>
       </x:c>
       <x:c r="Z19" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2537,7 +2545,7 @@
         <x:v>-0.14468947431159854</x:v>
       </x:c>
       <x:c r="I20" s="11" t="n">
-        <x:v>5599</x:v>
+        <x:v>7175.2</x:v>
       </x:c>
       <x:c r="J20" s="4" t="n">
         <x:v>13</x:v>
@@ -2588,13 +2596,13 @@
         <x:v>完成率41.00%&lt;100%</x:v>
       </x:c>
       <x:c r="Z20" s="4" t="str">
-        <x:v>小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
+        <x:v>新签营收=总营收-总续卡金额；新卡金额保留小程序截图原值；新客取飞书周表；老客取飞书账单按会员ID周内去重；总引流和扫楼取用户最终确认截图</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83c572f26dda4643"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74668e1706424b34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4134,7 +4142,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f0596783d884072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd6195488f2c4582"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6616,7 +6624,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26eb5c5676c54c65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c4bfd6b490446bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8014,7 +8022,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R880d75b5a85749a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf59290215954dd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>